--- a/QA_Audit_Sample.xlsx
+++ b/QA_Audit_Sample.xlsx
@@ -121,7 +121,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -139,11 +139,17 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="5" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="166" fontId="4" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="166" fontId="4" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -636,7 +642,7 @@
       </c>
       <c r="E6" s="7" t="inlineStr">
         <is>
-          <t>Bullying &amp; Harassment</t>
+          <t>Adult Sexual Solicitation &amp; Prostitution</t>
         </is>
       </c>
     </row>
@@ -1011,7 +1017,7 @@
       </c>
       <c r="E21" s="5" t="inlineStr">
         <is>
-          <t>Misinformation</t>
+          <t>Spam</t>
         </is>
       </c>
     </row>
@@ -1036,7 +1042,7 @@
       </c>
       <c r="E22" s="7" t="inlineStr">
         <is>
-          <t>Bullying &amp; Harassment</t>
+          <t>Adult Sexual Solicitation &amp; Prostitution</t>
         </is>
       </c>
     </row>
@@ -1086,7 +1092,7 @@
       </c>
       <c r="E24" s="7" t="inlineStr">
         <is>
-          <t>Spam</t>
+          <t>Bullying &amp; Harassment</t>
         </is>
       </c>
     </row>
@@ -1161,7 +1167,7 @@
       </c>
       <c r="E27" s="5" t="inlineStr">
         <is>
-          <t>Spam</t>
+          <t>Bullying &amp; Harassment</t>
         </is>
       </c>
     </row>
@@ -1186,7 +1192,7 @@
       </c>
       <c r="E28" s="7" t="inlineStr">
         <is>
-          <t>Bullying &amp; Harassment</t>
+          <t>Adult Sexual Solicitation &amp; Prostitution</t>
         </is>
       </c>
     </row>
@@ -1286,7 +1292,7 @@
       </c>
       <c r="E32" s="7" t="inlineStr">
         <is>
-          <t>Misinformation</t>
+          <t>Spam</t>
         </is>
       </c>
     </row>
@@ -1361,7 +1367,7 @@
       </c>
       <c r="E35" s="5" t="inlineStr">
         <is>
-          <t>Spam</t>
+          <t>Bullying &amp; Harassment</t>
         </is>
       </c>
     </row>
@@ -1461,7 +1467,7 @@
       </c>
       <c r="E39" s="5" t="inlineStr">
         <is>
-          <t>Bullying &amp; Harassment</t>
+          <t>Adult Sexual Solicitation &amp; Prostitution</t>
         </is>
       </c>
     </row>
@@ -1536,7 +1542,7 @@
       </c>
       <c r="E42" s="7" t="inlineStr">
         <is>
-          <t>Bullying &amp; Harassment</t>
+          <t>Adult Sexual Solicitation &amp; Prostitution</t>
         </is>
       </c>
     </row>
@@ -1561,7 +1567,7 @@
       </c>
       <c r="E43" s="5" t="inlineStr">
         <is>
-          <t>Spam</t>
+          <t>Bullying &amp; Harassment</t>
         </is>
       </c>
     </row>
@@ -1586,7 +1592,7 @@
       </c>
       <c r="E44" s="7" t="inlineStr">
         <is>
-          <t>Spam</t>
+          <t>Bullying &amp; Harassment</t>
         </is>
       </c>
     </row>
@@ -1611,7 +1617,7 @@
       </c>
       <c r="E45" s="5" t="inlineStr">
         <is>
-          <t>Bullying &amp; Harassment</t>
+          <t>Adult Sexual Solicitation &amp; Prostitution</t>
         </is>
       </c>
     </row>
@@ -1736,7 +1742,7 @@
       </c>
       <c r="E50" s="7" t="inlineStr">
         <is>
-          <t>Bullying &amp; Harassment</t>
+          <t>Adult Sexual Solicitation &amp; Prostitution</t>
         </is>
       </c>
     </row>
@@ -1786,7 +1792,7 @@
       </c>
       <c r="E52" s="7" t="inlineStr">
         <is>
-          <t>Spam</t>
+          <t>Bullying &amp; Harassment</t>
         </is>
       </c>
     </row>
@@ -1861,7 +1867,7 @@
       </c>
       <c r="E55" s="5" t="inlineStr">
         <is>
-          <t>Spam</t>
+          <t>Bullying &amp; Harassment</t>
         </is>
       </c>
     </row>
@@ -1886,7 +1892,7 @@
       </c>
       <c r="E56" s="7" t="inlineStr">
         <is>
-          <t>Bullying &amp; Harassment</t>
+          <t>Adult Sexual Solicitation &amp; Prostitution</t>
         </is>
       </c>
     </row>
@@ -1961,7 +1967,7 @@
       </c>
       <c r="E59" s="5" t="inlineStr">
         <is>
-          <t>Spam</t>
+          <t>Bullying &amp; Harassment</t>
         </is>
       </c>
     </row>
@@ -2036,7 +2042,7 @@
       </c>
       <c r="E62" s="7" t="inlineStr">
         <is>
-          <t>Bullying &amp; Harassment</t>
+          <t>Adult Sexual Solicitation &amp; Prostitution</t>
         </is>
       </c>
     </row>
@@ -2111,7 +2117,7 @@
       </c>
       <c r="E65" s="5" t="inlineStr">
         <is>
-          <t>Bullying &amp; Harassment</t>
+          <t>Adult Sexual Solicitation &amp; Prostitution</t>
         </is>
       </c>
     </row>
@@ -2186,7 +2192,7 @@
       </c>
       <c r="E68" s="7" t="inlineStr">
         <is>
-          <t>Spam</t>
+          <t>Bullying &amp; Harassment</t>
         </is>
       </c>
     </row>
@@ -2336,7 +2342,7 @@
       </c>
       <c r="E74" s="7" t="inlineStr">
         <is>
-          <t>Misinformation</t>
+          <t>Spam</t>
         </is>
       </c>
     </row>
@@ -2386,7 +2392,7 @@
       </c>
       <c r="E76" s="7" t="inlineStr">
         <is>
-          <t>Misinformation</t>
+          <t>Spam</t>
         </is>
       </c>
     </row>
@@ -2436,7 +2442,7 @@
       </c>
       <c r="E78" s="7" t="inlineStr">
         <is>
-          <t>Bullying &amp; Harassment</t>
+          <t>Adult Sexual Solicitation &amp; Prostitution</t>
         </is>
       </c>
     </row>
@@ -2536,7 +2542,7 @@
       </c>
       <c r="E82" s="7" t="inlineStr">
         <is>
-          <t>Bullying &amp; Harassment</t>
+          <t>Adult Sexual Solicitation &amp; Prostitution</t>
         </is>
       </c>
     </row>
@@ -2561,7 +2567,7 @@
       </c>
       <c r="E83" s="5" t="inlineStr">
         <is>
-          <t>Spam</t>
+          <t>Bullying &amp; Harassment</t>
         </is>
       </c>
     </row>
@@ -2586,7 +2592,7 @@
       </c>
       <c r="E84" s="7" t="inlineStr">
         <is>
-          <t>Bullying &amp; Harassment</t>
+          <t>Adult Sexual Solicitation &amp; Prostitution</t>
         </is>
       </c>
     </row>
@@ -2661,7 +2667,7 @@
       </c>
       <c r="E87" s="5" t="inlineStr">
         <is>
-          <t>Bullying &amp; Harassment</t>
+          <t>Adult Sexual Solicitation &amp; Prostitution</t>
         </is>
       </c>
     </row>
@@ -2736,7 +2742,7 @@
       </c>
       <c r="E90" s="7" t="inlineStr">
         <is>
-          <t>Bullying &amp; Harassment</t>
+          <t>Adult Sexual Solicitation &amp; Prostitution</t>
         </is>
       </c>
     </row>
@@ -2811,7 +2817,7 @@
       </c>
       <c r="E93" s="5" t="inlineStr">
         <is>
-          <t>Spam</t>
+          <t>Bullying &amp; Harassment</t>
         </is>
       </c>
     </row>
@@ -2911,7 +2917,7 @@
       </c>
       <c r="E97" s="5" t="inlineStr">
         <is>
-          <t>Spam</t>
+          <t>Bullying &amp; Harassment</t>
         </is>
       </c>
     </row>
@@ -2961,7 +2967,7 @@
       </c>
       <c r="E99" s="5" t="inlineStr">
         <is>
-          <t>Spam</t>
+          <t>Bullying &amp; Harassment</t>
         </is>
       </c>
     </row>
@@ -2986,7 +2992,7 @@
       </c>
       <c r="E100" s="7" t="inlineStr">
         <is>
-          <t>Bullying &amp; Harassment</t>
+          <t>Adult Sexual Solicitation &amp; Prostitution</t>
         </is>
       </c>
     </row>
@@ -3361,7 +3367,7 @@
       </c>
       <c r="E115" s="5" t="inlineStr">
         <is>
-          <t>Misinformation</t>
+          <t>Spam</t>
         </is>
       </c>
     </row>
@@ -3386,7 +3392,7 @@
       </c>
       <c r="E116" s="7" t="inlineStr">
         <is>
-          <t>Spam</t>
+          <t>Bullying &amp; Harassment</t>
         </is>
       </c>
     </row>
@@ -3486,7 +3492,7 @@
       </c>
       <c r="E120" s="7" t="inlineStr">
         <is>
-          <t>Spam</t>
+          <t>Bullying &amp; Harassment</t>
         </is>
       </c>
     </row>
@@ -3686,7 +3692,7 @@
       </c>
       <c r="E128" s="7" t="inlineStr">
         <is>
-          <t>Spam</t>
+          <t>Bullying &amp; Harassment</t>
         </is>
       </c>
     </row>
@@ -3736,7 +3742,7 @@
       </c>
       <c r="E130" s="7" t="inlineStr">
         <is>
-          <t>Bullying &amp; Harassment</t>
+          <t>Adult Sexual Solicitation &amp; Prostitution</t>
         </is>
       </c>
     </row>
@@ -3886,7 +3892,7 @@
       </c>
       <c r="E136" s="7" t="inlineStr">
         <is>
-          <t>Misinformation</t>
+          <t>Spam</t>
         </is>
       </c>
     </row>
@@ -3936,7 +3942,7 @@
       </c>
       <c r="E138" s="7" t="inlineStr">
         <is>
-          <t>Misinformation</t>
+          <t>Spam</t>
         </is>
       </c>
     </row>
@@ -3961,7 +3967,7 @@
       </c>
       <c r="E139" s="5" t="inlineStr">
         <is>
-          <t>Misinformation</t>
+          <t>Spam</t>
         </is>
       </c>
     </row>
@@ -4061,7 +4067,7 @@
       </c>
       <c r="E143" s="5" t="inlineStr">
         <is>
-          <t>Misinformation</t>
+          <t>Spam</t>
         </is>
       </c>
     </row>
@@ -4386,7 +4392,7 @@
       </c>
       <c r="E156" s="7" t="inlineStr">
         <is>
-          <t>Misinformation</t>
+          <t>Spam</t>
         </is>
       </c>
     </row>
@@ -4436,7 +4442,7 @@
       </c>
       <c r="E158" s="7" t="inlineStr">
         <is>
-          <t>Misinformation</t>
+          <t>Spam</t>
         </is>
       </c>
     </row>
@@ -4486,7 +4492,7 @@
       </c>
       <c r="E160" s="7" t="inlineStr">
         <is>
-          <t>Misinformation</t>
+          <t>Spam</t>
         </is>
       </c>
     </row>
@@ -4511,7 +4517,7 @@
       </c>
       <c r="E161" s="5" t="inlineStr">
         <is>
-          <t>Misinformation</t>
+          <t>Spam</t>
         </is>
       </c>
     </row>
@@ -4561,7 +4567,7 @@
       </c>
       <c r="E163" s="5" t="inlineStr">
         <is>
-          <t>Misinformation</t>
+          <t>Spam</t>
         </is>
       </c>
     </row>
@@ -4736,7 +4742,7 @@
       </c>
       <c r="E170" s="7" t="inlineStr">
         <is>
-          <t>Spam</t>
+          <t>Bullying &amp; Harassment</t>
         </is>
       </c>
     </row>
@@ -5111,7 +5117,7 @@
       </c>
       <c r="E185" s="5" t="inlineStr">
         <is>
-          <t>Bullying &amp; Harassment</t>
+          <t>Adult Sexual Solicitation &amp; Prostitution</t>
         </is>
       </c>
     </row>
@@ -5136,7 +5142,7 @@
       </c>
       <c r="E186" s="7" t="inlineStr">
         <is>
-          <t>Spam</t>
+          <t>Bullying &amp; Harassment</t>
         </is>
       </c>
     </row>
@@ -5161,7 +5167,7 @@
       </c>
       <c r="E187" s="5" t="inlineStr">
         <is>
-          <t>Bullying &amp; Harassment</t>
+          <t>Adult Sexual Solicitation &amp; Prostitution</t>
         </is>
       </c>
     </row>
@@ -5211,7 +5217,7 @@
       </c>
       <c r="E189" s="5" t="inlineStr">
         <is>
-          <t>Bullying &amp; Harassment</t>
+          <t>Adult Sexual Solicitation &amp; Prostitution</t>
         </is>
       </c>
     </row>
@@ -5236,7 +5242,7 @@
       </c>
       <c r="E190" s="7" t="inlineStr">
         <is>
-          <t>Spam</t>
+          <t>Bullying &amp; Harassment</t>
         </is>
       </c>
     </row>
@@ -5411,7 +5417,7 @@
       </c>
       <c r="E197" s="5" t="inlineStr">
         <is>
-          <t>Spam</t>
+          <t>Bullying &amp; Harassment</t>
         </is>
       </c>
     </row>
@@ -5486,7 +5492,7 @@
       </c>
       <c r="E200" s="7" t="inlineStr">
         <is>
-          <t>Bullying &amp; Harassment</t>
+          <t>Adult Sexual Solicitation &amp; Prostitution</t>
         </is>
       </c>
     </row>
@@ -5561,7 +5567,7 @@
       </c>
       <c r="E203" s="5" t="inlineStr">
         <is>
-          <t>Bullying &amp; Harassment</t>
+          <t>Adult Sexual Solicitation &amp; Prostitution</t>
         </is>
       </c>
     </row>
@@ -5761,7 +5767,7 @@
       </c>
       <c r="E211" s="5" t="inlineStr">
         <is>
-          <t>Bullying &amp; Harassment</t>
+          <t>Adult Sexual Solicitation &amp; Prostitution</t>
         </is>
       </c>
     </row>
@@ -5811,7 +5817,7 @@
       </c>
       <c r="E213" s="5" t="inlineStr">
         <is>
-          <t>Spam</t>
+          <t>Bullying &amp; Harassment</t>
         </is>
       </c>
     </row>
@@ -5836,7 +5842,7 @@
       </c>
       <c r="E214" s="7" t="inlineStr">
         <is>
-          <t>Bullying &amp; Harassment</t>
+          <t>Adult Sexual Solicitation &amp; Prostitution</t>
         </is>
       </c>
     </row>
@@ -5911,7 +5917,7 @@
       </c>
       <c r="E217" s="5" t="inlineStr">
         <is>
-          <t>Misinformation</t>
+          <t>Spam</t>
         </is>
       </c>
     </row>
@@ -5936,7 +5942,7 @@
       </c>
       <c r="E218" s="7" t="inlineStr">
         <is>
-          <t>Bullying &amp; Harassment</t>
+          <t>Adult Sexual Solicitation &amp; Prostitution</t>
         </is>
       </c>
     </row>
@@ -6061,7 +6067,7 @@
       </c>
       <c r="E223" s="5" t="inlineStr">
         <is>
-          <t>Misinformation</t>
+          <t>Spam</t>
         </is>
       </c>
     </row>
@@ -6186,7 +6192,7 @@
       </c>
       <c r="E228" s="7" t="inlineStr">
         <is>
-          <t>Spam</t>
+          <t>Bullying &amp; Harassment</t>
         </is>
       </c>
     </row>
@@ -6236,7 +6242,7 @@
       </c>
       <c r="E230" s="7" t="inlineStr">
         <is>
-          <t>Misinformation</t>
+          <t>Spam</t>
         </is>
       </c>
     </row>
@@ -6286,7 +6292,7 @@
       </c>
       <c r="E232" s="7" t="inlineStr">
         <is>
-          <t>Spam</t>
+          <t>Bullying &amp; Harassment</t>
         </is>
       </c>
     </row>
@@ -6336,7 +6342,7 @@
       </c>
       <c r="E234" s="7" t="inlineStr">
         <is>
-          <t>Spam</t>
+          <t>Bullying &amp; Harassment</t>
         </is>
       </c>
     </row>
@@ -6436,7 +6442,7 @@
       </c>
       <c r="E238" s="7" t="inlineStr">
         <is>
-          <t>Misinformation</t>
+          <t>Spam</t>
         </is>
       </c>
     </row>
@@ -6561,7 +6567,7 @@
       </c>
       <c r="E243" s="5" t="inlineStr">
         <is>
-          <t>Misinformation</t>
+          <t>Spam</t>
         </is>
       </c>
     </row>
@@ -6611,7 +6617,7 @@
       </c>
       <c r="E245" s="5" t="inlineStr">
         <is>
-          <t>Spam</t>
+          <t>Bullying &amp; Harassment</t>
         </is>
       </c>
     </row>
@@ -6636,7 +6642,7 @@
       </c>
       <c r="E246" s="7" t="inlineStr">
         <is>
-          <t>Misinformation</t>
+          <t>Spam</t>
         </is>
       </c>
     </row>
@@ -6836,7 +6842,7 @@
       </c>
       <c r="E254" s="7" t="inlineStr">
         <is>
-          <t>Bullying &amp; Harassment</t>
+          <t>Adult Sexual Solicitation &amp; Prostitution</t>
         </is>
       </c>
     </row>
@@ -6936,7 +6942,7 @@
       </c>
       <c r="E258" s="7" t="inlineStr">
         <is>
-          <t>Spam</t>
+          <t>Bullying &amp; Harassment</t>
         </is>
       </c>
     </row>
@@ -6986,7 +6992,7 @@
       </c>
       <c r="E260" s="7" t="inlineStr">
         <is>
-          <t>Bullying &amp; Harassment</t>
+          <t>Adult Sexual Solicitation &amp; Prostitution</t>
         </is>
       </c>
     </row>
@@ -7086,7 +7092,7 @@
       </c>
       <c r="E264" s="7" t="inlineStr">
         <is>
-          <t>Bullying &amp; Harassment</t>
+          <t>Adult Sexual Solicitation &amp; Prostitution</t>
         </is>
       </c>
     </row>
@@ -7186,7 +7192,7 @@
       </c>
       <c r="E268" s="7" t="inlineStr">
         <is>
-          <t>Spam</t>
+          <t>Bullying &amp; Harassment</t>
         </is>
       </c>
     </row>
@@ -7211,7 +7217,7 @@
       </c>
       <c r="E269" s="5" t="inlineStr">
         <is>
-          <t>Spam</t>
+          <t>Bullying &amp; Harassment</t>
         </is>
       </c>
     </row>
@@ -7311,7 +7317,7 @@
       </c>
       <c r="E273" s="5" t="inlineStr">
         <is>
-          <t>Bullying &amp; Harassment</t>
+          <t>Adult Sexual Solicitation &amp; Prostitution</t>
         </is>
       </c>
     </row>
@@ -7336,7 +7342,7 @@
       </c>
       <c r="E274" s="7" t="inlineStr">
         <is>
-          <t>Misinformation</t>
+          <t>Spam</t>
         </is>
       </c>
     </row>
@@ -7436,7 +7442,7 @@
       </c>
       <c r="E278" s="7" t="inlineStr">
         <is>
-          <t>Misinformation</t>
+          <t>Spam</t>
         </is>
       </c>
     </row>
@@ -7461,7 +7467,7 @@
       </c>
       <c r="E279" s="5" t="inlineStr">
         <is>
-          <t>Spam</t>
+          <t>Bullying &amp; Harassment</t>
         </is>
       </c>
     </row>
@@ -7486,7 +7492,7 @@
       </c>
       <c r="E280" s="7" t="inlineStr">
         <is>
-          <t>Spam</t>
+          <t>Bullying &amp; Harassment</t>
         </is>
       </c>
     </row>
@@ -7536,7 +7542,7 @@
       </c>
       <c r="E282" s="7" t="inlineStr">
         <is>
-          <t>Bullying &amp; Harassment</t>
+          <t>Adult Sexual Solicitation &amp; Prostitution</t>
         </is>
       </c>
     </row>
@@ -7561,7 +7567,7 @@
       </c>
       <c r="E283" s="5" t="inlineStr">
         <is>
-          <t>Bullying &amp; Harassment</t>
+          <t>Adult Sexual Solicitation &amp; Prostitution</t>
         </is>
       </c>
     </row>
@@ -7586,7 +7592,7 @@
       </c>
       <c r="E284" s="7" t="inlineStr">
         <is>
-          <t>Misinformation</t>
+          <t>Spam</t>
         </is>
       </c>
     </row>
@@ -7611,7 +7617,7 @@
       </c>
       <c r="E285" s="5" t="inlineStr">
         <is>
-          <t>Misinformation</t>
+          <t>Spam</t>
         </is>
       </c>
     </row>
@@ -7636,7 +7642,7 @@
       </c>
       <c r="E286" s="7" t="inlineStr">
         <is>
-          <t>Bullying &amp; Harassment</t>
+          <t>Adult Sexual Solicitation &amp; Prostitution</t>
         </is>
       </c>
     </row>
@@ -7686,7 +7692,7 @@
       </c>
       <c r="E288" s="7" t="inlineStr">
         <is>
-          <t>Misinformation</t>
+          <t>Spam</t>
         </is>
       </c>
     </row>
@@ -7711,7 +7717,7 @@
       </c>
       <c r="E289" s="5" t="inlineStr">
         <is>
-          <t>Misinformation</t>
+          <t>Spam</t>
         </is>
       </c>
     </row>
@@ -7761,7 +7767,7 @@
       </c>
       <c r="E291" s="5" t="inlineStr">
         <is>
-          <t>Bullying &amp; Harassment</t>
+          <t>Adult Sexual Solicitation &amp; Prostitution</t>
         </is>
       </c>
     </row>
@@ -7836,7 +7842,7 @@
       </c>
       <c r="E294" s="7" t="inlineStr">
         <is>
-          <t>Bullying &amp; Harassment</t>
+          <t>Adult Sexual Solicitation &amp; Prostitution</t>
         </is>
       </c>
     </row>
@@ -7861,7 +7867,7 @@
       </c>
       <c r="E295" s="5" t="inlineStr">
         <is>
-          <t>Misinformation</t>
+          <t>Spam</t>
         </is>
       </c>
     </row>
@@ -7911,7 +7917,7 @@
       </c>
       <c r="E297" s="5" t="inlineStr">
         <is>
-          <t>Spam</t>
+          <t>Bullying &amp; Harassment</t>
         </is>
       </c>
     </row>
@@ -8161,7 +8167,7 @@
       </c>
       <c r="E307" s="5" t="inlineStr">
         <is>
-          <t>Bullying &amp; Harassment</t>
+          <t>Adult Sexual Solicitation &amp; Prostitution</t>
         </is>
       </c>
     </row>
@@ -8311,7 +8317,7 @@
       </c>
       <c r="E313" s="5" t="inlineStr">
         <is>
-          <t>Misinformation</t>
+          <t>Spam</t>
         </is>
       </c>
     </row>
@@ -8361,7 +8367,7 @@
       </c>
       <c r="E315" s="5" t="inlineStr">
         <is>
-          <t>Misinformation</t>
+          <t>Spam</t>
         </is>
       </c>
     </row>
@@ -8386,7 +8392,7 @@
       </c>
       <c r="E316" s="7" t="inlineStr">
         <is>
-          <t>Misinformation</t>
+          <t>Spam</t>
         </is>
       </c>
     </row>
@@ -8486,7 +8492,7 @@
       </c>
       <c r="E320" s="7" t="inlineStr">
         <is>
-          <t>Misinformation</t>
+          <t>Spam</t>
         </is>
       </c>
     </row>
@@ -8711,7 +8717,7 @@
       </c>
       <c r="E329" s="5" t="inlineStr">
         <is>
-          <t>Spam</t>
+          <t>Bullying &amp; Harassment</t>
         </is>
       </c>
     </row>
@@ -8861,7 +8867,7 @@
       </c>
       <c r="E335" s="5" t="inlineStr">
         <is>
-          <t>Bullying &amp; Harassment</t>
+          <t>Adult Sexual Solicitation &amp; Prostitution</t>
         </is>
       </c>
     </row>
@@ -8911,7 +8917,7 @@
       </c>
       <c r="E337" s="5" t="inlineStr">
         <is>
-          <t>Bullying &amp; Harassment</t>
+          <t>Adult Sexual Solicitation &amp; Prostitution</t>
         </is>
       </c>
     </row>
@@ -9011,7 +9017,7 @@
       </c>
       <c r="E341" s="5" t="inlineStr">
         <is>
-          <t>Bullying &amp; Harassment</t>
+          <t>Adult Sexual Solicitation &amp; Prostitution</t>
         </is>
       </c>
     </row>
@@ -9036,7 +9042,7 @@
       </c>
       <c r="E342" s="7" t="inlineStr">
         <is>
-          <t>Bullying &amp; Harassment</t>
+          <t>Adult Sexual Solicitation &amp; Prostitution</t>
         </is>
       </c>
     </row>
@@ -9061,7 +9067,7 @@
       </c>
       <c r="E343" s="5" t="inlineStr">
         <is>
-          <t>Spam</t>
+          <t>Bullying &amp; Harassment</t>
         </is>
       </c>
     </row>
@@ -9211,7 +9217,7 @@
       </c>
       <c r="E349" s="5" t="inlineStr">
         <is>
-          <t>Misinformation</t>
+          <t>Spam</t>
         </is>
       </c>
     </row>
@@ -9236,7 +9242,7 @@
       </c>
       <c r="E350" s="7" t="inlineStr">
         <is>
-          <t>Spam</t>
+          <t>Bullying &amp; Harassment</t>
         </is>
       </c>
     </row>
@@ -9311,7 +9317,7 @@
       </c>
       <c r="E353" s="5" t="inlineStr">
         <is>
-          <t>Misinformation</t>
+          <t>Spam</t>
         </is>
       </c>
     </row>
@@ -9436,7 +9442,7 @@
       </c>
       <c r="E358" s="7" t="inlineStr">
         <is>
-          <t>Spam</t>
+          <t>Bullying &amp; Harassment</t>
         </is>
       </c>
     </row>
@@ -9461,7 +9467,7 @@
       </c>
       <c r="E359" s="5" t="inlineStr">
         <is>
-          <t>Misinformation</t>
+          <t>Spam</t>
         </is>
       </c>
     </row>
@@ -9486,7 +9492,7 @@
       </c>
       <c r="E360" s="7" t="inlineStr">
         <is>
-          <t>Misinformation</t>
+          <t>Spam</t>
         </is>
       </c>
     </row>
@@ -9611,7 +9617,7 @@
       </c>
       <c r="E365" s="5" t="inlineStr">
         <is>
-          <t>Misinformation</t>
+          <t>Spam</t>
         </is>
       </c>
     </row>
@@ -9661,7 +9667,7 @@
       </c>
       <c r="E367" s="5" t="inlineStr">
         <is>
-          <t>Spam</t>
+          <t>Bullying &amp; Harassment</t>
         </is>
       </c>
     </row>
@@ -9686,7 +9692,7 @@
       </c>
       <c r="E368" s="7" t="inlineStr">
         <is>
-          <t>Misinformation</t>
+          <t>Spam</t>
         </is>
       </c>
     </row>
@@ -9811,7 +9817,7 @@
       </c>
       <c r="E373" s="5" t="inlineStr">
         <is>
-          <t>Misinformation</t>
+          <t>Spam</t>
         </is>
       </c>
     </row>
@@ -9886,7 +9892,7 @@
       </c>
       <c r="E376" s="7" t="inlineStr">
         <is>
-          <t>Misinformation</t>
+          <t>Spam</t>
         </is>
       </c>
     </row>
@@ -9961,7 +9967,7 @@
       </c>
       <c r="E379" s="5" t="inlineStr">
         <is>
-          <t>Misinformation</t>
+          <t>Spam</t>
         </is>
       </c>
     </row>
@@ -10011,7 +10017,7 @@
       </c>
       <c r="E381" s="5" t="inlineStr">
         <is>
-          <t>Spam</t>
+          <t>Bullying &amp; Harassment</t>
         </is>
       </c>
     </row>
@@ -10036,7 +10042,7 @@
       </c>
       <c r="E382" s="7" t="inlineStr">
         <is>
-          <t>Misinformation</t>
+          <t>Spam</t>
         </is>
       </c>
     </row>
@@ -10061,7 +10067,7 @@
       </c>
       <c r="E383" s="5" t="inlineStr">
         <is>
-          <t>Misinformation</t>
+          <t>Spam</t>
         </is>
       </c>
     </row>
@@ -10161,7 +10167,7 @@
       </c>
       <c r="E387" s="5" t="inlineStr">
         <is>
-          <t>Spam</t>
+          <t>Bullying &amp; Harassment</t>
         </is>
       </c>
     </row>
@@ -10411,7 +10417,7 @@
       </c>
       <c r="E397" s="5" t="inlineStr">
         <is>
-          <t>Bullying &amp; Harassment</t>
+          <t>Adult Sexual Solicitation &amp; Prostitution</t>
         </is>
       </c>
     </row>
@@ -10436,7 +10442,7 @@
       </c>
       <c r="E398" s="7" t="inlineStr">
         <is>
-          <t>Spam</t>
+          <t>Bullying &amp; Harassment</t>
         </is>
       </c>
     </row>
@@ -10586,7 +10592,7 @@
       </c>
       <c r="E404" s="7" t="inlineStr">
         <is>
-          <t>Bullying &amp; Harassment</t>
+          <t>Adult Sexual Solicitation &amp; Prostitution</t>
         </is>
       </c>
     </row>
@@ -10611,7 +10617,7 @@
       </c>
       <c r="E405" s="5" t="inlineStr">
         <is>
-          <t>Misinformation</t>
+          <t>Spam</t>
         </is>
       </c>
     </row>
@@ -10711,7 +10717,7 @@
       </c>
       <c r="E409" s="5" t="inlineStr">
         <is>
-          <t>Bullying &amp; Harassment</t>
+          <t>Adult Sexual Solicitation &amp; Prostitution</t>
         </is>
       </c>
     </row>
@@ -10861,7 +10867,7 @@
       </c>
       <c r="E415" s="5" t="inlineStr">
         <is>
-          <t>Spam</t>
+          <t>Bullying &amp; Harassment</t>
         </is>
       </c>
     </row>
@@ -10911,7 +10917,7 @@
       </c>
       <c r="E417" s="5" t="inlineStr">
         <is>
-          <t>Spam</t>
+          <t>Bullying &amp; Harassment</t>
         </is>
       </c>
     </row>
@@ -10936,7 +10942,7 @@
       </c>
       <c r="E418" s="7" t="inlineStr">
         <is>
-          <t>Misinformation</t>
+          <t>Spam</t>
         </is>
       </c>
     </row>
@@ -10986,7 +10992,7 @@
       </c>
       <c r="E420" s="7" t="inlineStr">
         <is>
-          <t>Misinformation</t>
+          <t>Spam</t>
         </is>
       </c>
     </row>
@@ -11111,7 +11117,7 @@
       </c>
       <c r="E425" s="5" t="inlineStr">
         <is>
-          <t>Bullying &amp; Harassment</t>
+          <t>Adult Sexual Solicitation &amp; Prostitution</t>
         </is>
       </c>
     </row>
@@ -11186,7 +11192,7 @@
       </c>
       <c r="E428" s="7" t="inlineStr">
         <is>
-          <t>Misinformation</t>
+          <t>Spam</t>
         </is>
       </c>
     </row>
@@ -11236,7 +11242,7 @@
       </c>
       <c r="E430" s="7" t="inlineStr">
         <is>
-          <t>Spam</t>
+          <t>Bullying &amp; Harassment</t>
         </is>
       </c>
     </row>
@@ -11386,7 +11392,7 @@
       </c>
       <c r="E436" s="7" t="inlineStr">
         <is>
-          <t>Misinformation</t>
+          <t>Spam</t>
         </is>
       </c>
     </row>
@@ -11436,7 +11442,7 @@
       </c>
       <c r="E438" s="7" t="inlineStr">
         <is>
-          <t>Spam</t>
+          <t>Bullying &amp; Harassment</t>
         </is>
       </c>
     </row>
@@ -11486,7 +11492,7 @@
       </c>
       <c r="E440" s="7" t="inlineStr">
         <is>
-          <t>Spam</t>
+          <t>Bullying &amp; Harassment</t>
         </is>
       </c>
     </row>
@@ -11511,7 +11517,7 @@
       </c>
       <c r="E441" s="5" t="inlineStr">
         <is>
-          <t>Bullying &amp; Harassment</t>
+          <t>Adult Sexual Solicitation &amp; Prostitution</t>
         </is>
       </c>
     </row>
@@ -11536,7 +11542,7 @@
       </c>
       <c r="E442" s="7" t="inlineStr">
         <is>
-          <t>Bullying &amp; Harassment</t>
+          <t>Adult Sexual Solicitation &amp; Prostitution</t>
         </is>
       </c>
     </row>
@@ -11586,7 +11592,7 @@
       </c>
       <c r="E444" s="7" t="inlineStr">
         <is>
-          <t>Bullying &amp; Harassment</t>
+          <t>Adult Sexual Solicitation &amp; Prostitution</t>
         </is>
       </c>
     </row>
@@ -11686,7 +11692,7 @@
       </c>
       <c r="E448" s="7" t="inlineStr">
         <is>
-          <t>Misinformation</t>
+          <t>Spam</t>
         </is>
       </c>
     </row>
@@ -11811,7 +11817,7 @@
       </c>
       <c r="E453" s="5" t="inlineStr">
         <is>
-          <t>Bullying &amp; Harassment</t>
+          <t>Adult Sexual Solicitation &amp; Prostitution</t>
         </is>
       </c>
     </row>
@@ -11836,7 +11842,7 @@
       </c>
       <c r="E454" s="7" t="inlineStr">
         <is>
-          <t>Misinformation</t>
+          <t>Spam</t>
         </is>
       </c>
     </row>
@@ -11961,7 +11967,7 @@
       </c>
       <c r="E459" s="5" t="inlineStr">
         <is>
-          <t>Misinformation</t>
+          <t>Spam</t>
         </is>
       </c>
     </row>
@@ -12011,7 +12017,7 @@
       </c>
       <c r="E461" s="5" t="inlineStr">
         <is>
-          <t>Spam</t>
+          <t>Bullying &amp; Harassment</t>
         </is>
       </c>
     </row>
@@ -12061,7 +12067,7 @@
       </c>
       <c r="E463" s="5" t="inlineStr">
         <is>
-          <t>Bullying &amp; Harassment</t>
+          <t>Adult Sexual Solicitation &amp; Prostitution</t>
         </is>
       </c>
     </row>
@@ -12311,7 +12317,7 @@
       </c>
       <c r="E473" s="5" t="inlineStr">
         <is>
-          <t>Bullying &amp; Harassment</t>
+          <t>Adult Sexual Solicitation &amp; Prostitution</t>
         </is>
       </c>
     </row>
@@ -12461,7 +12467,7 @@
       </c>
       <c r="E479" s="5" t="inlineStr">
         <is>
-          <t>Bullying &amp; Harassment</t>
+          <t>Adult Sexual Solicitation &amp; Prostitution</t>
         </is>
       </c>
     </row>
@@ -12511,7 +12517,7 @@
       </c>
       <c r="E481" s="5" t="inlineStr">
         <is>
-          <t>Bullying &amp; Harassment</t>
+          <t>Adult Sexual Solicitation &amp; Prostitution</t>
         </is>
       </c>
     </row>
@@ -12611,7 +12617,7 @@
       </c>
       <c r="E485" s="5" t="inlineStr">
         <is>
-          <t>Bullying &amp; Harassment</t>
+          <t>Adult Sexual Solicitation &amp; Prostitution</t>
         </is>
       </c>
     </row>
@@ -12686,7 +12692,7 @@
       </c>
       <c r="E488" s="7" t="inlineStr">
         <is>
-          <t>Bullying &amp; Harassment</t>
+          <t>Adult Sexual Solicitation &amp; Prostitution</t>
         </is>
       </c>
     </row>
@@ -12936,7 +12942,7 @@
       </c>
       <c r="E498" s="7" t="inlineStr">
         <is>
-          <t>Misinformation</t>
+          <t>Spam</t>
         </is>
       </c>
     </row>
@@ -13111,7 +13117,7 @@
       </c>
       <c r="E505" s="5" t="inlineStr">
         <is>
-          <t>Bullying &amp; Harassment</t>
+          <t>Adult Sexual Solicitation &amp; Prostitution</t>
         </is>
       </c>
     </row>
@@ -13361,7 +13367,7 @@
       </c>
       <c r="E515" s="5" t="inlineStr">
         <is>
-          <t>Misinformation</t>
+          <t>Spam</t>
         </is>
       </c>
     </row>
@@ -13411,7 +13417,7 @@
       </c>
       <c r="E517" s="5" t="inlineStr">
         <is>
-          <t>Bullying &amp; Harassment</t>
+          <t>Adult Sexual Solicitation &amp; Prostitution</t>
         </is>
       </c>
     </row>
@@ -13461,7 +13467,7 @@
       </c>
       <c r="E519" s="5" t="inlineStr">
         <is>
-          <t>Bullying &amp; Harassment</t>
+          <t>Adult Sexual Solicitation &amp; Prostitution</t>
         </is>
       </c>
     </row>
@@ -13536,7 +13542,7 @@
       </c>
       <c r="E522" s="7" t="inlineStr">
         <is>
-          <t>Bullying &amp; Harassment</t>
+          <t>Adult Sexual Solicitation &amp; Prostitution</t>
         </is>
       </c>
     </row>
@@ -13686,7 +13692,7 @@
       </c>
       <c r="E528" s="7" t="inlineStr">
         <is>
-          <t>Bullying &amp; Harassment</t>
+          <t>Adult Sexual Solicitation &amp; Prostitution</t>
         </is>
       </c>
     </row>
@@ -13761,7 +13767,7 @@
       </c>
       <c r="E531" s="5" t="inlineStr">
         <is>
-          <t>Bullying &amp; Harassment</t>
+          <t>Adult Sexual Solicitation &amp; Prostitution</t>
         </is>
       </c>
     </row>
@@ -13811,7 +13817,7 @@
       </c>
       <c r="E533" s="5" t="inlineStr">
         <is>
-          <t>Bullying &amp; Harassment</t>
+          <t>Adult Sexual Solicitation &amp; Prostitution</t>
         </is>
       </c>
     </row>
@@ -13861,7 +13867,7 @@
       </c>
       <c r="E535" s="5" t="inlineStr">
         <is>
-          <t>Bullying &amp; Harassment</t>
+          <t>Adult Sexual Solicitation &amp; Prostitution</t>
         </is>
       </c>
     </row>
@@ -13886,7 +13892,7 @@
       </c>
       <c r="E536" s="7" t="inlineStr">
         <is>
-          <t>Misinformation</t>
+          <t>Spam</t>
         </is>
       </c>
     </row>
@@ -14011,7 +14017,7 @@
       </c>
       <c r="E541" s="5" t="inlineStr">
         <is>
-          <t>Misinformation</t>
+          <t>Spam</t>
         </is>
       </c>
     </row>
@@ -14036,7 +14042,7 @@
       </c>
       <c r="E542" s="7" t="inlineStr">
         <is>
-          <t>Spam</t>
+          <t>Bullying &amp; Harassment</t>
         </is>
       </c>
     </row>
@@ -14061,7 +14067,7 @@
       </c>
       <c r="E543" s="5" t="inlineStr">
         <is>
-          <t>Bullying &amp; Harassment</t>
+          <t>Adult Sexual Solicitation &amp; Prostitution</t>
         </is>
       </c>
     </row>
@@ -14161,7 +14167,7 @@
       </c>
       <c r="E547" s="5" t="inlineStr">
         <is>
-          <t>Bullying &amp; Harassment</t>
+          <t>Adult Sexual Solicitation &amp; Prostitution</t>
         </is>
       </c>
     </row>
@@ -14286,7 +14292,7 @@
       </c>
       <c r="E552" s="7" t="inlineStr">
         <is>
-          <t>Bullying &amp; Harassment</t>
+          <t>Adult Sexual Solicitation &amp; Prostitution</t>
         </is>
       </c>
     </row>
@@ -14386,7 +14392,7 @@
       </c>
       <c r="E556" s="7" t="inlineStr">
         <is>
-          <t>Misinformation</t>
+          <t>Spam</t>
         </is>
       </c>
     </row>
@@ -14411,7 +14417,7 @@
       </c>
       <c r="E557" s="5" t="inlineStr">
         <is>
-          <t>Spam</t>
+          <t>Bullying &amp; Harassment</t>
         </is>
       </c>
     </row>
@@ -14486,7 +14492,7 @@
       </c>
       <c r="E560" s="7" t="inlineStr">
         <is>
-          <t>Misinformation</t>
+          <t>Spam</t>
         </is>
       </c>
     </row>
@@ -14536,7 +14542,7 @@
       </c>
       <c r="E562" s="7" t="inlineStr">
         <is>
-          <t>Misinformation</t>
+          <t>Spam</t>
         </is>
       </c>
     </row>
@@ -14611,7 +14617,7 @@
       </c>
       <c r="E565" s="5" t="inlineStr">
         <is>
-          <t>Spam</t>
+          <t>Bullying &amp; Harassment</t>
         </is>
       </c>
     </row>
@@ -14636,7 +14642,7 @@
       </c>
       <c r="E566" s="7" t="inlineStr">
         <is>
-          <t>Spam</t>
+          <t>Bullying &amp; Harassment</t>
         </is>
       </c>
     </row>
@@ -14661,7 +14667,7 @@
       </c>
       <c r="E567" s="5" t="inlineStr">
         <is>
-          <t>Misinformation</t>
+          <t>Spam</t>
         </is>
       </c>
     </row>
@@ -14761,7 +14767,7 @@
       </c>
       <c r="E571" s="5" t="inlineStr">
         <is>
-          <t>Misinformation</t>
+          <t>Spam</t>
         </is>
       </c>
     </row>
@@ -14811,7 +14817,7 @@
       </c>
       <c r="E573" s="5" t="inlineStr">
         <is>
-          <t>Spam</t>
+          <t>Bullying &amp; Harassment</t>
         </is>
       </c>
     </row>
@@ -14911,7 +14917,7 @@
       </c>
       <c r="E577" s="5" t="inlineStr">
         <is>
-          <t>Bullying &amp; Harassment</t>
+          <t>Adult Sexual Solicitation &amp; Prostitution</t>
         </is>
       </c>
     </row>
@@ -14961,7 +14967,7 @@
       </c>
       <c r="E579" s="5" t="inlineStr">
         <is>
-          <t>Bullying &amp; Harassment</t>
+          <t>Adult Sexual Solicitation &amp; Prostitution</t>
         </is>
       </c>
     </row>
@@ -15261,7 +15267,7 @@
       </c>
       <c r="E591" s="5" t="inlineStr">
         <is>
-          <t>Bullying &amp; Harassment</t>
+          <t>Adult Sexual Solicitation &amp; Prostitution</t>
         </is>
       </c>
     </row>
@@ -15286,7 +15292,7 @@
       </c>
       <c r="E592" s="7" t="inlineStr">
         <is>
-          <t>Bullying &amp; Harassment</t>
+          <t>Adult Sexual Solicitation &amp; Prostitution</t>
         </is>
       </c>
     </row>
@@ -15386,7 +15392,7 @@
       </c>
       <c r="E596" s="7" t="inlineStr">
         <is>
-          <t>Misinformation</t>
+          <t>Spam</t>
         </is>
       </c>
     </row>
@@ -15486,7 +15492,7 @@
       </c>
       <c r="E600" s="7" t="inlineStr">
         <is>
-          <t>Misinformation</t>
+          <t>Spam</t>
         </is>
       </c>
     </row>
@@ -15561,7 +15567,7 @@
       </c>
       <c r="E603" s="5" t="inlineStr">
         <is>
-          <t>Bullying &amp; Harassment</t>
+          <t>Adult Sexual Solicitation &amp; Prostitution</t>
         </is>
       </c>
     </row>
@@ -15686,7 +15692,7 @@
       </c>
       <c r="E608" s="7" t="inlineStr">
         <is>
-          <t>Spam</t>
+          <t>Bullying &amp; Harassment</t>
         </is>
       </c>
     </row>
@@ -15786,7 +15792,7 @@
       </c>
       <c r="E612" s="7" t="inlineStr">
         <is>
-          <t>Spam</t>
+          <t>Bullying &amp; Harassment</t>
         </is>
       </c>
     </row>
@@ -15861,7 +15867,7 @@
       </c>
       <c r="E615" s="5" t="inlineStr">
         <is>
-          <t>Misinformation</t>
+          <t>Spam</t>
         </is>
       </c>
     </row>
@@ -15886,7 +15892,7 @@
       </c>
       <c r="E616" s="7" t="inlineStr">
         <is>
-          <t>Misinformation</t>
+          <t>Spam</t>
         </is>
       </c>
     </row>
@@ -15911,7 +15917,7 @@
       </c>
       <c r="E617" s="5" t="inlineStr">
         <is>
-          <t>Spam</t>
+          <t>Bullying &amp; Harassment</t>
         </is>
       </c>
     </row>
@@ -15961,7 +15967,7 @@
       </c>
       <c r="E619" s="5" t="inlineStr">
         <is>
-          <t>Misinformation</t>
+          <t>Spam</t>
         </is>
       </c>
     </row>
@@ -16061,7 +16067,7 @@
       </c>
       <c r="E623" s="5" t="inlineStr">
         <is>
-          <t>Spam</t>
+          <t>Bullying &amp; Harassment</t>
         </is>
       </c>
     </row>
@@ -16261,7 +16267,7 @@
       </c>
       <c r="E631" s="5" t="inlineStr">
         <is>
-          <t>Bullying &amp; Harassment</t>
+          <t>Adult Sexual Solicitation &amp; Prostitution</t>
         </is>
       </c>
     </row>
@@ -16311,7 +16317,7 @@
       </c>
       <c r="E633" s="5" t="inlineStr">
         <is>
-          <t>Misinformation</t>
+          <t>Spam</t>
         </is>
       </c>
     </row>
@@ -16361,7 +16367,7 @@
       </c>
       <c r="E635" s="5" t="inlineStr">
         <is>
-          <t>Spam</t>
+          <t>Bullying &amp; Harassment</t>
         </is>
       </c>
     </row>
@@ -16411,7 +16417,7 @@
       </c>
       <c r="E637" s="5" t="inlineStr">
         <is>
-          <t>Spam</t>
+          <t>Bullying &amp; Harassment</t>
         </is>
       </c>
     </row>
@@ -16536,7 +16542,7 @@
       </c>
       <c r="E642" s="7" t="inlineStr">
         <is>
-          <t>Bullying &amp; Harassment</t>
+          <t>Adult Sexual Solicitation &amp; Prostitution</t>
         </is>
       </c>
     </row>
@@ -16636,7 +16642,7 @@
       </c>
       <c r="E646" s="7" t="inlineStr">
         <is>
-          <t>Bullying &amp; Harassment</t>
+          <t>Adult Sexual Solicitation &amp; Prostitution</t>
         </is>
       </c>
     </row>
@@ -16686,7 +16692,7 @@
       </c>
       <c r="E648" s="7" t="inlineStr">
         <is>
-          <t>Spam</t>
+          <t>Bullying &amp; Harassment</t>
         </is>
       </c>
     </row>
@@ -16736,7 +16742,7 @@
       </c>
       <c r="E650" s="7" t="inlineStr">
         <is>
-          <t>Spam</t>
+          <t>Bullying &amp; Harassment</t>
         </is>
       </c>
     </row>
@@ -16761,7 +16767,7 @@
       </c>
       <c r="E651" s="5" t="inlineStr">
         <is>
-          <t>Misinformation</t>
+          <t>Spam</t>
         </is>
       </c>
     </row>
@@ -16811,7 +16817,7 @@
       </c>
       <c r="E653" s="5" t="inlineStr">
         <is>
-          <t>Misinformation</t>
+          <t>Spam</t>
         </is>
       </c>
     </row>
@@ -16911,7 +16917,7 @@
       </c>
       <c r="E657" s="5" t="inlineStr">
         <is>
-          <t>Misinformation</t>
+          <t>Spam</t>
         </is>
       </c>
     </row>
@@ -17011,7 +17017,7 @@
       </c>
       <c r="E661" s="5" t="inlineStr">
         <is>
-          <t>Bullying &amp; Harassment</t>
+          <t>Adult Sexual Solicitation &amp; Prostitution</t>
         </is>
       </c>
     </row>
@@ -17036,7 +17042,7 @@
       </c>
       <c r="E662" s="7" t="inlineStr">
         <is>
-          <t>Bullying &amp; Harassment</t>
+          <t>Adult Sexual Solicitation &amp; Prostitution</t>
         </is>
       </c>
     </row>
@@ -17111,7 +17117,7 @@
       </c>
       <c r="E665" s="5" t="inlineStr">
         <is>
-          <t>Bullying &amp; Harassment</t>
+          <t>Adult Sexual Solicitation &amp; Prostitution</t>
         </is>
       </c>
     </row>
@@ -17186,7 +17192,7 @@
       </c>
       <c r="E668" s="7" t="inlineStr">
         <is>
-          <t>Spam</t>
+          <t>Bullying &amp; Harassment</t>
         </is>
       </c>
     </row>
@@ -17211,7 +17217,7 @@
       </c>
       <c r="E669" s="5" t="inlineStr">
         <is>
-          <t>Bullying &amp; Harassment</t>
+          <t>Adult Sexual Solicitation &amp; Prostitution</t>
         </is>
       </c>
     </row>
@@ -17236,7 +17242,7 @@
       </c>
       <c r="E670" s="7" t="inlineStr">
         <is>
-          <t>Misinformation</t>
+          <t>Spam</t>
         </is>
       </c>
     </row>
@@ -17286,7 +17292,7 @@
       </c>
       <c r="E672" s="7" t="inlineStr">
         <is>
-          <t>Bullying &amp; Harassment</t>
+          <t>Adult Sexual Solicitation &amp; Prostitution</t>
         </is>
       </c>
     </row>
@@ -17311,7 +17317,7 @@
       </c>
       <c r="E673" s="5" t="inlineStr">
         <is>
-          <t>Misinformation</t>
+          <t>Spam</t>
         </is>
       </c>
     </row>
@@ -17436,7 +17442,7 @@
       </c>
       <c r="E678" s="7" t="inlineStr">
         <is>
-          <t>Bullying &amp; Harassment</t>
+          <t>Adult Sexual Solicitation &amp; Prostitution</t>
         </is>
       </c>
     </row>
@@ -17461,7 +17467,7 @@
       </c>
       <c r="E679" s="5" t="inlineStr">
         <is>
-          <t>Misinformation</t>
+          <t>Spam</t>
         </is>
       </c>
     </row>
@@ -17586,7 +17592,7 @@
       </c>
       <c r="E684" s="7" t="inlineStr">
         <is>
-          <t>Bullying &amp; Harassment</t>
+          <t>Adult Sexual Solicitation &amp; Prostitution</t>
         </is>
       </c>
     </row>
@@ -17636,7 +17642,7 @@
       </c>
       <c r="E686" s="7" t="inlineStr">
         <is>
-          <t>Spam</t>
+          <t>Bullying &amp; Harassment</t>
         </is>
       </c>
     </row>
@@ -17686,7 +17692,7 @@
       </c>
       <c r="E688" s="7" t="inlineStr">
         <is>
-          <t>Bullying &amp; Harassment</t>
+          <t>Adult Sexual Solicitation &amp; Prostitution</t>
         </is>
       </c>
     </row>
@@ -17861,7 +17867,7 @@
       </c>
       <c r="E695" s="5" t="inlineStr">
         <is>
-          <t>Bullying &amp; Harassment</t>
+          <t>Adult Sexual Solicitation &amp; Prostitution</t>
         </is>
       </c>
     </row>
@@ -17886,7 +17892,7 @@
       </c>
       <c r="E696" s="7" t="inlineStr">
         <is>
-          <t>Misinformation</t>
+          <t>Spam</t>
         </is>
       </c>
     </row>
@@ -17986,7 +17992,7 @@
       </c>
       <c r="E700" s="7" t="inlineStr">
         <is>
-          <t>Bullying &amp; Harassment</t>
+          <t>Adult Sexual Solicitation &amp; Prostitution</t>
         </is>
       </c>
     </row>
@@ -18061,7 +18067,7 @@
       </c>
       <c r="E703" s="5" t="inlineStr">
         <is>
-          <t>Bullying &amp; Harassment</t>
+          <t>Adult Sexual Solicitation &amp; Prostitution</t>
         </is>
       </c>
     </row>
@@ -18086,7 +18092,7 @@
       </c>
       <c r="E704" s="7" t="inlineStr">
         <is>
-          <t>Spam</t>
+          <t>Bullying &amp; Harassment</t>
         </is>
       </c>
     </row>
@@ -18186,7 +18192,7 @@
       </c>
       <c r="E708" s="7" t="inlineStr">
         <is>
-          <t>Misinformation</t>
+          <t>Spam</t>
         </is>
       </c>
     </row>
@@ -18261,7 +18267,7 @@
       </c>
       <c r="E711" s="5" t="inlineStr">
         <is>
-          <t>Misinformation</t>
+          <t>Spam</t>
         </is>
       </c>
     </row>
@@ -18286,7 +18292,7 @@
       </c>
       <c r="E712" s="7" t="inlineStr">
         <is>
-          <t>Bullying &amp; Harassment</t>
+          <t>Adult Sexual Solicitation &amp; Prostitution</t>
         </is>
       </c>
     </row>
@@ -18336,7 +18342,7 @@
       </c>
       <c r="E714" s="7" t="inlineStr">
         <is>
-          <t>Spam</t>
+          <t>Bullying &amp; Harassment</t>
         </is>
       </c>
     </row>
@@ -18361,7 +18367,7 @@
       </c>
       <c r="E715" s="5" t="inlineStr">
         <is>
-          <t>Bullying &amp; Harassment</t>
+          <t>Adult Sexual Solicitation &amp; Prostitution</t>
         </is>
       </c>
     </row>
@@ -18386,7 +18392,7 @@
       </c>
       <c r="E716" s="7" t="inlineStr">
         <is>
-          <t>Misinformation</t>
+          <t>Spam</t>
         </is>
       </c>
     </row>
@@ -18411,7 +18417,7 @@
       </c>
       <c r="E717" s="5" t="inlineStr">
         <is>
-          <t>Spam</t>
+          <t>Bullying &amp; Harassment</t>
         </is>
       </c>
     </row>
@@ -18586,7 +18592,7 @@
       </c>
       <c r="E724" s="7" t="inlineStr">
         <is>
-          <t>Bullying &amp; Harassment</t>
+          <t>Adult Sexual Solicitation &amp; Prostitution</t>
         </is>
       </c>
     </row>
@@ -18611,7 +18617,7 @@
       </c>
       <c r="E725" s="5" t="inlineStr">
         <is>
-          <t>Misinformation</t>
+          <t>Spam</t>
         </is>
       </c>
     </row>
@@ -18861,7 +18867,7 @@
       </c>
       <c r="E735" s="5" t="inlineStr">
         <is>
-          <t>Misinformation</t>
+          <t>Spam</t>
         </is>
       </c>
     </row>
@@ -18936,7 +18942,7 @@
       </c>
       <c r="E738" s="7" t="inlineStr">
         <is>
-          <t>Misinformation</t>
+          <t>Spam</t>
         </is>
       </c>
     </row>
@@ -18986,7 +18992,7 @@
       </c>
       <c r="E740" s="7" t="inlineStr">
         <is>
-          <t>Spam</t>
+          <t>Bullying &amp; Harassment</t>
         </is>
       </c>
     </row>
@@ -19061,7 +19067,7 @@
       </c>
       <c r="E743" s="5" t="inlineStr">
         <is>
-          <t>Spam</t>
+          <t>Bullying &amp; Harassment</t>
         </is>
       </c>
     </row>
@@ -19086,7 +19092,7 @@
       </c>
       <c r="E744" s="7" t="inlineStr">
         <is>
-          <t>Spam</t>
+          <t>Bullying &amp; Harassment</t>
         </is>
       </c>
     </row>
@@ -19111,7 +19117,7 @@
       </c>
       <c r="E745" s="5" t="inlineStr">
         <is>
-          <t>Spam</t>
+          <t>Bullying &amp; Harassment</t>
         </is>
       </c>
     </row>
@@ -19136,7 +19142,7 @@
       </c>
       <c r="E746" s="7" t="inlineStr">
         <is>
-          <t>Misinformation</t>
+          <t>Spam</t>
         </is>
       </c>
     </row>
@@ -19286,7 +19292,7 @@
       </c>
       <c r="E752" s="7" t="inlineStr">
         <is>
-          <t>Spam</t>
+          <t>Bullying &amp; Harassment</t>
         </is>
       </c>
     </row>
@@ -19511,7 +19517,7 @@
       </c>
       <c r="E761" s="5" t="inlineStr">
         <is>
-          <t>Bullying &amp; Harassment</t>
+          <t>Adult Sexual Solicitation &amp; Prostitution</t>
         </is>
       </c>
     </row>
@@ -19686,7 +19692,7 @@
       </c>
       <c r="E768" s="7" t="inlineStr">
         <is>
-          <t>Spam</t>
+          <t>Bullying &amp; Harassment</t>
         </is>
       </c>
     </row>
@@ -19761,7 +19767,7 @@
       </c>
       <c r="E771" s="5" t="inlineStr">
         <is>
-          <t>Misinformation</t>
+          <t>Spam</t>
         </is>
       </c>
     </row>
@@ -19861,7 +19867,7 @@
       </c>
       <c r="E775" s="5" t="inlineStr">
         <is>
-          <t>Spam</t>
+          <t>Bullying &amp; Harassment</t>
         </is>
       </c>
     </row>
@@ -20086,7 +20092,7 @@
       </c>
       <c r="E784" s="7" t="inlineStr">
         <is>
-          <t>Misinformation</t>
+          <t>Spam</t>
         </is>
       </c>
     </row>
@@ -20236,7 +20242,7 @@
       </c>
       <c r="E790" s="7" t="inlineStr">
         <is>
-          <t>Bullying &amp; Harassment</t>
+          <t>Adult Sexual Solicitation &amp; Prostitution</t>
         </is>
       </c>
     </row>
@@ -20286,7 +20292,7 @@
       </c>
       <c r="E792" s="7" t="inlineStr">
         <is>
-          <t>Spam</t>
+          <t>Bullying &amp; Harassment</t>
         </is>
       </c>
     </row>
@@ -20336,7 +20342,7 @@
       </c>
       <c r="E794" s="7" t="inlineStr">
         <is>
-          <t>Bullying &amp; Harassment</t>
+          <t>Adult Sexual Solicitation &amp; Prostitution</t>
         </is>
       </c>
     </row>
@@ -20386,7 +20392,7 @@
       </c>
       <c r="E796" s="7" t="inlineStr">
         <is>
-          <t>Misinformation</t>
+          <t>Spam</t>
         </is>
       </c>
     </row>
@@ -20536,7 +20542,7 @@
       </c>
       <c r="E802" s="7" t="inlineStr">
         <is>
-          <t>Spam</t>
+          <t>Bullying &amp; Harassment</t>
         </is>
       </c>
     </row>
@@ -20586,7 +20592,7 @@
       </c>
       <c r="E804" s="7" t="inlineStr">
         <is>
-          <t>Misinformation</t>
+          <t>Spam</t>
         </is>
       </c>
     </row>
@@ -20636,7 +20642,7 @@
       </c>
       <c r="E806" s="7" t="inlineStr">
         <is>
-          <t>Misinformation</t>
+          <t>Spam</t>
         </is>
       </c>
     </row>
@@ -20661,7 +20667,7 @@
       </c>
       <c r="E807" s="5" t="inlineStr">
         <is>
-          <t>Bullying &amp; Harassment</t>
+          <t>Adult Sexual Solicitation &amp; Prostitution</t>
         </is>
       </c>
     </row>
@@ -20811,7 +20817,7 @@
       </c>
       <c r="E813" s="5" t="inlineStr">
         <is>
-          <t>Spam</t>
+          <t>Bullying &amp; Harassment</t>
         </is>
       </c>
     </row>
@@ -20911,7 +20917,7 @@
       </c>
       <c r="E817" s="5" t="inlineStr">
         <is>
-          <t>Spam</t>
+          <t>Bullying &amp; Harassment</t>
         </is>
       </c>
     </row>
@@ -20961,7 +20967,7 @@
       </c>
       <c r="E819" s="5" t="inlineStr">
         <is>
-          <t>Spam</t>
+          <t>Bullying &amp; Harassment</t>
         </is>
       </c>
     </row>
@@ -20986,7 +20992,7 @@
       </c>
       <c r="E820" s="7" t="inlineStr">
         <is>
-          <t>Misinformation</t>
+          <t>Spam</t>
         </is>
       </c>
     </row>
@@ -21061,7 +21067,7 @@
       </c>
       <c r="E823" s="5" t="inlineStr">
         <is>
-          <t>Spam</t>
+          <t>Bullying &amp; Harassment</t>
         </is>
       </c>
     </row>
@@ -21236,7 +21242,7 @@
       </c>
       <c r="E830" s="7" t="inlineStr">
         <is>
-          <t>Bullying &amp; Harassment</t>
+          <t>Adult Sexual Solicitation &amp; Prostitution</t>
         </is>
       </c>
     </row>
@@ -21286,7 +21292,7 @@
       </c>
       <c r="E832" s="7" t="inlineStr">
         <is>
-          <t>Misinformation</t>
+          <t>Spam</t>
         </is>
       </c>
     </row>
@@ -21411,7 +21417,7 @@
       </c>
       <c r="E837" s="5" t="inlineStr">
         <is>
-          <t>Bullying &amp; Harassment</t>
+          <t>Adult Sexual Solicitation &amp; Prostitution</t>
         </is>
       </c>
     </row>
@@ -21461,7 +21467,7 @@
       </c>
       <c r="E839" s="5" t="inlineStr">
         <is>
-          <t>Bullying &amp; Harassment</t>
+          <t>Adult Sexual Solicitation &amp; Prostitution</t>
         </is>
       </c>
     </row>
@@ -21486,7 +21492,7 @@
       </c>
       <c r="E840" s="7" t="inlineStr">
         <is>
-          <t>Spam</t>
+          <t>Bullying &amp; Harassment</t>
         </is>
       </c>
     </row>
@@ -21561,7 +21567,7 @@
       </c>
       <c r="E843" s="5" t="inlineStr">
         <is>
-          <t>Misinformation</t>
+          <t>Spam</t>
         </is>
       </c>
     </row>
@@ -21661,7 +21667,7 @@
       </c>
       <c r="E847" s="5" t="inlineStr">
         <is>
-          <t>Misinformation</t>
+          <t>Spam</t>
         </is>
       </c>
     </row>
@@ -21736,7 +21742,7 @@
       </c>
       <c r="E850" s="7" t="inlineStr">
         <is>
-          <t>Bullying &amp; Harassment</t>
+          <t>Adult Sexual Solicitation &amp; Prostitution</t>
         </is>
       </c>
     </row>
@@ -21761,7 +21767,7 @@
       </c>
       <c r="E851" s="5" t="inlineStr">
         <is>
-          <t>Spam</t>
+          <t>Bullying &amp; Harassment</t>
         </is>
       </c>
     </row>
@@ -21961,7 +21967,7 @@
       </c>
       <c r="E859" s="5" t="inlineStr">
         <is>
-          <t>Misinformation</t>
+          <t>Spam</t>
         </is>
       </c>
     </row>
@@ -22011,7 +22017,7 @@
       </c>
       <c r="E861" s="5" t="inlineStr">
         <is>
-          <t>Misinformation</t>
+          <t>Spam</t>
         </is>
       </c>
     </row>
@@ -22086,7 +22092,7 @@
       </c>
       <c r="E864" s="7" t="inlineStr">
         <is>
-          <t>Spam</t>
+          <t>Bullying &amp; Harassment</t>
         </is>
       </c>
     </row>
@@ -22186,7 +22192,7 @@
       </c>
       <c r="E868" s="7" t="inlineStr">
         <is>
-          <t>Bullying &amp; Harassment</t>
+          <t>Adult Sexual Solicitation &amp; Prostitution</t>
         </is>
       </c>
     </row>
@@ -22286,7 +22292,7 @@
       </c>
       <c r="E872" s="7" t="inlineStr">
         <is>
-          <t>Bullying &amp; Harassment</t>
+          <t>Adult Sexual Solicitation &amp; Prostitution</t>
         </is>
       </c>
     </row>
@@ -22336,7 +22342,7 @@
       </c>
       <c r="E874" s="7" t="inlineStr">
         <is>
-          <t>Bullying &amp; Harassment</t>
+          <t>Adult Sexual Solicitation &amp; Prostitution</t>
         </is>
       </c>
     </row>
@@ -22361,7 +22367,7 @@
       </c>
       <c r="E875" s="5" t="inlineStr">
         <is>
-          <t>Spam</t>
+          <t>Bullying &amp; Harassment</t>
         </is>
       </c>
     </row>
@@ -22411,7 +22417,7 @@
       </c>
       <c r="E877" s="5" t="inlineStr">
         <is>
-          <t>Misinformation</t>
+          <t>Spam</t>
         </is>
       </c>
     </row>
@@ -22536,7 +22542,7 @@
       </c>
       <c r="E882" s="7" t="inlineStr">
         <is>
-          <t>Spam</t>
+          <t>Bullying &amp; Harassment</t>
         </is>
       </c>
     </row>
@@ -22561,7 +22567,7 @@
       </c>
       <c r="E883" s="5" t="inlineStr">
         <is>
-          <t>Misinformation</t>
+          <t>Spam</t>
         </is>
       </c>
     </row>
@@ -22661,7 +22667,7 @@
       </c>
       <c r="E887" s="5" t="inlineStr">
         <is>
-          <t>Spam</t>
+          <t>Bullying &amp; Harassment</t>
         </is>
       </c>
     </row>
@@ -22686,7 +22692,7 @@
       </c>
       <c r="E888" s="7" t="inlineStr">
         <is>
-          <t>Misinformation</t>
+          <t>Spam</t>
         </is>
       </c>
     </row>
@@ -22711,7 +22717,7 @@
       </c>
       <c r="E889" s="5" t="inlineStr">
         <is>
-          <t>Misinformation</t>
+          <t>Spam</t>
         </is>
       </c>
     </row>
@@ -22736,7 +22742,7 @@
       </c>
       <c r="E890" s="7" t="inlineStr">
         <is>
-          <t>Misinformation</t>
+          <t>Spam</t>
         </is>
       </c>
     </row>
@@ -22861,7 +22867,7 @@
       </c>
       <c r="E895" s="5" t="inlineStr">
         <is>
-          <t>Spam</t>
+          <t>Bullying &amp; Harassment</t>
         </is>
       </c>
     </row>
@@ -22886,7 +22892,7 @@
       </c>
       <c r="E896" s="7" t="inlineStr">
         <is>
-          <t>Misinformation</t>
+          <t>Spam</t>
         </is>
       </c>
     </row>
@@ -22936,7 +22942,7 @@
       </c>
       <c r="E898" s="7" t="inlineStr">
         <is>
-          <t>Misinformation</t>
+          <t>Spam</t>
         </is>
       </c>
     </row>
@@ -22961,7 +22967,7 @@
       </c>
       <c r="E899" s="5" t="inlineStr">
         <is>
-          <t>Misinformation</t>
+          <t>Spam</t>
         </is>
       </c>
     </row>
@@ -23011,7 +23017,7 @@
       </c>
       <c r="E901" s="5" t="inlineStr">
         <is>
-          <t>Bullying &amp; Harassment</t>
+          <t>Adult Sexual Solicitation &amp; Prostitution</t>
         </is>
       </c>
     </row>
@@ -23036,7 +23042,7 @@
       </c>
       <c r="E902" s="7" t="inlineStr">
         <is>
-          <t>Spam</t>
+          <t>Bullying &amp; Harassment</t>
         </is>
       </c>
     </row>
@@ -23061,7 +23067,7 @@
       </c>
       <c r="E903" s="5" t="inlineStr">
         <is>
-          <t>Spam</t>
+          <t>Bullying &amp; Harassment</t>
         </is>
       </c>
     </row>
@@ -23161,7 +23167,7 @@
       </c>
       <c r="E907" s="5" t="inlineStr">
         <is>
-          <t>Spam</t>
+          <t>Bullying &amp; Harassment</t>
         </is>
       </c>
     </row>
@@ -23236,7 +23242,7 @@
       </c>
       <c r="E910" s="7" t="inlineStr">
         <is>
-          <t>Bullying &amp; Harassment</t>
+          <t>Adult Sexual Solicitation &amp; Prostitution</t>
         </is>
       </c>
     </row>
@@ -23461,7 +23467,7 @@
       </c>
       <c r="E919" s="5" t="inlineStr">
         <is>
-          <t>Spam</t>
+          <t>Bullying &amp; Harassment</t>
         </is>
       </c>
     </row>
@@ -23536,7 +23542,7 @@
       </c>
       <c r="E922" s="7" t="inlineStr">
         <is>
-          <t>Bullying &amp; Harassment</t>
+          <t>Adult Sexual Solicitation &amp; Prostitution</t>
         </is>
       </c>
     </row>
@@ -23561,7 +23567,7 @@
       </c>
       <c r="E923" s="5" t="inlineStr">
         <is>
-          <t>Bullying &amp; Harassment</t>
+          <t>Adult Sexual Solicitation &amp; Prostitution</t>
         </is>
       </c>
     </row>
@@ -23636,7 +23642,7 @@
       </c>
       <c r="E926" s="7" t="inlineStr">
         <is>
-          <t>Bullying &amp; Harassment</t>
+          <t>Adult Sexual Solicitation &amp; Prostitution</t>
         </is>
       </c>
     </row>
@@ -23711,7 +23717,7 @@
       </c>
       <c r="E929" s="5" t="inlineStr">
         <is>
-          <t>Bullying &amp; Harassment</t>
+          <t>Adult Sexual Solicitation &amp; Prostitution</t>
         </is>
       </c>
     </row>
@@ -23786,7 +23792,7 @@
       </c>
       <c r="E932" s="7" t="inlineStr">
         <is>
-          <t>Misinformation</t>
+          <t>Spam</t>
         </is>
       </c>
     </row>
@@ -24161,7 +24167,7 @@
       </c>
       <c r="E947" s="5" t="inlineStr">
         <is>
-          <t>Spam</t>
+          <t>Bullying &amp; Harassment</t>
         </is>
       </c>
     </row>
@@ -24186,7 +24192,7 @@
       </c>
       <c r="E948" s="7" t="inlineStr">
         <is>
-          <t>Bullying &amp; Harassment</t>
+          <t>Adult Sexual Solicitation &amp; Prostitution</t>
         </is>
       </c>
     </row>
@@ -24211,7 +24217,7 @@
       </c>
       <c r="E949" s="5" t="inlineStr">
         <is>
-          <t>Misinformation</t>
+          <t>Spam</t>
         </is>
       </c>
     </row>
@@ -24236,7 +24242,7 @@
       </c>
       <c r="E950" s="7" t="inlineStr">
         <is>
-          <t>Spam</t>
+          <t>Bullying &amp; Harassment</t>
         </is>
       </c>
     </row>
@@ -24286,7 +24292,7 @@
       </c>
       <c r="E952" s="7" t="inlineStr">
         <is>
-          <t>Spam</t>
+          <t>Bullying &amp; Harassment</t>
         </is>
       </c>
     </row>
@@ -24311,7 +24317,7 @@
       </c>
       <c r="E953" s="5" t="inlineStr">
         <is>
-          <t>Spam</t>
+          <t>Bullying &amp; Harassment</t>
         </is>
       </c>
     </row>
@@ -24361,7 +24367,7 @@
       </c>
       <c r="E955" s="5" t="inlineStr">
         <is>
-          <t>Misinformation</t>
+          <t>Spam</t>
         </is>
       </c>
     </row>
@@ -24386,7 +24392,7 @@
       </c>
       <c r="E956" s="7" t="inlineStr">
         <is>
-          <t>Bullying &amp; Harassment</t>
+          <t>Adult Sexual Solicitation &amp; Prostitution</t>
         </is>
       </c>
     </row>
@@ -24511,7 +24517,7 @@
       </c>
       <c r="E961" s="5" t="inlineStr">
         <is>
-          <t>Spam</t>
+          <t>Bullying &amp; Harassment</t>
         </is>
       </c>
     </row>
@@ -24536,7 +24542,7 @@
       </c>
       <c r="E962" s="7" t="inlineStr">
         <is>
-          <t>Misinformation</t>
+          <t>Spam</t>
         </is>
       </c>
     </row>
@@ -24636,7 +24642,7 @@
       </c>
       <c r="E966" s="7" t="inlineStr">
         <is>
-          <t>Spam</t>
+          <t>Bullying &amp; Harassment</t>
         </is>
       </c>
     </row>
@@ -24711,7 +24717,7 @@
       </c>
       <c r="E969" s="5" t="inlineStr">
         <is>
-          <t>Misinformation</t>
+          <t>Spam</t>
         </is>
       </c>
     </row>
@@ -24736,7 +24742,7 @@
       </c>
       <c r="E970" s="7" t="inlineStr">
         <is>
-          <t>Spam</t>
+          <t>Bullying &amp; Harassment</t>
         </is>
       </c>
     </row>
@@ -24761,7 +24767,7 @@
       </c>
       <c r="E971" s="5" t="inlineStr">
         <is>
-          <t>Bullying &amp; Harassment</t>
+          <t>Adult Sexual Solicitation &amp; Prostitution</t>
         </is>
       </c>
     </row>
@@ -24886,7 +24892,7 @@
       </c>
       <c r="E976" s="7" t="inlineStr">
         <is>
-          <t>Bullying &amp; Harassment</t>
+          <t>Adult Sexual Solicitation &amp; Prostitution</t>
         </is>
       </c>
     </row>
@@ -24986,7 +24992,7 @@
       </c>
       <c r="E980" s="7" t="inlineStr">
         <is>
-          <t>Spam</t>
+          <t>Bullying &amp; Harassment</t>
         </is>
       </c>
     </row>
@@ -25186,7 +25192,7 @@
       </c>
       <c r="E988" s="7" t="inlineStr">
         <is>
-          <t>Misinformation</t>
+          <t>Spam</t>
         </is>
       </c>
     </row>
@@ -25311,7 +25317,7 @@
       </c>
       <c r="E993" s="5" t="inlineStr">
         <is>
-          <t>Bullying &amp; Harassment</t>
+          <t>Adult Sexual Solicitation &amp; Prostitution</t>
         </is>
       </c>
     </row>
@@ -25436,7 +25442,7 @@
       </c>
       <c r="E998" s="7" t="inlineStr">
         <is>
-          <t>Bullying &amp; Harassment</t>
+          <t>Adult Sexual Solicitation &amp; Prostitution</t>
         </is>
       </c>
     </row>
@@ -25461,7 +25467,7 @@
       </c>
       <c r="E999" s="5" t="inlineStr">
         <is>
-          <t>Misinformation</t>
+          <t>Spam</t>
         </is>
       </c>
     </row>
@@ -25561,7 +25567,7 @@
       </c>
       <c r="E1003" s="5" t="inlineStr">
         <is>
-          <t>Bullying &amp; Harassment</t>
+          <t>Adult Sexual Solicitation &amp; Prostitution</t>
         </is>
       </c>
     </row>
@@ -25611,7 +25617,7 @@
       </c>
       <c r="E1005" s="5" t="inlineStr">
         <is>
-          <t>Spam</t>
+          <t>Bullying &amp; Harassment</t>
         </is>
       </c>
     </row>
@@ -25811,7 +25817,7 @@
       </c>
       <c r="E1013" s="5" t="inlineStr">
         <is>
-          <t>Misinformation</t>
+          <t>Spam</t>
         </is>
       </c>
     </row>
@@ -25886,7 +25892,7 @@
       </c>
       <c r="E1016" s="7" t="inlineStr">
         <is>
-          <t>Spam</t>
+          <t>Bullying &amp; Harassment</t>
         </is>
       </c>
     </row>
@@ -26061,7 +26067,7 @@
       </c>
       <c r="E1023" s="5" t="inlineStr">
         <is>
-          <t>Spam</t>
+          <t>Bullying &amp; Harassment</t>
         </is>
       </c>
     </row>
@@ -26111,7 +26117,7 @@
       </c>
       <c r="E1025" s="5" t="inlineStr">
         <is>
-          <t>Spam</t>
+          <t>Bullying &amp; Harassment</t>
         </is>
       </c>
     </row>
@@ -26286,7 +26292,7 @@
       </c>
       <c r="E1032" s="7" t="inlineStr">
         <is>
-          <t>Bullying &amp; Harassment</t>
+          <t>Adult Sexual Solicitation &amp; Prostitution</t>
         </is>
       </c>
     </row>
@@ -26361,7 +26367,7 @@
       </c>
       <c r="E1035" s="5" t="inlineStr">
         <is>
-          <t>Misinformation</t>
+          <t>Spam</t>
         </is>
       </c>
     </row>
@@ -26386,7 +26392,7 @@
       </c>
       <c r="E1036" s="7" t="inlineStr">
         <is>
-          <t>Bullying &amp; Harassment</t>
+          <t>Adult Sexual Solicitation &amp; Prostitution</t>
         </is>
       </c>
     </row>
@@ -26411,7 +26417,7 @@
       </c>
       <c r="E1037" s="5" t="inlineStr">
         <is>
-          <t>Bullying &amp; Harassment</t>
+          <t>Adult Sexual Solicitation &amp; Prostitution</t>
         </is>
       </c>
     </row>
@@ -26461,7 +26467,7 @@
       </c>
       <c r="E1039" s="5" t="inlineStr">
         <is>
-          <t>Misinformation</t>
+          <t>Spam</t>
         </is>
       </c>
     </row>
@@ -26661,7 +26667,7 @@
       </c>
       <c r="E1047" s="5" t="inlineStr">
         <is>
-          <t>Misinformation</t>
+          <t>Spam</t>
         </is>
       </c>
     </row>
@@ -26736,7 +26742,7 @@
       </c>
       <c r="E1050" s="7" t="inlineStr">
         <is>
-          <t>Misinformation</t>
+          <t>Spam</t>
         </is>
       </c>
     </row>
@@ -26786,7 +26792,7 @@
       </c>
       <c r="E1052" s="7" t="inlineStr">
         <is>
-          <t>Spam</t>
+          <t>Bullying &amp; Harassment</t>
         </is>
       </c>
     </row>
@@ -26936,7 +26942,7 @@
       </c>
       <c r="E1058" s="7" t="inlineStr">
         <is>
-          <t>Misinformation</t>
+          <t>Spam</t>
         </is>
       </c>
     </row>
@@ -26961,7 +26967,7 @@
       </c>
       <c r="E1059" s="5" t="inlineStr">
         <is>
-          <t>Bullying &amp; Harassment</t>
+          <t>Adult Sexual Solicitation &amp; Prostitution</t>
         </is>
       </c>
     </row>
@@ -27111,7 +27117,7 @@
       </c>
       <c r="E1065" s="5" t="inlineStr">
         <is>
-          <t>Spam</t>
+          <t>Bullying &amp; Harassment</t>
         </is>
       </c>
     </row>
@@ -27336,7 +27342,7 @@
       </c>
       <c r="E1074" s="7" t="inlineStr">
         <is>
-          <t>Bullying &amp; Harassment</t>
+          <t>Adult Sexual Solicitation &amp; Prostitution</t>
         </is>
       </c>
     </row>
@@ -27436,7 +27442,7 @@
       </c>
       <c r="E1078" s="7" t="inlineStr">
         <is>
-          <t>Bullying &amp; Harassment</t>
+          <t>Adult Sexual Solicitation &amp; Prostitution</t>
         </is>
       </c>
     </row>
@@ -27461,7 +27467,7 @@
       </c>
       <c r="E1079" s="5" t="inlineStr">
         <is>
-          <t>Misinformation</t>
+          <t>Spam</t>
         </is>
       </c>
     </row>
@@ -27511,7 +27517,7 @@
       </c>
       <c r="E1081" s="5" t="inlineStr">
         <is>
-          <t>Bullying &amp; Harassment</t>
+          <t>Adult Sexual Solicitation &amp; Prostitution</t>
         </is>
       </c>
     </row>
@@ -27561,7 +27567,7 @@
       </c>
       <c r="E1083" s="5" t="inlineStr">
         <is>
-          <t>Spam</t>
+          <t>Bullying &amp; Harassment</t>
         </is>
       </c>
     </row>
@@ -27611,7 +27617,7 @@
       </c>
       <c r="E1085" s="5" t="inlineStr">
         <is>
-          <t>Spam</t>
+          <t>Bullying &amp; Harassment</t>
         </is>
       </c>
     </row>
@@ -27661,7 +27667,7 @@
       </c>
       <c r="E1087" s="5" t="inlineStr">
         <is>
-          <t>Spam</t>
+          <t>Bullying &amp; Harassment</t>
         </is>
       </c>
     </row>
@@ -27686,7 +27692,7 @@
       </c>
       <c r="E1088" s="7" t="inlineStr">
         <is>
-          <t>Misinformation</t>
+          <t>Spam</t>
         </is>
       </c>
     </row>
@@ -27736,7 +27742,7 @@
       </c>
       <c r="E1090" s="7" t="inlineStr">
         <is>
-          <t>Misinformation</t>
+          <t>Spam</t>
         </is>
       </c>
     </row>
@@ -27861,7 +27867,7 @@
       </c>
       <c r="E1095" s="5" t="inlineStr">
         <is>
-          <t>Misinformation</t>
+          <t>Spam</t>
         </is>
       </c>
     </row>
@@ -27886,7 +27892,7 @@
       </c>
       <c r="E1096" s="7" t="inlineStr">
         <is>
-          <t>Misinformation</t>
+          <t>Spam</t>
         </is>
       </c>
     </row>
@@ -27936,7 +27942,7 @@
       </c>
       <c r="E1098" s="7" t="inlineStr">
         <is>
-          <t>Bullying &amp; Harassment</t>
+          <t>Adult Sexual Solicitation &amp; Prostitution</t>
         </is>
       </c>
     </row>
@@ -27986,7 +27992,7 @@
       </c>
       <c r="E1100" s="7" t="inlineStr">
         <is>
-          <t>Spam</t>
+          <t>Bullying &amp; Harassment</t>
         </is>
       </c>
     </row>
@@ -28011,7 +28017,7 @@
       </c>
       <c r="E1101" s="5" t="inlineStr">
         <is>
-          <t>Bullying &amp; Harassment</t>
+          <t>Adult Sexual Solicitation &amp; Prostitution</t>
         </is>
       </c>
     </row>
@@ -28061,7 +28067,7 @@
       </c>
       <c r="E1103" s="5" t="inlineStr">
         <is>
-          <t>Misinformation</t>
+          <t>Spam</t>
         </is>
       </c>
     </row>
@@ -28136,7 +28142,7 @@
       </c>
       <c r="E1106" s="7" t="inlineStr">
         <is>
-          <t>Spam</t>
+          <t>Bullying &amp; Harassment</t>
         </is>
       </c>
     </row>
@@ -28161,7 +28167,7 @@
       </c>
       <c r="E1107" s="5" t="inlineStr">
         <is>
-          <t>Misinformation</t>
+          <t>Spam</t>
         </is>
       </c>
     </row>
@@ -28211,7 +28217,7 @@
       </c>
       <c r="E1109" s="5" t="inlineStr">
         <is>
-          <t>Misinformation</t>
+          <t>Spam</t>
         </is>
       </c>
     </row>
@@ -28411,7 +28417,7 @@
       </c>
       <c r="E1117" s="5" t="inlineStr">
         <is>
-          <t>Spam</t>
+          <t>Bullying &amp; Harassment</t>
         </is>
       </c>
     </row>
@@ -28436,7 +28442,7 @@
       </c>
       <c r="E1118" s="7" t="inlineStr">
         <is>
-          <t>Misinformation</t>
+          <t>Spam</t>
         </is>
       </c>
     </row>
@@ -28536,7 +28542,7 @@
       </c>
       <c r="E1122" s="7" t="inlineStr">
         <is>
-          <t>Spam</t>
+          <t>Bullying &amp; Harassment</t>
         </is>
       </c>
     </row>
@@ -28611,7 +28617,7 @@
       </c>
       <c r="E1125" s="5" t="inlineStr">
         <is>
-          <t>Spam</t>
+          <t>Bullying &amp; Harassment</t>
         </is>
       </c>
     </row>
@@ -28636,7 +28642,7 @@
       </c>
       <c r="E1126" s="7" t="inlineStr">
         <is>
-          <t>Spam</t>
+          <t>Bullying &amp; Harassment</t>
         </is>
       </c>
     </row>
@@ -28661,7 +28667,7 @@
       </c>
       <c r="E1127" s="5" t="inlineStr">
         <is>
-          <t>Bullying &amp; Harassment</t>
+          <t>Adult Sexual Solicitation &amp; Prostitution</t>
         </is>
       </c>
     </row>
@@ -28786,7 +28792,7 @@
       </c>
       <c r="E1132" s="7" t="inlineStr">
         <is>
-          <t>Bullying &amp; Harassment</t>
+          <t>Adult Sexual Solicitation &amp; Prostitution</t>
         </is>
       </c>
     </row>
@@ -28811,7 +28817,7 @@
       </c>
       <c r="E1133" s="5" t="inlineStr">
         <is>
-          <t>Bullying &amp; Harassment</t>
+          <t>Adult Sexual Solicitation &amp; Prostitution</t>
         </is>
       </c>
     </row>
@@ -29011,7 +29017,7 @@
       </c>
       <c r="E1141" s="5" t="inlineStr">
         <is>
-          <t>Spam</t>
+          <t>Bullying &amp; Harassment</t>
         </is>
       </c>
     </row>
@@ -29036,7 +29042,7 @@
       </c>
       <c r="E1142" s="7" t="inlineStr">
         <is>
-          <t>Spam</t>
+          <t>Bullying &amp; Harassment</t>
         </is>
       </c>
     </row>
@@ -29111,7 +29117,7 @@
       </c>
       <c r="E1145" s="5" t="inlineStr">
         <is>
-          <t>Bullying &amp; Harassment</t>
+          <t>Adult Sexual Solicitation &amp; Prostitution</t>
         </is>
       </c>
     </row>
@@ -29161,7 +29167,7 @@
       </c>
       <c r="E1147" s="5" t="inlineStr">
         <is>
-          <t>Spam</t>
+          <t>Bullying &amp; Harassment</t>
         </is>
       </c>
     </row>
@@ -29286,7 +29292,7 @@
       </c>
       <c r="E1152" s="7" t="inlineStr">
         <is>
-          <t>Spam</t>
+          <t>Bullying &amp; Harassment</t>
         </is>
       </c>
     </row>
@@ -29436,7 +29442,7 @@
       </c>
       <c r="E1158" s="7" t="inlineStr">
         <is>
-          <t>Bullying &amp; Harassment</t>
+          <t>Adult Sexual Solicitation &amp; Prostitution</t>
         </is>
       </c>
     </row>
@@ -29486,7 +29492,7 @@
       </c>
       <c r="E1160" s="7" t="inlineStr">
         <is>
-          <t>Misinformation</t>
+          <t>Spam</t>
         </is>
       </c>
     </row>
@@ -29511,7 +29517,7 @@
       </c>
       <c r="E1161" s="5" t="inlineStr">
         <is>
-          <t>Misinformation</t>
+          <t>Spam</t>
         </is>
       </c>
     </row>
@@ -29861,7 +29867,7 @@
       </c>
       <c r="E1175" s="5" t="inlineStr">
         <is>
-          <t>Spam</t>
+          <t>Bullying &amp; Harassment</t>
         </is>
       </c>
     </row>
@@ -29936,7 +29942,7 @@
       </c>
       <c r="E1178" s="7" t="inlineStr">
         <is>
-          <t>Bullying &amp; Harassment</t>
+          <t>Adult Sexual Solicitation &amp; Prostitution</t>
         </is>
       </c>
     </row>
@@ -30061,7 +30067,7 @@
       </c>
       <c r="E1183" s="5" t="inlineStr">
         <is>
-          <t>Bullying &amp; Harassment</t>
+          <t>Adult Sexual Solicitation &amp; Prostitution</t>
         </is>
       </c>
     </row>
@@ -30486,7 +30492,7 @@
       </c>
       <c r="E1200" s="7" t="inlineStr">
         <is>
-          <t>Bullying &amp; Harassment</t>
+          <t>Adult Sexual Solicitation &amp; Prostitution</t>
         </is>
       </c>
     </row>
@@ -30536,7 +30542,7 @@
       </c>
       <c r="E1202" s="7" t="inlineStr">
         <is>
-          <t>Misinformation</t>
+          <t>Spam</t>
         </is>
       </c>
     </row>
@@ -30661,7 +30667,7 @@
       </c>
       <c r="E1207" s="5" t="inlineStr">
         <is>
-          <t>Spam</t>
+          <t>Bullying &amp; Harassment</t>
         </is>
       </c>
     </row>
@@ -30711,7 +30717,7 @@
       </c>
       <c r="E1209" s="5" t="inlineStr">
         <is>
-          <t>Spam</t>
+          <t>Bullying &amp; Harassment</t>
         </is>
       </c>
     </row>
@@ -30736,7 +30742,7 @@
       </c>
       <c r="E1210" s="7" t="inlineStr">
         <is>
-          <t>Spam</t>
+          <t>Bullying &amp; Harassment</t>
         </is>
       </c>
     </row>
@@ -30786,7 +30792,7 @@
       </c>
       <c r="E1212" s="7" t="inlineStr">
         <is>
-          <t>Spam</t>
+          <t>Bullying &amp; Harassment</t>
         </is>
       </c>
     </row>
@@ -30836,7 +30842,7 @@
       </c>
       <c r="E1214" s="7" t="inlineStr">
         <is>
-          <t>Spam</t>
+          <t>Bullying &amp; Harassment</t>
         </is>
       </c>
     </row>
@@ -30886,7 +30892,7 @@
       </c>
       <c r="E1216" s="7" t="inlineStr">
         <is>
-          <t>Bullying &amp; Harassment</t>
+          <t>Adult Sexual Solicitation &amp; Prostitution</t>
         </is>
       </c>
     </row>
@@ -30961,7 +30967,7 @@
       </c>
       <c r="E1219" s="5" t="inlineStr">
         <is>
-          <t>Bullying &amp; Harassment</t>
+          <t>Adult Sexual Solicitation &amp; Prostitution</t>
         </is>
       </c>
     </row>
@@ -31061,7 +31067,7 @@
       </c>
       <c r="E1223" s="5" t="inlineStr">
         <is>
-          <t>Spam</t>
+          <t>Bullying &amp; Harassment</t>
         </is>
       </c>
     </row>
@@ -31111,7 +31117,7 @@
       </c>
       <c r="E1225" s="5" t="inlineStr">
         <is>
-          <t>Spam</t>
+          <t>Bullying &amp; Harassment</t>
         </is>
       </c>
     </row>
@@ -31211,7 +31217,7 @@
       </c>
       <c r="E1229" s="5" t="inlineStr">
         <is>
-          <t>Bullying &amp; Harassment</t>
+          <t>Adult Sexual Solicitation &amp; Prostitution</t>
         </is>
       </c>
     </row>
@@ -31261,7 +31267,7 @@
       </c>
       <c r="E1231" s="5" t="inlineStr">
         <is>
-          <t>Misinformation</t>
+          <t>Spam</t>
         </is>
       </c>
     </row>
@@ -31361,7 +31367,7 @@
       </c>
       <c r="E1235" s="5" t="inlineStr">
         <is>
-          <t>Bullying &amp; Harassment</t>
+          <t>Adult Sexual Solicitation &amp; Prostitution</t>
         </is>
       </c>
     </row>
@@ -31511,7 +31517,7 @@
       </c>
       <c r="E1241" s="5" t="inlineStr">
         <is>
-          <t>Bullying &amp; Harassment</t>
+          <t>Adult Sexual Solicitation &amp; Prostitution</t>
         </is>
       </c>
     </row>
@@ -31536,7 +31542,7 @@
       </c>
       <c r="E1242" s="7" t="inlineStr">
         <is>
-          <t>Spam</t>
+          <t>Bullying &amp; Harassment</t>
         </is>
       </c>
     </row>
@@ -31561,7 +31567,7 @@
       </c>
       <c r="E1243" s="5" t="inlineStr">
         <is>
-          <t>Misinformation</t>
+          <t>Spam</t>
         </is>
       </c>
     </row>
@@ -31661,7 +31667,7 @@
       </c>
       <c r="E1247" s="5" t="inlineStr">
         <is>
-          <t>Spam</t>
+          <t>Bullying &amp; Harassment</t>
         </is>
       </c>
     </row>
@@ -31686,7 +31692,7 @@
       </c>
       <c r="E1248" s="7" t="inlineStr">
         <is>
-          <t>Bullying &amp; Harassment</t>
+          <t>Adult Sexual Solicitation &amp; Prostitution</t>
         </is>
       </c>
     </row>
@@ -31711,7 +31717,7 @@
       </c>
       <c r="E1249" s="5" t="inlineStr">
         <is>
-          <t>Misinformation</t>
+          <t>Spam</t>
         </is>
       </c>
     </row>
@@ -31861,7 +31867,7 @@
       </c>
       <c r="E1255" s="5" t="inlineStr">
         <is>
-          <t>Misinformation</t>
+          <t>Spam</t>
         </is>
       </c>
     </row>
@@ -31886,7 +31892,7 @@
       </c>
       <c r="E1256" s="7" t="inlineStr">
         <is>
-          <t>Spam</t>
+          <t>Bullying &amp; Harassment</t>
         </is>
       </c>
     </row>
@@ -31911,7 +31917,7 @@
       </c>
       <c r="E1257" s="5" t="inlineStr">
         <is>
-          <t>Spam</t>
+          <t>Bullying &amp; Harassment</t>
         </is>
       </c>
     </row>
@@ -32061,7 +32067,7 @@
       </c>
       <c r="E1263" s="5" t="inlineStr">
         <is>
-          <t>Spam</t>
+          <t>Bullying &amp; Harassment</t>
         </is>
       </c>
     </row>
@@ -32186,7 +32192,7 @@
       </c>
       <c r="E1268" s="7" t="inlineStr">
         <is>
-          <t>Spam</t>
+          <t>Bullying &amp; Harassment</t>
         </is>
       </c>
     </row>
@@ -32286,7 +32292,7 @@
       </c>
       <c r="E1272" s="7" t="inlineStr">
         <is>
-          <t>Bullying &amp; Harassment</t>
+          <t>Adult Sexual Solicitation &amp; Prostitution</t>
         </is>
       </c>
     </row>
@@ -32311,7 +32317,7 @@
       </c>
       <c r="E1273" s="5" t="inlineStr">
         <is>
-          <t>Spam</t>
+          <t>Bullying &amp; Harassment</t>
         </is>
       </c>
     </row>
@@ -32461,7 +32467,7 @@
       </c>
       <c r="E1279" s="5" t="inlineStr">
         <is>
-          <t>Spam</t>
+          <t>Bullying &amp; Harassment</t>
         </is>
       </c>
     </row>
@@ -32736,7 +32742,7 @@
       </c>
       <c r="E1290" s="7" t="inlineStr">
         <is>
-          <t>Misinformation</t>
+          <t>Spam</t>
         </is>
       </c>
     </row>
@@ -32861,7 +32867,7 @@
       </c>
       <c r="E1295" s="5" t="inlineStr">
         <is>
-          <t>Spam</t>
+          <t>Bullying &amp; Harassment</t>
         </is>
       </c>
     </row>
@@ -33061,7 +33067,7 @@
       </c>
       <c r="E1303" s="5" t="inlineStr">
         <is>
-          <t>Spam</t>
+          <t>Bullying &amp; Harassment</t>
         </is>
       </c>
     </row>
@@ -33111,7 +33117,7 @@
       </c>
       <c r="E1305" s="5" t="inlineStr">
         <is>
-          <t>Misinformation</t>
+          <t>Spam</t>
         </is>
       </c>
     </row>
@@ -33211,7 +33217,7 @@
       </c>
       <c r="E1309" s="5" t="inlineStr">
         <is>
-          <t>Bullying &amp; Harassment</t>
+          <t>Adult Sexual Solicitation &amp; Prostitution</t>
         </is>
       </c>
     </row>
@@ -33336,7 +33342,7 @@
       </c>
       <c r="E1314" s="7" t="inlineStr">
         <is>
-          <t>Bullying &amp; Harassment</t>
+          <t>Adult Sexual Solicitation &amp; Prostitution</t>
         </is>
       </c>
     </row>
@@ -33461,7 +33467,7 @@
       </c>
       <c r="E1319" s="5" t="inlineStr">
         <is>
-          <t>Bullying &amp; Harassment</t>
+          <t>Adult Sexual Solicitation &amp; Prostitution</t>
         </is>
       </c>
     </row>
@@ -33536,7 +33542,7 @@
       </c>
       <c r="E1322" s="7" t="inlineStr">
         <is>
-          <t>Misinformation</t>
+          <t>Spam</t>
         </is>
       </c>
     </row>
@@ -33561,7 +33567,7 @@
       </c>
       <c r="E1323" s="5" t="inlineStr">
         <is>
-          <t>Spam</t>
+          <t>Bullying &amp; Harassment</t>
         </is>
       </c>
     </row>
@@ -33686,7 +33692,7 @@
       </c>
       <c r="E1328" s="7" t="inlineStr">
         <is>
-          <t>Bullying &amp; Harassment</t>
+          <t>Adult Sexual Solicitation &amp; Prostitution</t>
         </is>
       </c>
     </row>
@@ -33811,7 +33817,7 @@
       </c>
       <c r="E1333" s="5" t="inlineStr">
         <is>
-          <t>Bullying &amp; Harassment</t>
+          <t>Adult Sexual Solicitation &amp; Prostitution</t>
         </is>
       </c>
     </row>
@@ -33986,7 +33992,7 @@
       </c>
       <c r="E1340" s="7" t="inlineStr">
         <is>
-          <t>Spam</t>
+          <t>Bullying &amp; Harassment</t>
         </is>
       </c>
     </row>
@@ -34161,7 +34167,7 @@
       </c>
       <c r="E1347" s="5" t="inlineStr">
         <is>
-          <t>Bullying &amp; Harassment</t>
+          <t>Adult Sexual Solicitation &amp; Prostitution</t>
         </is>
       </c>
     </row>
@@ -34186,7 +34192,7 @@
       </c>
       <c r="E1348" s="7" t="inlineStr">
         <is>
-          <t>Bullying &amp; Harassment</t>
+          <t>Adult Sexual Solicitation &amp; Prostitution</t>
         </is>
       </c>
     </row>
@@ -34436,7 +34442,7 @@
       </c>
       <c r="E1358" s="7" t="inlineStr">
         <is>
-          <t>Bullying &amp; Harassment</t>
+          <t>Adult Sexual Solicitation &amp; Prostitution</t>
         </is>
       </c>
     </row>
@@ -34486,7 +34492,7 @@
       </c>
       <c r="E1360" s="7" t="inlineStr">
         <is>
-          <t>Bullying &amp; Harassment</t>
+          <t>Adult Sexual Solicitation &amp; Prostitution</t>
         </is>
       </c>
     </row>
@@ -34536,7 +34542,7 @@
       </c>
       <c r="E1362" s="7" t="inlineStr">
         <is>
-          <t>Spam</t>
+          <t>Bullying &amp; Harassment</t>
         </is>
       </c>
     </row>
@@ -34686,7 +34692,7 @@
       </c>
       <c r="E1368" s="7" t="inlineStr">
         <is>
-          <t>Bullying &amp; Harassment</t>
+          <t>Adult Sexual Solicitation &amp; Prostitution</t>
         </is>
       </c>
     </row>
@@ -34786,7 +34792,7 @@
       </c>
       <c r="E1372" s="7" t="inlineStr">
         <is>
-          <t>Bullying &amp; Harassment</t>
+          <t>Adult Sexual Solicitation &amp; Prostitution</t>
         </is>
       </c>
     </row>
@@ -34836,7 +34842,7 @@
       </c>
       <c r="E1374" s="7" t="inlineStr">
         <is>
-          <t>Spam</t>
+          <t>Bullying &amp; Harassment</t>
         </is>
       </c>
     </row>
@@ -34861,7 +34867,7 @@
       </c>
       <c r="E1375" s="5" t="inlineStr">
         <is>
-          <t>Bullying &amp; Harassment</t>
+          <t>Adult Sexual Solicitation &amp; Prostitution</t>
         </is>
       </c>
     </row>
@@ -34936,7 +34942,7 @@
       </c>
       <c r="E1378" s="7" t="inlineStr">
         <is>
-          <t>Misinformation</t>
+          <t>Spam</t>
         </is>
       </c>
     </row>
@@ -34961,7 +34967,7 @@
       </c>
       <c r="E1379" s="5" t="inlineStr">
         <is>
-          <t>Misinformation</t>
+          <t>Spam</t>
         </is>
       </c>
     </row>
@@ -34986,7 +34992,7 @@
       </c>
       <c r="E1380" s="7" t="inlineStr">
         <is>
-          <t>Spam</t>
+          <t>Bullying &amp; Harassment</t>
         </is>
       </c>
     </row>
@@ -35011,7 +35017,7 @@
       </c>
       <c r="E1381" s="5" t="inlineStr">
         <is>
-          <t>Misinformation</t>
+          <t>Spam</t>
         </is>
       </c>
     </row>
@@ -35086,7 +35092,7 @@
       </c>
       <c r="E1384" s="7" t="inlineStr">
         <is>
-          <t>Spam</t>
+          <t>Bullying &amp; Harassment</t>
         </is>
       </c>
     </row>
@@ -35136,7 +35142,7 @@
       </c>
       <c r="E1386" s="7" t="inlineStr">
         <is>
-          <t>Bullying &amp; Harassment</t>
+          <t>Adult Sexual Solicitation &amp; Prostitution</t>
         </is>
       </c>
     </row>
@@ -35186,7 +35192,7 @@
       </c>
       <c r="E1388" s="7" t="inlineStr">
         <is>
-          <t>Bullying &amp; Harassment</t>
+          <t>Adult Sexual Solicitation &amp; Prostitution</t>
         </is>
       </c>
     </row>
@@ -35261,7 +35267,7 @@
       </c>
       <c r="E1391" s="5" t="inlineStr">
         <is>
-          <t>Bullying &amp; Harassment</t>
+          <t>Adult Sexual Solicitation &amp; Prostitution</t>
         </is>
       </c>
     </row>
@@ -35286,7 +35292,7 @@
       </c>
       <c r="E1392" s="7" t="inlineStr">
         <is>
-          <t>Spam</t>
+          <t>Bullying &amp; Harassment</t>
         </is>
       </c>
     </row>
@@ -35361,7 +35367,7 @@
       </c>
       <c r="E1395" s="5" t="inlineStr">
         <is>
-          <t>Bullying &amp; Harassment</t>
+          <t>Adult Sexual Solicitation &amp; Prostitution</t>
         </is>
       </c>
     </row>
@@ -35386,7 +35392,7 @@
       </c>
       <c r="E1396" s="7" t="inlineStr">
         <is>
-          <t>Misinformation</t>
+          <t>Spam</t>
         </is>
       </c>
     </row>
@@ -35436,7 +35442,7 @@
       </c>
       <c r="E1398" s="7" t="inlineStr">
         <is>
-          <t>Bullying &amp; Harassment</t>
+          <t>Adult Sexual Solicitation &amp; Prostitution</t>
         </is>
       </c>
     </row>
@@ -35486,7 +35492,7 @@
       </c>
       <c r="E1400" s="7" t="inlineStr">
         <is>
-          <t>Bullying &amp; Harassment</t>
+          <t>Adult Sexual Solicitation &amp; Prostitution</t>
         </is>
       </c>
     </row>
@@ -35636,7 +35642,7 @@
       </c>
       <c r="E1406" s="7" t="inlineStr">
         <is>
-          <t>Misinformation</t>
+          <t>Spam</t>
         </is>
       </c>
     </row>
@@ -35861,7 +35867,7 @@
       </c>
       <c r="E1415" s="5" t="inlineStr">
         <is>
-          <t>Spam</t>
+          <t>Bullying &amp; Harassment</t>
         </is>
       </c>
     </row>
@@ -36011,7 +36017,7 @@
       </c>
       <c r="E1421" s="5" t="inlineStr">
         <is>
-          <t>Spam</t>
+          <t>Bullying &amp; Harassment</t>
         </is>
       </c>
     </row>
@@ -36236,7 +36242,7 @@
       </c>
       <c r="E1430" s="7" t="inlineStr">
         <is>
-          <t>Misinformation</t>
+          <t>Spam</t>
         </is>
       </c>
     </row>
@@ -36311,7 +36317,7 @@
       </c>
       <c r="E1433" s="5" t="inlineStr">
         <is>
-          <t>Bullying &amp; Harassment</t>
+          <t>Adult Sexual Solicitation &amp; Prostitution</t>
         </is>
       </c>
     </row>
@@ -36361,7 +36367,7 @@
       </c>
       <c r="E1435" s="5" t="inlineStr">
         <is>
-          <t>Bullying &amp; Harassment</t>
+          <t>Adult Sexual Solicitation &amp; Prostitution</t>
         </is>
       </c>
     </row>
@@ -36461,7 +36467,7 @@
       </c>
       <c r="E1439" s="5" t="inlineStr">
         <is>
-          <t>Misinformation</t>
+          <t>Spam</t>
         </is>
       </c>
     </row>
@@ -36586,7 +36592,7 @@
       </c>
       <c r="E1444" s="7" t="inlineStr">
         <is>
-          <t>Bullying &amp; Harassment</t>
+          <t>Adult Sexual Solicitation &amp; Prostitution</t>
         </is>
       </c>
     </row>
@@ -36661,7 +36667,7 @@
       </c>
       <c r="E1447" s="5" t="inlineStr">
         <is>
-          <t>Misinformation</t>
+          <t>Spam</t>
         </is>
       </c>
     </row>
@@ -36686,7 +36692,7 @@
       </c>
       <c r="E1448" s="7" t="inlineStr">
         <is>
-          <t>Misinformation</t>
+          <t>Spam</t>
         </is>
       </c>
     </row>
@@ -36711,7 +36717,7 @@
       </c>
       <c r="E1449" s="5" t="inlineStr">
         <is>
-          <t>Misinformation</t>
+          <t>Spam</t>
         </is>
       </c>
     </row>
@@ -36786,7 +36792,7 @@
       </c>
       <c r="E1452" s="7" t="inlineStr">
         <is>
-          <t>Spam</t>
+          <t>Bullying &amp; Harassment</t>
         </is>
       </c>
     </row>
@@ -36836,7 +36842,7 @@
       </c>
       <c r="E1454" s="7" t="inlineStr">
         <is>
-          <t>Misinformation</t>
+          <t>Spam</t>
         </is>
       </c>
     </row>
@@ -37136,7 +37142,7 @@
       </c>
       <c r="E1466" s="7" t="inlineStr">
         <is>
-          <t>Misinformation</t>
+          <t>Spam</t>
         </is>
       </c>
     </row>
@@ -37557,7 +37563,7 @@
       </c>
       <c r="E6" s="7" t="inlineStr">
         <is>
-          <t>Spam</t>
+          <t>Bullying &amp; Harassment</t>
         </is>
       </c>
     </row>
@@ -37607,7 +37613,7 @@
       </c>
       <c r="E8" s="7" t="inlineStr">
         <is>
-          <t>Bullying &amp; Harassment</t>
+          <t>Adult Sexual Solicitation &amp; Prostitution</t>
         </is>
       </c>
     </row>
@@ -37682,7 +37688,7 @@
       </c>
       <c r="E11" s="5" t="inlineStr">
         <is>
-          <t>Bullying &amp; Harassment</t>
+          <t>Adult Sexual Solicitation &amp; Prostitution</t>
         </is>
       </c>
     </row>
@@ -37882,7 +37888,7 @@
       </c>
       <c r="E19" s="5" t="inlineStr">
         <is>
-          <t>Misinformation</t>
+          <t>Spam</t>
         </is>
       </c>
     </row>
@@ -38032,7 +38038,7 @@
       </c>
       <c r="E25" s="5" t="inlineStr">
         <is>
-          <t>Misinformation</t>
+          <t>Spam</t>
         </is>
       </c>
     </row>
@@ -38082,7 +38088,7 @@
       </c>
       <c r="E27" s="5" t="inlineStr">
         <is>
-          <t>Spam</t>
+          <t>Bullying &amp; Harassment</t>
         </is>
       </c>
     </row>
@@ -38407,7 +38413,7 @@
       </c>
       <c r="E40" s="7" t="inlineStr">
         <is>
-          <t>Misinformation</t>
+          <t>Spam</t>
         </is>
       </c>
     </row>
@@ -38457,7 +38463,7 @@
       </c>
       <c r="E42" s="7" t="inlineStr">
         <is>
-          <t>Spam</t>
+          <t>Bullying &amp; Harassment</t>
         </is>
       </c>
     </row>
@@ -38482,7 +38488,7 @@
       </c>
       <c r="E43" s="5" t="inlineStr">
         <is>
-          <t>Bullying &amp; Harassment</t>
+          <t>Adult Sexual Solicitation &amp; Prostitution</t>
         </is>
       </c>
     </row>
@@ -38582,7 +38588,7 @@
       </c>
       <c r="E47" s="5" t="inlineStr">
         <is>
-          <t>Misinformation</t>
+          <t>Spam</t>
         </is>
       </c>
     </row>
@@ -38633,7 +38639,7 @@
     <col width="30" customWidth="1" min="5" max="5"/>
     <col width="30" customWidth="1" min="6" max="6"/>
     <col width="14" customWidth="1" min="7" max="7"/>
-    <col width="30" customWidth="1" min="8" max="8"/>
+    <col width="42" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -38737,7 +38743,7 @@
         <f>IF(E5=F5,"Match","ERROR")</f>
         <v/>
       </c>
-      <c r="H5" s="5" t="inlineStr"/>
+      <c r="H5" s="13" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="7" t="inlineStr">
@@ -38745,32 +38751,32 @@
           <t>T-100339</t>
         </is>
       </c>
-      <c r="B6" s="13">
+      <c r="B6" s="14">
         <f>IFERROR(VLOOKUP(A6,'Raw Export (Scuba TSV)'!$A$5:$E$1478,2,FALSE),"")</f>
         <v/>
       </c>
-      <c r="C6" s="13">
+      <c r="C6" s="14">
         <f>IFERROR(VLOOKUP(A6,'Raw Export (Scuba TSV)'!$A$5:$E$1478,3,FALSE),"")</f>
         <v/>
       </c>
-      <c r="D6" s="14">
+      <c r="D6" s="15">
         <f>IFERROR(VLOOKUP(A6,'Raw Export (Scuba TSV)'!$A$5:$E$1478,4,FALSE),"")</f>
         <v/>
       </c>
-      <c r="E6" s="13">
+      <c r="E6" s="14">
         <f>IFERROR(VLOOKUP(A6,'Raw Export (Scuba TSV)'!$A$5:$E$1478,5,FALSE),"")</f>
         <v/>
       </c>
-      <c r="F6" s="15" t="inlineStr">
-        <is>
-          <t>Spam</t>
-        </is>
-      </c>
-      <c r="G6" s="16">
+      <c r="F6" s="16" t="inlineStr">
+        <is>
+          <t>Bullying &amp; Harassment</t>
+        </is>
+      </c>
+      <c r="G6" s="17">
         <f>IF(E6=F6,"Match","ERROR")</f>
         <v/>
       </c>
-      <c r="H6" s="7" t="inlineStr"/>
+      <c r="H6" s="18" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="5" t="inlineStr">
@@ -38803,7 +38809,7 @@
         <f>IF(E7=F7,"Match","ERROR")</f>
         <v/>
       </c>
-      <c r="H7" s="5" t="inlineStr"/>
+      <c r="H7" s="13" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="7" t="inlineStr">
@@ -38811,32 +38817,32 @@
           <t>T-100989</t>
         </is>
       </c>
-      <c r="B8" s="13">
+      <c r="B8" s="14">
         <f>IFERROR(VLOOKUP(A8,'Raw Export (Scuba TSV)'!$A$5:$E$1478,2,FALSE),"")</f>
         <v/>
       </c>
-      <c r="C8" s="13">
+      <c r="C8" s="14">
         <f>IFERROR(VLOOKUP(A8,'Raw Export (Scuba TSV)'!$A$5:$E$1478,3,FALSE),"")</f>
         <v/>
       </c>
-      <c r="D8" s="14">
+      <c r="D8" s="15">
         <f>IFERROR(VLOOKUP(A8,'Raw Export (Scuba TSV)'!$A$5:$E$1478,4,FALSE),"")</f>
         <v/>
       </c>
-      <c r="E8" s="13">
+      <c r="E8" s="14">
         <f>IFERROR(VLOOKUP(A8,'Raw Export (Scuba TSV)'!$A$5:$E$1478,5,FALSE),"")</f>
         <v/>
       </c>
-      <c r="F8" s="15" t="inlineStr">
-        <is>
-          <t>Bullying &amp; Harassment</t>
-        </is>
-      </c>
-      <c r="G8" s="16">
+      <c r="F8" s="16" t="inlineStr">
+        <is>
+          <t>Adult Sexual Solicitation &amp; Prostitution</t>
+        </is>
+      </c>
+      <c r="G8" s="17">
         <f>IF(E8=F8,"Match","ERROR")</f>
         <v/>
       </c>
-      <c r="H8" s="7" t="inlineStr"/>
+      <c r="H8" s="18" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="5" t="inlineStr">
@@ -38869,7 +38875,7 @@
         <f>IF(E9=F9,"Match","ERROR")</f>
         <v/>
       </c>
-      <c r="H9" s="5" t="inlineStr"/>
+      <c r="H9" s="13" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="7" t="inlineStr">
@@ -38877,32 +38883,32 @@
           <t>T-101119</t>
         </is>
       </c>
-      <c r="B10" s="13">
+      <c r="B10" s="14">
         <f>IFERROR(VLOOKUP(A10,'Raw Export (Scuba TSV)'!$A$5:$E$1478,2,FALSE),"")</f>
         <v/>
       </c>
-      <c r="C10" s="13">
+      <c r="C10" s="14">
         <f>IFERROR(VLOOKUP(A10,'Raw Export (Scuba TSV)'!$A$5:$E$1478,3,FALSE),"")</f>
         <v/>
       </c>
-      <c r="D10" s="14">
+      <c r="D10" s="15">
         <f>IFERROR(VLOOKUP(A10,'Raw Export (Scuba TSV)'!$A$5:$E$1478,4,FALSE),"")</f>
         <v/>
       </c>
-      <c r="E10" s="13">
+      <c r="E10" s="14">
         <f>IFERROR(VLOOKUP(A10,'Raw Export (Scuba TSV)'!$A$5:$E$1478,5,FALSE),"")</f>
         <v/>
       </c>
-      <c r="F10" s="15" t="inlineStr">
+      <c r="F10" s="16" t="inlineStr">
         <is>
           <t>Hate Speech</t>
         </is>
       </c>
-      <c r="G10" s="16">
+      <c r="G10" s="17">
         <f>IF(E10=F10,"Match","ERROR")</f>
         <v/>
       </c>
-      <c r="H10" s="7" t="inlineStr"/>
+      <c r="H10" s="18" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
@@ -38928,14 +38934,14 @@
       </c>
       <c r="F11" s="11" t="inlineStr">
         <is>
-          <t>Bullying &amp; Harassment</t>
+          <t>Adult Sexual Solicitation &amp; Prostitution</t>
         </is>
       </c>
       <c r="G11" s="12">
         <f>IF(E11=F11,"Match","ERROR")</f>
         <v/>
       </c>
-      <c r="H11" s="5" t="inlineStr"/>
+      <c r="H11" s="13" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="7" t="inlineStr">
@@ -38943,32 +38949,32 @@
           <t>T-100662</t>
         </is>
       </c>
-      <c r="B12" s="13">
+      <c r="B12" s="14">
         <f>IFERROR(VLOOKUP(A12,'Raw Export (Scuba TSV)'!$A$5:$E$1478,2,FALSE),"")</f>
         <v/>
       </c>
-      <c r="C12" s="13">
+      <c r="C12" s="14">
         <f>IFERROR(VLOOKUP(A12,'Raw Export (Scuba TSV)'!$A$5:$E$1478,3,FALSE),"")</f>
         <v/>
       </c>
-      <c r="D12" s="14">
+      <c r="D12" s="15">
         <f>IFERROR(VLOOKUP(A12,'Raw Export (Scuba TSV)'!$A$5:$E$1478,4,FALSE),"")</f>
         <v/>
       </c>
-      <c r="E12" s="13">
+      <c r="E12" s="14">
         <f>IFERROR(VLOOKUP(A12,'Raw Export (Scuba TSV)'!$A$5:$E$1478,5,FALSE),"")</f>
         <v/>
       </c>
-      <c r="F12" s="15" t="inlineStr">
+      <c r="F12" s="16" t="inlineStr">
         <is>
           <t>Child Safety</t>
         </is>
       </c>
-      <c r="G12" s="16">
+      <c r="G12" s="17">
         <f>IF(E12=F12,"Match","ERROR")</f>
         <v/>
       </c>
-      <c r="H12" s="7" t="inlineStr"/>
+      <c r="H12" s="18" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="5" t="inlineStr">
@@ -39001,7 +39007,7 @@
         <f>IF(E13=F13,"Match","ERROR")</f>
         <v/>
       </c>
-      <c r="H13" s="5" t="inlineStr"/>
+      <c r="H13" s="13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="7" t="inlineStr">
@@ -39009,32 +39015,32 @@
           <t>T-101309</t>
         </is>
       </c>
-      <c r="B14" s="13">
+      <c r="B14" s="14">
         <f>IFERROR(VLOOKUP(A14,'Raw Export (Scuba TSV)'!$A$5:$E$1478,2,FALSE),"")</f>
         <v/>
       </c>
-      <c r="C14" s="13">
+      <c r="C14" s="14">
         <f>IFERROR(VLOOKUP(A14,'Raw Export (Scuba TSV)'!$A$5:$E$1478,3,FALSE),"")</f>
         <v/>
       </c>
-      <c r="D14" s="14">
+      <c r="D14" s="15">
         <f>IFERROR(VLOOKUP(A14,'Raw Export (Scuba TSV)'!$A$5:$E$1478,4,FALSE),"")</f>
         <v/>
       </c>
-      <c r="E14" s="13">
+      <c r="E14" s="14">
         <f>IFERROR(VLOOKUP(A14,'Raw Export (Scuba TSV)'!$A$5:$E$1478,5,FALSE),"")</f>
         <v/>
       </c>
-      <c r="F14" s="15" t="inlineStr">
+      <c r="F14" s="16" t="inlineStr">
         <is>
           <t>Adult Nudity &amp; Sexual Activity</t>
         </is>
       </c>
-      <c r="G14" s="16">
+      <c r="G14" s="17">
         <f>IF(E14=F14,"Match","ERROR")</f>
         <v/>
       </c>
-      <c r="H14" s="7" t="inlineStr"/>
+      <c r="H14" s="18" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="5" t="inlineStr">
@@ -39067,7 +39073,7 @@
         <f>IF(E15=F15,"Match","ERROR")</f>
         <v/>
       </c>
-      <c r="H15" s="5" t="inlineStr"/>
+      <c r="H15" s="13" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="7" t="inlineStr">
@@ -39075,32 +39081,32 @@
           <t>T-100164</t>
         </is>
       </c>
-      <c r="B16" s="13">
+      <c r="B16" s="14">
         <f>IFERROR(VLOOKUP(A16,'Raw Export (Scuba TSV)'!$A$5:$E$1478,2,FALSE),"")</f>
         <v/>
       </c>
-      <c r="C16" s="13">
+      <c r="C16" s="14">
         <f>IFERROR(VLOOKUP(A16,'Raw Export (Scuba TSV)'!$A$5:$E$1478,3,FALSE),"")</f>
         <v/>
       </c>
-      <c r="D16" s="14">
+      <c r="D16" s="15">
         <f>IFERROR(VLOOKUP(A16,'Raw Export (Scuba TSV)'!$A$5:$E$1478,4,FALSE),"")</f>
         <v/>
       </c>
-      <c r="E16" s="13">
+      <c r="E16" s="14">
         <f>IFERROR(VLOOKUP(A16,'Raw Export (Scuba TSV)'!$A$5:$E$1478,5,FALSE),"")</f>
         <v/>
       </c>
-      <c r="F16" s="15" t="inlineStr">
+      <c r="F16" s="16" t="inlineStr">
         <is>
           <t>Dangerous Organizations</t>
         </is>
       </c>
-      <c r="G16" s="16">
+      <c r="G16" s="17">
         <f>IF(E16=F16,"Match","ERROR")</f>
         <v/>
       </c>
-      <c r="H16" s="7" t="inlineStr"/>
+      <c r="H16" s="18" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="5" t="inlineStr">
@@ -39133,7 +39139,7 @@
         <f>IF(E17=F17,"Match","ERROR")</f>
         <v/>
       </c>
-      <c r="H17" s="5" t="inlineStr"/>
+      <c r="H17" s="13" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="7" t="inlineStr">
@@ -39141,32 +39147,32 @@
           <t>T-101465</t>
         </is>
       </c>
-      <c r="B18" s="13">
+      <c r="B18" s="14">
         <f>IFERROR(VLOOKUP(A18,'Raw Export (Scuba TSV)'!$A$5:$E$1478,2,FALSE),"")</f>
         <v/>
       </c>
-      <c r="C18" s="13">
+      <c r="C18" s="14">
         <f>IFERROR(VLOOKUP(A18,'Raw Export (Scuba TSV)'!$A$5:$E$1478,3,FALSE),"")</f>
         <v/>
       </c>
-      <c r="D18" s="14">
+      <c r="D18" s="15">
         <f>IFERROR(VLOOKUP(A18,'Raw Export (Scuba TSV)'!$A$5:$E$1478,4,FALSE),"")</f>
         <v/>
       </c>
-      <c r="E18" s="13">
+      <c r="E18" s="14">
         <f>IFERROR(VLOOKUP(A18,'Raw Export (Scuba TSV)'!$A$5:$E$1478,5,FALSE),"")</f>
         <v/>
       </c>
-      <c r="F18" s="15" t="inlineStr">
+      <c r="F18" s="16" t="inlineStr">
         <is>
           <t>Hate Speech</t>
         </is>
       </c>
-      <c r="G18" s="16">
+      <c r="G18" s="17">
         <f>IF(E18=F18,"Match","ERROR")</f>
         <v/>
       </c>
-      <c r="H18" s="7" t="inlineStr"/>
+      <c r="H18" s="18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="5" t="inlineStr">
@@ -39192,14 +39198,14 @@
       </c>
       <c r="F19" s="11" t="inlineStr">
         <is>
-          <t>Misinformation</t>
+          <t>Spam</t>
         </is>
       </c>
       <c r="G19" s="12">
         <f>IF(E19=F19,"Match","ERROR")</f>
         <v/>
       </c>
-      <c r="H19" s="5" t="inlineStr"/>
+      <c r="H19" s="13" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="7" t="inlineStr">
@@ -39207,32 +39213,32 @@
           <t>T-101178</t>
         </is>
       </c>
-      <c r="B20" s="13">
+      <c r="B20" s="14">
         <f>IFERROR(VLOOKUP(A20,'Raw Export (Scuba TSV)'!$A$5:$E$1478,2,FALSE),"")</f>
         <v/>
       </c>
-      <c r="C20" s="13">
+      <c r="C20" s="14">
         <f>IFERROR(VLOOKUP(A20,'Raw Export (Scuba TSV)'!$A$5:$E$1478,3,FALSE),"")</f>
         <v/>
       </c>
-      <c r="D20" s="14">
+      <c r="D20" s="15">
         <f>IFERROR(VLOOKUP(A20,'Raw Export (Scuba TSV)'!$A$5:$E$1478,4,FALSE),"")</f>
         <v/>
       </c>
-      <c r="E20" s="13">
+      <c r="E20" s="14">
         <f>IFERROR(VLOOKUP(A20,'Raw Export (Scuba TSV)'!$A$5:$E$1478,5,FALSE),"")</f>
         <v/>
       </c>
-      <c r="F20" s="15" t="inlineStr">
+      <c r="F20" s="16" t="inlineStr">
         <is>
           <t>Graphic Violence</t>
         </is>
       </c>
-      <c r="G20" s="16">
+      <c r="G20" s="17">
         <f>IF(E20=F20,"Match","ERROR")</f>
         <v/>
       </c>
-      <c r="H20" s="7" t="inlineStr"/>
+      <c r="H20" s="18" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="5" t="inlineStr">
@@ -39265,7 +39271,7 @@
         <f>IF(E21=F21,"Match","ERROR")</f>
         <v/>
       </c>
-      <c r="H21" s="5" t="inlineStr"/>
+      <c r="H21" s="13" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="7" t="inlineStr">
@@ -39273,32 +39279,32 @@
           <t>T-101372</t>
         </is>
       </c>
-      <c r="B22" s="13">
+      <c r="B22" s="14">
         <f>IFERROR(VLOOKUP(A22,'Raw Export (Scuba TSV)'!$A$5:$E$1478,2,FALSE),"")</f>
         <v/>
       </c>
-      <c r="C22" s="13">
+      <c r="C22" s="14">
         <f>IFERROR(VLOOKUP(A22,'Raw Export (Scuba TSV)'!$A$5:$E$1478,3,FALSE),"")</f>
         <v/>
       </c>
-      <c r="D22" s="14">
+      <c r="D22" s="15">
         <f>IFERROR(VLOOKUP(A22,'Raw Export (Scuba TSV)'!$A$5:$E$1478,4,FALSE),"")</f>
         <v/>
       </c>
-      <c r="E22" s="13">
+      <c r="E22" s="14">
         <f>IFERROR(VLOOKUP(A22,'Raw Export (Scuba TSV)'!$A$5:$E$1478,5,FALSE),"")</f>
         <v/>
       </c>
-      <c r="F22" s="15" t="inlineStr">
+      <c r="F22" s="16" t="inlineStr">
         <is>
           <t>Adult Nudity &amp; Sexual Activity</t>
         </is>
       </c>
-      <c r="G22" s="16">
+      <c r="G22" s="17">
         <f>IF(E22=F22,"Match","ERROR")</f>
         <v/>
       </c>
-      <c r="H22" s="7" t="inlineStr"/>
+      <c r="H22" s="18" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" s="5" t="inlineStr">
@@ -39331,7 +39337,7 @@
         <f>IF(E23=F23,"Match","ERROR")</f>
         <v/>
       </c>
-      <c r="H23" s="5" t="inlineStr"/>
+      <c r="H23" s="13" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" s="7" t="inlineStr">
@@ -39339,32 +39345,32 @@
           <t>T-100688</t>
         </is>
       </c>
-      <c r="B24" s="13">
+      <c r="B24" s="14">
         <f>IFERROR(VLOOKUP(A24,'Raw Export (Scuba TSV)'!$A$5:$E$1478,2,FALSE),"")</f>
         <v/>
       </c>
-      <c r="C24" s="13">
+      <c r="C24" s="14">
         <f>IFERROR(VLOOKUP(A24,'Raw Export (Scuba TSV)'!$A$5:$E$1478,3,FALSE),"")</f>
         <v/>
       </c>
-      <c r="D24" s="14">
+      <c r="D24" s="15">
         <f>IFERROR(VLOOKUP(A24,'Raw Export (Scuba TSV)'!$A$5:$E$1478,4,FALSE),"")</f>
         <v/>
       </c>
-      <c r="E24" s="13">
+      <c r="E24" s="14">
         <f>IFERROR(VLOOKUP(A24,'Raw Export (Scuba TSV)'!$A$5:$E$1478,5,FALSE),"")</f>
         <v/>
       </c>
-      <c r="F24" s="15" t="inlineStr">
+      <c r="F24" s="16" t="inlineStr">
         <is>
           <t>Fraud &amp; Deceptive Practices</t>
         </is>
       </c>
-      <c r="G24" s="16">
+      <c r="G24" s="17">
         <f>IF(E24=F24,"Match","ERROR")</f>
         <v/>
       </c>
-      <c r="H24" s="7" t="inlineStr"/>
+      <c r="H24" s="18" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" s="5" t="inlineStr">
@@ -39390,14 +39396,14 @@
       </c>
       <c r="F25" s="11" t="inlineStr">
         <is>
-          <t>Misinformation</t>
+          <t>Spam</t>
         </is>
       </c>
       <c r="G25" s="12">
         <f>IF(E25=F25,"Match","ERROR")</f>
         <v/>
       </c>
-      <c r="H25" s="5" t="inlineStr"/>
+      <c r="H25" s="13" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" s="7" t="inlineStr">
@@ -39405,32 +39411,32 @@
           <t>T-101285</t>
         </is>
       </c>
-      <c r="B26" s="13">
+      <c r="B26" s="14">
         <f>IFERROR(VLOOKUP(A26,'Raw Export (Scuba TSV)'!$A$5:$E$1478,2,FALSE),"")</f>
         <v/>
       </c>
-      <c r="C26" s="13">
+      <c r="C26" s="14">
         <f>IFERROR(VLOOKUP(A26,'Raw Export (Scuba TSV)'!$A$5:$E$1478,3,FALSE),"")</f>
         <v/>
       </c>
-      <c r="D26" s="14">
+      <c r="D26" s="15">
         <f>IFERROR(VLOOKUP(A26,'Raw Export (Scuba TSV)'!$A$5:$E$1478,4,FALSE),"")</f>
         <v/>
       </c>
-      <c r="E26" s="13">
+      <c r="E26" s="14">
         <f>IFERROR(VLOOKUP(A26,'Raw Export (Scuba TSV)'!$A$5:$E$1478,5,FALSE),"")</f>
         <v/>
       </c>
-      <c r="F26" s="15" t="inlineStr">
+      <c r="F26" s="16" t="inlineStr">
         <is>
           <t>Dangerous Organizations</t>
         </is>
       </c>
-      <c r="G26" s="16">
+      <c r="G26" s="17">
         <f>IF(E26=F26,"Match","ERROR")</f>
         <v/>
       </c>
-      <c r="H26" s="7" t="inlineStr"/>
+      <c r="H26" s="18" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" s="5" t="inlineStr">
@@ -39456,14 +39462,14 @@
       </c>
       <c r="F27" s="11" t="inlineStr">
         <is>
-          <t>Spam</t>
+          <t>Bullying &amp; Harassment</t>
         </is>
       </c>
       <c r="G27" s="12">
         <f>IF(E27=F27,"Match","ERROR")</f>
         <v/>
       </c>
-      <c r="H27" s="5" t="inlineStr"/>
+      <c r="H27" s="13" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" s="7" t="inlineStr">
@@ -39471,32 +39477,32 @@
           <t>T-100198</t>
         </is>
       </c>
-      <c r="B28" s="13">
+      <c r="B28" s="14">
         <f>IFERROR(VLOOKUP(A28,'Raw Export (Scuba TSV)'!$A$5:$E$1478,2,FALSE),"")</f>
         <v/>
       </c>
-      <c r="C28" s="13">
+      <c r="C28" s="14">
         <f>IFERROR(VLOOKUP(A28,'Raw Export (Scuba TSV)'!$A$5:$E$1478,3,FALSE),"")</f>
         <v/>
       </c>
-      <c r="D28" s="14">
+      <c r="D28" s="15">
         <f>IFERROR(VLOOKUP(A28,'Raw Export (Scuba TSV)'!$A$5:$E$1478,4,FALSE),"")</f>
         <v/>
       </c>
-      <c r="E28" s="13">
+      <c r="E28" s="14">
         <f>IFERROR(VLOOKUP(A28,'Raw Export (Scuba TSV)'!$A$5:$E$1478,5,FALSE),"")</f>
         <v/>
       </c>
-      <c r="F28" s="15" t="inlineStr">
+      <c r="F28" s="16" t="inlineStr">
         <is>
           <t>Child Safety</t>
         </is>
       </c>
-      <c r="G28" s="16">
+      <c r="G28" s="17">
         <f>IF(E28=F28,"Match","ERROR")</f>
         <v/>
       </c>
-      <c r="H28" s="7" t="inlineStr"/>
+      <c r="H28" s="18" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" s="5" t="inlineStr">
@@ -39529,7 +39535,7 @@
         <f>IF(E29=F29,"Match","ERROR")</f>
         <v/>
       </c>
-      <c r="H29" s="5" t="inlineStr"/>
+      <c r="H29" s="13" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" s="7" t="inlineStr">
@@ -39537,32 +39543,32 @@
           <t>T-100610</t>
         </is>
       </c>
-      <c r="B30" s="13">
+      <c r="B30" s="14">
         <f>IFERROR(VLOOKUP(A30,'Raw Export (Scuba TSV)'!$A$5:$E$1478,2,FALSE),"")</f>
         <v/>
       </c>
-      <c r="C30" s="13">
+      <c r="C30" s="14">
         <f>IFERROR(VLOOKUP(A30,'Raw Export (Scuba TSV)'!$A$5:$E$1478,3,FALSE),"")</f>
         <v/>
       </c>
-      <c r="D30" s="14">
+      <c r="D30" s="15">
         <f>IFERROR(VLOOKUP(A30,'Raw Export (Scuba TSV)'!$A$5:$E$1478,4,FALSE),"")</f>
         <v/>
       </c>
-      <c r="E30" s="13">
+      <c r="E30" s="14">
         <f>IFERROR(VLOOKUP(A30,'Raw Export (Scuba TSV)'!$A$5:$E$1478,5,FALSE),"")</f>
         <v/>
       </c>
-      <c r="F30" s="15" t="inlineStr">
+      <c r="F30" s="16" t="inlineStr">
         <is>
           <t>Adult Nudity &amp; Sexual Activity</t>
         </is>
       </c>
-      <c r="G30" s="16">
+      <c r="G30" s="17">
         <f>IF(E30=F30,"Match","ERROR")</f>
         <v/>
       </c>
-      <c r="H30" s="7" t="inlineStr"/>
+      <c r="H30" s="18" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" s="5" t="inlineStr">
@@ -39595,7 +39601,7 @@
         <f>IF(E31=F31,"Match","ERROR")</f>
         <v/>
       </c>
-      <c r="H31" s="5" t="inlineStr"/>
+      <c r="H31" s="13" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" s="7" t="inlineStr">
@@ -39603,32 +39609,32 @@
           <t>T-100390</t>
         </is>
       </c>
-      <c r="B32" s="13">
+      <c r="B32" s="14">
         <f>IFERROR(VLOOKUP(A32,'Raw Export (Scuba TSV)'!$A$5:$E$1478,2,FALSE),"")</f>
         <v/>
       </c>
-      <c r="C32" s="13">
+      <c r="C32" s="14">
         <f>IFERROR(VLOOKUP(A32,'Raw Export (Scuba TSV)'!$A$5:$E$1478,3,FALSE),"")</f>
         <v/>
       </c>
-      <c r="D32" s="14">
+      <c r="D32" s="15">
         <f>IFERROR(VLOOKUP(A32,'Raw Export (Scuba TSV)'!$A$5:$E$1478,4,FALSE),"")</f>
         <v/>
       </c>
-      <c r="E32" s="13">
+      <c r="E32" s="14">
         <f>IFERROR(VLOOKUP(A32,'Raw Export (Scuba TSV)'!$A$5:$E$1478,5,FALSE),"")</f>
         <v/>
       </c>
-      <c r="F32" s="15" t="inlineStr">
+      <c r="F32" s="16" t="inlineStr">
         <is>
           <t>Graphic Violence</t>
         </is>
       </c>
-      <c r="G32" s="16">
+      <c r="G32" s="17">
         <f>IF(E32=F32,"Match","ERROR")</f>
         <v/>
       </c>
-      <c r="H32" s="7" t="inlineStr"/>
+      <c r="H32" s="18" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" s="5" t="inlineStr">
@@ -39661,7 +39667,7 @@
         <f>IF(E33=F33,"Match","ERROR")</f>
         <v/>
       </c>
-      <c r="H33" s="5" t="inlineStr"/>
+      <c r="H33" s="13" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" s="7" t="inlineStr">
@@ -39669,32 +39675,32 @@
           <t>T-100485</t>
         </is>
       </c>
-      <c r="B34" s="13">
+      <c r="B34" s="14">
         <f>IFERROR(VLOOKUP(A34,'Raw Export (Scuba TSV)'!$A$5:$E$1478,2,FALSE),"")</f>
         <v/>
       </c>
-      <c r="C34" s="13">
+      <c r="C34" s="14">
         <f>IFERROR(VLOOKUP(A34,'Raw Export (Scuba TSV)'!$A$5:$E$1478,3,FALSE),"")</f>
         <v/>
       </c>
-      <c r="D34" s="14">
+      <c r="D34" s="15">
         <f>IFERROR(VLOOKUP(A34,'Raw Export (Scuba TSV)'!$A$5:$E$1478,4,FALSE),"")</f>
         <v/>
       </c>
-      <c r="E34" s="13">
+      <c r="E34" s="14">
         <f>IFERROR(VLOOKUP(A34,'Raw Export (Scuba TSV)'!$A$5:$E$1478,5,FALSE),"")</f>
         <v/>
       </c>
-      <c r="F34" s="15" t="inlineStr">
+      <c r="F34" s="16" t="inlineStr">
         <is>
           <t>Fraud &amp; Deceptive Practices</t>
         </is>
       </c>
-      <c r="G34" s="16">
+      <c r="G34" s="17">
         <f>IF(E34=F34,"Match","ERROR")</f>
         <v/>
       </c>
-      <c r="H34" s="7" t="inlineStr"/>
+      <c r="H34" s="18" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" s="5" t="inlineStr">
@@ -39727,7 +39733,7 @@
         <f>IF(E35=F35,"Match","ERROR")</f>
         <v/>
       </c>
-      <c r="H35" s="5" t="inlineStr"/>
+      <c r="H35" s="13" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" s="7" t="inlineStr">
@@ -39735,32 +39741,32 @@
           <t>T-100180</t>
         </is>
       </c>
-      <c r="B36" s="13">
+      <c r="B36" s="14">
         <f>IFERROR(VLOOKUP(A36,'Raw Export (Scuba TSV)'!$A$5:$E$1478,2,FALSE),"")</f>
         <v/>
       </c>
-      <c r="C36" s="13">
+      <c r="C36" s="14">
         <f>IFERROR(VLOOKUP(A36,'Raw Export (Scuba TSV)'!$A$5:$E$1478,3,FALSE),"")</f>
         <v/>
       </c>
-      <c r="D36" s="14">
+      <c r="D36" s="15">
         <f>IFERROR(VLOOKUP(A36,'Raw Export (Scuba TSV)'!$A$5:$E$1478,4,FALSE),"")</f>
         <v/>
       </c>
-      <c r="E36" s="13">
+      <c r="E36" s="14">
         <f>IFERROR(VLOOKUP(A36,'Raw Export (Scuba TSV)'!$A$5:$E$1478,5,FALSE),"")</f>
         <v/>
       </c>
-      <c r="F36" s="15" t="inlineStr">
+      <c r="F36" s="16" t="inlineStr">
         <is>
           <t>Child Safety</t>
         </is>
       </c>
-      <c r="G36" s="16">
+      <c r="G36" s="17">
         <f>IF(E36=F36,"Match","ERROR")</f>
         <v/>
       </c>
-      <c r="H36" s="7" t="inlineStr"/>
+      <c r="H36" s="18" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" s="5" t="inlineStr">
@@ -39793,7 +39799,7 @@
         <f>IF(E37=F37,"Match","ERROR")</f>
         <v/>
       </c>
-      <c r="H37" s="5" t="inlineStr"/>
+      <c r="H37" s="13" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" s="7" t="inlineStr">
@@ -39801,32 +39807,32 @@
           <t>T-100464</t>
         </is>
       </c>
-      <c r="B38" s="13">
+      <c r="B38" s="14">
         <f>IFERROR(VLOOKUP(A38,'Raw Export (Scuba TSV)'!$A$5:$E$1478,2,FALSE),"")</f>
         <v/>
       </c>
-      <c r="C38" s="13">
+      <c r="C38" s="14">
         <f>IFERROR(VLOOKUP(A38,'Raw Export (Scuba TSV)'!$A$5:$E$1478,3,FALSE),"")</f>
         <v/>
       </c>
-      <c r="D38" s="14">
+      <c r="D38" s="15">
         <f>IFERROR(VLOOKUP(A38,'Raw Export (Scuba TSV)'!$A$5:$E$1478,4,FALSE),"")</f>
         <v/>
       </c>
-      <c r="E38" s="13">
+      <c r="E38" s="14">
         <f>IFERROR(VLOOKUP(A38,'Raw Export (Scuba TSV)'!$A$5:$E$1478,5,FALSE),"")</f>
         <v/>
       </c>
-      <c r="F38" s="15" t="inlineStr">
+      <c r="F38" s="16" t="inlineStr">
         <is>
           <t>Graphic Violence</t>
         </is>
       </c>
-      <c r="G38" s="16">
+      <c r="G38" s="17">
         <f>IF(E38=F38,"Match","ERROR")</f>
         <v/>
       </c>
-      <c r="H38" s="7" t="inlineStr"/>
+      <c r="H38" s="18" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" s="5" t="inlineStr">
@@ -39859,7 +39865,7 @@
         <f>IF(E39=F39,"Match","ERROR")</f>
         <v/>
       </c>
-      <c r="H39" s="5" t="inlineStr"/>
+      <c r="H39" s="13" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" s="7" t="inlineStr">
@@ -39867,32 +39873,32 @@
           <t>T-100552</t>
         </is>
       </c>
-      <c r="B40" s="13">
+      <c r="B40" s="14">
         <f>IFERROR(VLOOKUP(A40,'Raw Export (Scuba TSV)'!$A$5:$E$1478,2,FALSE),"")</f>
         <v/>
       </c>
-      <c r="C40" s="13">
+      <c r="C40" s="14">
         <f>IFERROR(VLOOKUP(A40,'Raw Export (Scuba TSV)'!$A$5:$E$1478,3,FALSE),"")</f>
         <v/>
       </c>
-      <c r="D40" s="14">
+      <c r="D40" s="15">
         <f>IFERROR(VLOOKUP(A40,'Raw Export (Scuba TSV)'!$A$5:$E$1478,4,FALSE),"")</f>
         <v/>
       </c>
-      <c r="E40" s="13">
+      <c r="E40" s="14">
         <f>IFERROR(VLOOKUP(A40,'Raw Export (Scuba TSV)'!$A$5:$E$1478,5,FALSE),"")</f>
         <v/>
       </c>
-      <c r="F40" s="15" t="inlineStr">
-        <is>
-          <t>Misinformation</t>
-        </is>
-      </c>
-      <c r="G40" s="16">
+      <c r="F40" s="16" t="inlineStr">
+        <is>
+          <t>Spam</t>
+        </is>
+      </c>
+      <c r="G40" s="17">
         <f>IF(E40=F40,"Match","ERROR")</f>
         <v/>
       </c>
-      <c r="H40" s="7" t="inlineStr"/>
+      <c r="H40" s="18" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" s="5" t="inlineStr">
@@ -39925,7 +39931,7 @@
         <f>IF(E41=F41,"Match","ERROR")</f>
         <v/>
       </c>
-      <c r="H41" s="5" t="inlineStr"/>
+      <c r="H41" s="13" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" s="7" t="inlineStr">
@@ -39933,32 +39939,32 @@
           <t>T-100254</t>
         </is>
       </c>
-      <c r="B42" s="13">
+      <c r="B42" s="14">
         <f>IFERROR(VLOOKUP(A42,'Raw Export (Scuba TSV)'!$A$5:$E$1478,2,FALSE),"")</f>
         <v/>
       </c>
-      <c r="C42" s="13">
+      <c r="C42" s="14">
         <f>IFERROR(VLOOKUP(A42,'Raw Export (Scuba TSV)'!$A$5:$E$1478,3,FALSE),"")</f>
         <v/>
       </c>
-      <c r="D42" s="14">
+      <c r="D42" s="15">
         <f>IFERROR(VLOOKUP(A42,'Raw Export (Scuba TSV)'!$A$5:$E$1478,4,FALSE),"")</f>
         <v/>
       </c>
-      <c r="E42" s="13">
+      <c r="E42" s="14">
         <f>IFERROR(VLOOKUP(A42,'Raw Export (Scuba TSV)'!$A$5:$E$1478,5,FALSE),"")</f>
         <v/>
       </c>
-      <c r="F42" s="15" t="inlineStr">
-        <is>
-          <t>Spam</t>
-        </is>
-      </c>
-      <c r="G42" s="16">
+      <c r="F42" s="16" t="inlineStr">
+        <is>
+          <t>Bullying &amp; Harassment</t>
+        </is>
+      </c>
+      <c r="G42" s="17">
         <f>IF(E42=F42,"Match","ERROR")</f>
         <v/>
       </c>
-      <c r="H42" s="7" t="inlineStr"/>
+      <c r="H42" s="18" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" s="5" t="inlineStr">
@@ -39984,14 +39990,14 @@
       </c>
       <c r="F43" s="11" t="inlineStr">
         <is>
-          <t>Bullying &amp; Harassment</t>
+          <t>Adult Sexual Solicitation &amp; Prostitution</t>
         </is>
       </c>
       <c r="G43" s="12">
         <f>IF(E43=F43,"Match","ERROR")</f>
         <v/>
       </c>
-      <c r="H43" s="5" t="inlineStr"/>
+      <c r="H43" s="13" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" s="7" t="inlineStr">
@@ -39999,32 +40005,32 @@
           <t>T-101423</t>
         </is>
       </c>
-      <c r="B44" s="13">
+      <c r="B44" s="14">
         <f>IFERROR(VLOOKUP(A44,'Raw Export (Scuba TSV)'!$A$5:$E$1478,2,FALSE),"")</f>
         <v/>
       </c>
-      <c r="C44" s="13">
+      <c r="C44" s="14">
         <f>IFERROR(VLOOKUP(A44,'Raw Export (Scuba TSV)'!$A$5:$E$1478,3,FALSE),"")</f>
         <v/>
       </c>
-      <c r="D44" s="14">
+      <c r="D44" s="15">
         <f>IFERROR(VLOOKUP(A44,'Raw Export (Scuba TSV)'!$A$5:$E$1478,4,FALSE),"")</f>
         <v/>
       </c>
-      <c r="E44" s="13">
+      <c r="E44" s="14">
         <f>IFERROR(VLOOKUP(A44,'Raw Export (Scuba TSV)'!$A$5:$E$1478,5,FALSE),"")</f>
         <v/>
       </c>
-      <c r="F44" s="15" t="inlineStr">
+      <c r="F44" s="16" t="inlineStr">
         <is>
           <t>Child Safety</t>
         </is>
       </c>
-      <c r="G44" s="16">
+      <c r="G44" s="17">
         <f>IF(E44=F44,"Match","ERROR")</f>
         <v/>
       </c>
-      <c r="H44" s="7" t="inlineStr"/>
+      <c r="H44" s="18" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" s="5" t="inlineStr">
@@ -40057,7 +40063,7 @@
         <f>IF(E45=F45,"Match","ERROR")</f>
         <v/>
       </c>
-      <c r="H45" s="5" t="inlineStr"/>
+      <c r="H45" s="13" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" s="7" t="inlineStr">
@@ -40065,32 +40071,32 @@
           <t>T-100934</t>
         </is>
       </c>
-      <c r="B46" s="13">
+      <c r="B46" s="14">
         <f>IFERROR(VLOOKUP(A46,'Raw Export (Scuba TSV)'!$A$5:$E$1478,2,FALSE),"")</f>
         <v/>
       </c>
-      <c r="C46" s="13">
+      <c r="C46" s="14">
         <f>IFERROR(VLOOKUP(A46,'Raw Export (Scuba TSV)'!$A$5:$E$1478,3,FALSE),"")</f>
         <v/>
       </c>
-      <c r="D46" s="14">
+      <c r="D46" s="15">
         <f>IFERROR(VLOOKUP(A46,'Raw Export (Scuba TSV)'!$A$5:$E$1478,4,FALSE),"")</f>
         <v/>
       </c>
-      <c r="E46" s="13">
+      <c r="E46" s="14">
         <f>IFERROR(VLOOKUP(A46,'Raw Export (Scuba TSV)'!$A$5:$E$1478,5,FALSE),"")</f>
         <v/>
       </c>
-      <c r="F46" s="15" t="inlineStr">
+      <c r="F46" s="16" t="inlineStr">
         <is>
           <t>Child Safety</t>
         </is>
       </c>
-      <c r="G46" s="16">
+      <c r="G46" s="17">
         <f>IF(E46=F46,"Match","ERROR")</f>
         <v/>
       </c>
-      <c r="H46" s="7" t="inlineStr"/>
+      <c r="H46" s="18" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" s="5" t="inlineStr">
@@ -40123,7 +40129,7 @@
         <f>IF(E47=F47,"Match","ERROR")</f>
         <v/>
       </c>
-      <c r="H47" s="5" t="inlineStr"/>
+      <c r="H47" s="13" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" s="7" t="inlineStr">
@@ -40131,32 +40137,32 @@
           <t>T-100130</t>
         </is>
       </c>
-      <c r="B48" s="13">
+      <c r="B48" s="14">
         <f>IFERROR(VLOOKUP(A48,'Raw Export (Scuba TSV)'!$A$5:$E$1478,2,FALSE),"")</f>
         <v/>
       </c>
-      <c r="C48" s="13">
+      <c r="C48" s="14">
         <f>IFERROR(VLOOKUP(A48,'Raw Export (Scuba TSV)'!$A$5:$E$1478,3,FALSE),"")</f>
         <v/>
       </c>
-      <c r="D48" s="14">
+      <c r="D48" s="15">
         <f>IFERROR(VLOOKUP(A48,'Raw Export (Scuba TSV)'!$A$5:$E$1478,4,FALSE),"")</f>
         <v/>
       </c>
-      <c r="E48" s="13">
+      <c r="E48" s="14">
         <f>IFERROR(VLOOKUP(A48,'Raw Export (Scuba TSV)'!$A$5:$E$1478,5,FALSE),"")</f>
         <v/>
       </c>
-      <c r="F48" s="15" t="inlineStr">
+      <c r="F48" s="16" t="inlineStr">
         <is>
           <t>Fraud &amp; Deceptive Practices</t>
         </is>
       </c>
-      <c r="G48" s="16">
+      <c r="G48" s="17">
         <f>IF(E48=F48,"Match","ERROR")</f>
         <v/>
       </c>
-      <c r="H48" s="7" t="inlineStr"/>
+      <c r="H48" s="18" t="inlineStr"/>
     </row>
   </sheetData>
   <conditionalFormatting sqref="G5:G48">
@@ -40169,7 +40175,7 @@
   </conditionalFormatting>
   <dataValidations count="1">
     <dataValidation sqref="F5:F48" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"No Violation,Hate Speech,Graphic Violence,Adult Nudity &amp; Sexual Activity,Bullying &amp; Harassment,Spam,Misinformation,Fraud &amp; Deceptive Practices,Child Safety,Dangerous Organizations"</formula1>
+      <formula1>"No Violation,Hate Speech,Graphic Violence,Adult Nudity &amp; Sexual Activity,Adult Sexual Solicitation &amp; Prostitution,Bullying &amp; Harassment,Spam,Fraud &amp; Deceptive Practices,Child Safety,Dangerous Organizations"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -40193,7 +40199,7 @@
     <col width="30" customWidth="1" min="5" max="5"/>
     <col width="30" customWidth="1" min="6" max="6"/>
     <col width="14" customWidth="1" min="7" max="7"/>
-    <col width="30" customWidth="1" min="8" max="8"/>
+    <col width="42" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -40289,32 +40295,32 @@
         <f>IF(OR(B5="",F5=""),"",IF(E5=F5,"Match","ERROR"))</f>
         <v/>
       </c>
-      <c r="H5" s="5" t="n"/>
+      <c r="H5" s="13" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="7" t="n"/>
-      <c r="B6" s="13">
+      <c r="B6" s="14">
         <f>IF(A6="","",IFERROR(INDEX(FILTER('Audit Sample List'!$A$5:$A$48,'Audit Sample List'!$B$5:$B$48=A6),COUNTIF($A$5:A6,A6)),""))</f>
         <v/>
       </c>
-      <c r="C6" s="13">
+      <c r="C6" s="14">
         <f>IF(B6="","",IFERROR(VLOOKUP(B6,'Raw Export (Scuba TSV)'!$A$5:$E$1478,3,FALSE),""))</f>
         <v/>
       </c>
-      <c r="D6" s="14">
+      <c r="D6" s="15">
         <f>IF(B6="","",IFERROR(VLOOKUP(B6,'Raw Export (Scuba TSV)'!$A$5:$E$1478,4,FALSE),""))</f>
         <v/>
       </c>
-      <c r="E6" s="13">
+      <c r="E6" s="14">
         <f>IF(B6="","",IFERROR(VLOOKUP(B6,'Raw Export (Scuba TSV)'!$A$5:$E$1478,5,FALSE),""))</f>
         <v/>
       </c>
-      <c r="F6" s="15" t="n"/>
-      <c r="G6" s="16">
+      <c r="F6" s="16" t="n"/>
+      <c r="G6" s="17">
         <f>IF(OR(B6="",F6=""),"",IF(E6=F6,"Match","ERROR"))</f>
         <v/>
       </c>
-      <c r="H6" s="7" t="n"/>
+      <c r="H6" s="18" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="5" t="n"/>
@@ -40339,32 +40345,32 @@
         <f>IF(OR(B7="",F7=""),"",IF(E7=F7,"Match","ERROR"))</f>
         <v/>
       </c>
-      <c r="H7" s="5" t="n"/>
+      <c r="H7" s="13" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="7" t="n"/>
-      <c r="B8" s="13">
+      <c r="B8" s="14">
         <f>IF(A8="","",IFERROR(INDEX(FILTER('Audit Sample List'!$A$5:$A$48,'Audit Sample List'!$B$5:$B$48=A8),COUNTIF($A$5:A8,A8)),""))</f>
         <v/>
       </c>
-      <c r="C8" s="13">
+      <c r="C8" s="14">
         <f>IF(B8="","",IFERROR(VLOOKUP(B8,'Raw Export (Scuba TSV)'!$A$5:$E$1478,3,FALSE),""))</f>
         <v/>
       </c>
-      <c r="D8" s="14">
+      <c r="D8" s="15">
         <f>IF(B8="","",IFERROR(VLOOKUP(B8,'Raw Export (Scuba TSV)'!$A$5:$E$1478,4,FALSE),""))</f>
         <v/>
       </c>
-      <c r="E8" s="13">
+      <c r="E8" s="14">
         <f>IF(B8="","",IFERROR(VLOOKUP(B8,'Raw Export (Scuba TSV)'!$A$5:$E$1478,5,FALSE),""))</f>
         <v/>
       </c>
-      <c r="F8" s="15" t="n"/>
-      <c r="G8" s="16">
+      <c r="F8" s="16" t="n"/>
+      <c r="G8" s="17">
         <f>IF(OR(B8="",F8=""),"",IF(E8=F8,"Match","ERROR"))</f>
         <v/>
       </c>
-      <c r="H8" s="7" t="n"/>
+      <c r="H8" s="18" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="5" t="n"/>
@@ -40389,32 +40395,32 @@
         <f>IF(OR(B9="",F9=""),"",IF(E9=F9,"Match","ERROR"))</f>
         <v/>
       </c>
-      <c r="H9" s="5" t="n"/>
+      <c r="H9" s="13" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="7" t="n"/>
-      <c r="B10" s="13">
+      <c r="B10" s="14">
         <f>IF(A10="","",IFERROR(INDEX(FILTER('Audit Sample List'!$A$5:$A$48,'Audit Sample List'!$B$5:$B$48=A10),COUNTIF($A$5:A10,A10)),""))</f>
         <v/>
       </c>
-      <c r="C10" s="13">
+      <c r="C10" s="14">
         <f>IF(B10="","",IFERROR(VLOOKUP(B10,'Raw Export (Scuba TSV)'!$A$5:$E$1478,3,FALSE),""))</f>
         <v/>
       </c>
-      <c r="D10" s="14">
+      <c r="D10" s="15">
         <f>IF(B10="","",IFERROR(VLOOKUP(B10,'Raw Export (Scuba TSV)'!$A$5:$E$1478,4,FALSE),""))</f>
         <v/>
       </c>
-      <c r="E10" s="13">
+      <c r="E10" s="14">
         <f>IF(B10="","",IFERROR(VLOOKUP(B10,'Raw Export (Scuba TSV)'!$A$5:$E$1478,5,FALSE),""))</f>
         <v/>
       </c>
-      <c r="F10" s="15" t="n"/>
-      <c r="G10" s="16">
+      <c r="F10" s="16" t="n"/>
+      <c r="G10" s="17">
         <f>IF(OR(B10="",F10=""),"",IF(E10=F10,"Match","ERROR"))</f>
         <v/>
       </c>
-      <c r="H10" s="7" t="n"/>
+      <c r="H10" s="18" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="5" t="n"/>
@@ -40439,32 +40445,32 @@
         <f>IF(OR(B11="",F11=""),"",IF(E11=F11,"Match","ERROR"))</f>
         <v/>
       </c>
-      <c r="H11" s="5" t="n"/>
+      <c r="H11" s="13" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="7" t="n"/>
-      <c r="B12" s="13">
+      <c r="B12" s="14">
         <f>IF(A12="","",IFERROR(INDEX(FILTER('Audit Sample List'!$A$5:$A$48,'Audit Sample List'!$B$5:$B$48=A12),COUNTIF($A$5:A12,A12)),""))</f>
         <v/>
       </c>
-      <c r="C12" s="13">
+      <c r="C12" s="14">
         <f>IF(B12="","",IFERROR(VLOOKUP(B12,'Raw Export (Scuba TSV)'!$A$5:$E$1478,3,FALSE),""))</f>
         <v/>
       </c>
-      <c r="D12" s="14">
+      <c r="D12" s="15">
         <f>IF(B12="","",IFERROR(VLOOKUP(B12,'Raw Export (Scuba TSV)'!$A$5:$E$1478,4,FALSE),""))</f>
         <v/>
       </c>
-      <c r="E12" s="13">
+      <c r="E12" s="14">
         <f>IF(B12="","",IFERROR(VLOOKUP(B12,'Raw Export (Scuba TSV)'!$A$5:$E$1478,5,FALSE),""))</f>
         <v/>
       </c>
-      <c r="F12" s="15" t="n"/>
-      <c r="G12" s="16">
+      <c r="F12" s="16" t="n"/>
+      <c r="G12" s="17">
         <f>IF(OR(B12="",F12=""),"",IF(E12=F12,"Match","ERROR"))</f>
         <v/>
       </c>
-      <c r="H12" s="7" t="n"/>
+      <c r="H12" s="18" t="n"/>
     </row>
     <row r="13">
       <c r="A13" s="5" t="n"/>
@@ -40489,32 +40495,32 @@
         <f>IF(OR(B13="",F13=""),"",IF(E13=F13,"Match","ERROR"))</f>
         <v/>
       </c>
-      <c r="H13" s="5" t="n"/>
+      <c r="H13" s="13" t="n"/>
     </row>
     <row r="14">
       <c r="A14" s="7" t="n"/>
-      <c r="B14" s="13">
+      <c r="B14" s="14">
         <f>IF(A14="","",IFERROR(INDEX(FILTER('Audit Sample List'!$A$5:$A$48,'Audit Sample List'!$B$5:$B$48=A14),COUNTIF($A$5:A14,A14)),""))</f>
         <v/>
       </c>
-      <c r="C14" s="13">
+      <c r="C14" s="14">
         <f>IF(B14="","",IFERROR(VLOOKUP(B14,'Raw Export (Scuba TSV)'!$A$5:$E$1478,3,FALSE),""))</f>
         <v/>
       </c>
-      <c r="D14" s="14">
+      <c r="D14" s="15">
         <f>IF(B14="","",IFERROR(VLOOKUP(B14,'Raw Export (Scuba TSV)'!$A$5:$E$1478,4,FALSE),""))</f>
         <v/>
       </c>
-      <c r="E14" s="13">
+      <c r="E14" s="14">
         <f>IF(B14="","",IFERROR(VLOOKUP(B14,'Raw Export (Scuba TSV)'!$A$5:$E$1478,5,FALSE),""))</f>
         <v/>
       </c>
-      <c r="F14" s="15" t="n"/>
-      <c r="G14" s="16">
+      <c r="F14" s="16" t="n"/>
+      <c r="G14" s="17">
         <f>IF(OR(B14="",F14=""),"",IF(E14=F14,"Match","ERROR"))</f>
         <v/>
       </c>
-      <c r="H14" s="7" t="n"/>
+      <c r="H14" s="18" t="n"/>
     </row>
     <row r="15">
       <c r="A15" s="5" t="n"/>
@@ -40539,32 +40545,32 @@
         <f>IF(OR(B15="",F15=""),"",IF(E15=F15,"Match","ERROR"))</f>
         <v/>
       </c>
-      <c r="H15" s="5" t="n"/>
+      <c r="H15" s="13" t="n"/>
     </row>
     <row r="16">
       <c r="A16" s="7" t="n"/>
-      <c r="B16" s="13">
+      <c r="B16" s="14">
         <f>IF(A16="","",IFERROR(INDEX(FILTER('Audit Sample List'!$A$5:$A$48,'Audit Sample List'!$B$5:$B$48=A16),COUNTIF($A$5:A16,A16)),""))</f>
         <v/>
       </c>
-      <c r="C16" s="13">
+      <c r="C16" s="14">
         <f>IF(B16="","",IFERROR(VLOOKUP(B16,'Raw Export (Scuba TSV)'!$A$5:$E$1478,3,FALSE),""))</f>
         <v/>
       </c>
-      <c r="D16" s="14">
+      <c r="D16" s="15">
         <f>IF(B16="","",IFERROR(VLOOKUP(B16,'Raw Export (Scuba TSV)'!$A$5:$E$1478,4,FALSE),""))</f>
         <v/>
       </c>
-      <c r="E16" s="13">
+      <c r="E16" s="14">
         <f>IF(B16="","",IFERROR(VLOOKUP(B16,'Raw Export (Scuba TSV)'!$A$5:$E$1478,5,FALSE),""))</f>
         <v/>
       </c>
-      <c r="F16" s="15" t="n"/>
-      <c r="G16" s="16">
+      <c r="F16" s="16" t="n"/>
+      <c r="G16" s="17">
         <f>IF(OR(B16="",F16=""),"",IF(E16=F16,"Match","ERROR"))</f>
         <v/>
       </c>
-      <c r="H16" s="7" t="n"/>
+      <c r="H16" s="18" t="n"/>
     </row>
     <row r="17">
       <c r="A17" s="5" t="n"/>
@@ -40589,32 +40595,32 @@
         <f>IF(OR(B17="",F17=""),"",IF(E17=F17,"Match","ERROR"))</f>
         <v/>
       </c>
-      <c r="H17" s="5" t="n"/>
+      <c r="H17" s="13" t="n"/>
     </row>
     <row r="18">
       <c r="A18" s="7" t="n"/>
-      <c r="B18" s="13">
+      <c r="B18" s="14">
         <f>IF(A18="","",IFERROR(INDEX(FILTER('Audit Sample List'!$A$5:$A$48,'Audit Sample List'!$B$5:$B$48=A18),COUNTIF($A$5:A18,A18)),""))</f>
         <v/>
       </c>
-      <c r="C18" s="13">
+      <c r="C18" s="14">
         <f>IF(B18="","",IFERROR(VLOOKUP(B18,'Raw Export (Scuba TSV)'!$A$5:$E$1478,3,FALSE),""))</f>
         <v/>
       </c>
-      <c r="D18" s="14">
+      <c r="D18" s="15">
         <f>IF(B18="","",IFERROR(VLOOKUP(B18,'Raw Export (Scuba TSV)'!$A$5:$E$1478,4,FALSE),""))</f>
         <v/>
       </c>
-      <c r="E18" s="13">
+      <c r="E18" s="14">
         <f>IF(B18="","",IFERROR(VLOOKUP(B18,'Raw Export (Scuba TSV)'!$A$5:$E$1478,5,FALSE),""))</f>
         <v/>
       </c>
-      <c r="F18" s="15" t="n"/>
-      <c r="G18" s="16">
+      <c r="F18" s="16" t="n"/>
+      <c r="G18" s="17">
         <f>IF(OR(B18="",F18=""),"",IF(E18=F18,"Match","ERROR"))</f>
         <v/>
       </c>
-      <c r="H18" s="7" t="n"/>
+      <c r="H18" s="18" t="n"/>
     </row>
     <row r="19">
       <c r="A19" s="5" t="n"/>
@@ -40639,32 +40645,32 @@
         <f>IF(OR(B19="",F19=""),"",IF(E19=F19,"Match","ERROR"))</f>
         <v/>
       </c>
-      <c r="H19" s="5" t="n"/>
+      <c r="H19" s="13" t="n"/>
     </row>
     <row r="20">
       <c r="A20" s="7" t="n"/>
-      <c r="B20" s="13">
+      <c r="B20" s="14">
         <f>IF(A20="","",IFERROR(INDEX(FILTER('Audit Sample List'!$A$5:$A$48,'Audit Sample List'!$B$5:$B$48=A20),COUNTIF($A$5:A20,A20)),""))</f>
         <v/>
       </c>
-      <c r="C20" s="13">
+      <c r="C20" s="14">
         <f>IF(B20="","",IFERROR(VLOOKUP(B20,'Raw Export (Scuba TSV)'!$A$5:$E$1478,3,FALSE),""))</f>
         <v/>
       </c>
-      <c r="D20" s="14">
+      <c r="D20" s="15">
         <f>IF(B20="","",IFERROR(VLOOKUP(B20,'Raw Export (Scuba TSV)'!$A$5:$E$1478,4,FALSE),""))</f>
         <v/>
       </c>
-      <c r="E20" s="13">
+      <c r="E20" s="14">
         <f>IF(B20="","",IFERROR(VLOOKUP(B20,'Raw Export (Scuba TSV)'!$A$5:$E$1478,5,FALSE),""))</f>
         <v/>
       </c>
-      <c r="F20" s="15" t="n"/>
-      <c r="G20" s="16">
+      <c r="F20" s="16" t="n"/>
+      <c r="G20" s="17">
         <f>IF(OR(B20="",F20=""),"",IF(E20=F20,"Match","ERROR"))</f>
         <v/>
       </c>
-      <c r="H20" s="7" t="n"/>
+      <c r="H20" s="18" t="n"/>
     </row>
     <row r="21">
       <c r="A21" s="5" t="n"/>
@@ -40689,32 +40695,32 @@
         <f>IF(OR(B21="",F21=""),"",IF(E21=F21,"Match","ERROR"))</f>
         <v/>
       </c>
-      <c r="H21" s="5" t="n"/>
+      <c r="H21" s="13" t="n"/>
     </row>
     <row r="22">
       <c r="A22" s="7" t="n"/>
-      <c r="B22" s="13">
+      <c r="B22" s="14">
         <f>IF(A22="","",IFERROR(INDEX(FILTER('Audit Sample List'!$A$5:$A$48,'Audit Sample List'!$B$5:$B$48=A22),COUNTIF($A$5:A22,A22)),""))</f>
         <v/>
       </c>
-      <c r="C22" s="13">
+      <c r="C22" s="14">
         <f>IF(B22="","",IFERROR(VLOOKUP(B22,'Raw Export (Scuba TSV)'!$A$5:$E$1478,3,FALSE),""))</f>
         <v/>
       </c>
-      <c r="D22" s="14">
+      <c r="D22" s="15">
         <f>IF(B22="","",IFERROR(VLOOKUP(B22,'Raw Export (Scuba TSV)'!$A$5:$E$1478,4,FALSE),""))</f>
         <v/>
       </c>
-      <c r="E22" s="13">
+      <c r="E22" s="14">
         <f>IF(B22="","",IFERROR(VLOOKUP(B22,'Raw Export (Scuba TSV)'!$A$5:$E$1478,5,FALSE),""))</f>
         <v/>
       </c>
-      <c r="F22" s="15" t="n"/>
-      <c r="G22" s="16">
+      <c r="F22" s="16" t="n"/>
+      <c r="G22" s="17">
         <f>IF(OR(B22="",F22=""),"",IF(E22=F22,"Match","ERROR"))</f>
         <v/>
       </c>
-      <c r="H22" s="7" t="n"/>
+      <c r="H22" s="18" t="n"/>
     </row>
     <row r="23">
       <c r="A23" s="5" t="n"/>
@@ -40739,32 +40745,32 @@
         <f>IF(OR(B23="",F23=""),"",IF(E23=F23,"Match","ERROR"))</f>
         <v/>
       </c>
-      <c r="H23" s="5" t="n"/>
+      <c r="H23" s="13" t="n"/>
     </row>
     <row r="24">
       <c r="A24" s="7" t="n"/>
-      <c r="B24" s="13">
+      <c r="B24" s="14">
         <f>IF(A24="","",IFERROR(INDEX(FILTER('Audit Sample List'!$A$5:$A$48,'Audit Sample List'!$B$5:$B$48=A24),COUNTIF($A$5:A24,A24)),""))</f>
         <v/>
       </c>
-      <c r="C24" s="13">
+      <c r="C24" s="14">
         <f>IF(B24="","",IFERROR(VLOOKUP(B24,'Raw Export (Scuba TSV)'!$A$5:$E$1478,3,FALSE),""))</f>
         <v/>
       </c>
-      <c r="D24" s="14">
+      <c r="D24" s="15">
         <f>IF(B24="","",IFERROR(VLOOKUP(B24,'Raw Export (Scuba TSV)'!$A$5:$E$1478,4,FALSE),""))</f>
         <v/>
       </c>
-      <c r="E24" s="13">
+      <c r="E24" s="14">
         <f>IF(B24="","",IFERROR(VLOOKUP(B24,'Raw Export (Scuba TSV)'!$A$5:$E$1478,5,FALSE),""))</f>
         <v/>
       </c>
-      <c r="F24" s="15" t="n"/>
-      <c r="G24" s="16">
+      <c r="F24" s="16" t="n"/>
+      <c r="G24" s="17">
         <f>IF(OR(B24="",F24=""),"",IF(E24=F24,"Match","ERROR"))</f>
         <v/>
       </c>
-      <c r="H24" s="7" t="n"/>
+      <c r="H24" s="18" t="n"/>
     </row>
     <row r="25">
       <c r="A25" s="5" t="n"/>
@@ -40789,32 +40795,32 @@
         <f>IF(OR(B25="",F25=""),"",IF(E25=F25,"Match","ERROR"))</f>
         <v/>
       </c>
-      <c r="H25" s="5" t="n"/>
+      <c r="H25" s="13" t="n"/>
     </row>
     <row r="26">
       <c r="A26" s="7" t="n"/>
-      <c r="B26" s="13">
+      <c r="B26" s="14">
         <f>IF(A26="","",IFERROR(INDEX(FILTER('Audit Sample List'!$A$5:$A$48,'Audit Sample List'!$B$5:$B$48=A26),COUNTIF($A$5:A26,A26)),""))</f>
         <v/>
       </c>
-      <c r="C26" s="13">
+      <c r="C26" s="14">
         <f>IF(B26="","",IFERROR(VLOOKUP(B26,'Raw Export (Scuba TSV)'!$A$5:$E$1478,3,FALSE),""))</f>
         <v/>
       </c>
-      <c r="D26" s="14">
+      <c r="D26" s="15">
         <f>IF(B26="","",IFERROR(VLOOKUP(B26,'Raw Export (Scuba TSV)'!$A$5:$E$1478,4,FALSE),""))</f>
         <v/>
       </c>
-      <c r="E26" s="13">
+      <c r="E26" s="14">
         <f>IF(B26="","",IFERROR(VLOOKUP(B26,'Raw Export (Scuba TSV)'!$A$5:$E$1478,5,FALSE),""))</f>
         <v/>
       </c>
-      <c r="F26" s="15" t="n"/>
-      <c r="G26" s="16">
+      <c r="F26" s="16" t="n"/>
+      <c r="G26" s="17">
         <f>IF(OR(B26="",F26=""),"",IF(E26=F26,"Match","ERROR"))</f>
         <v/>
       </c>
-      <c r="H26" s="7" t="n"/>
+      <c r="H26" s="18" t="n"/>
     </row>
     <row r="27">
       <c r="A27" s="5" t="n"/>
@@ -40839,32 +40845,32 @@
         <f>IF(OR(B27="",F27=""),"",IF(E27=F27,"Match","ERROR"))</f>
         <v/>
       </c>
-      <c r="H27" s="5" t="n"/>
+      <c r="H27" s="13" t="n"/>
     </row>
     <row r="28">
       <c r="A28" s="7" t="n"/>
-      <c r="B28" s="13">
+      <c r="B28" s="14">
         <f>IF(A28="","",IFERROR(INDEX(FILTER('Audit Sample List'!$A$5:$A$48,'Audit Sample List'!$B$5:$B$48=A28),COUNTIF($A$5:A28,A28)),""))</f>
         <v/>
       </c>
-      <c r="C28" s="13">
+      <c r="C28" s="14">
         <f>IF(B28="","",IFERROR(VLOOKUP(B28,'Raw Export (Scuba TSV)'!$A$5:$E$1478,3,FALSE),""))</f>
         <v/>
       </c>
-      <c r="D28" s="14">
+      <c r="D28" s="15">
         <f>IF(B28="","",IFERROR(VLOOKUP(B28,'Raw Export (Scuba TSV)'!$A$5:$E$1478,4,FALSE),""))</f>
         <v/>
       </c>
-      <c r="E28" s="13">
+      <c r="E28" s="14">
         <f>IF(B28="","",IFERROR(VLOOKUP(B28,'Raw Export (Scuba TSV)'!$A$5:$E$1478,5,FALSE),""))</f>
         <v/>
       </c>
-      <c r="F28" s="15" t="n"/>
-      <c r="G28" s="16">
+      <c r="F28" s="16" t="n"/>
+      <c r="G28" s="17">
         <f>IF(OR(B28="",F28=""),"",IF(E28=F28,"Match","ERROR"))</f>
         <v/>
       </c>
-      <c r="H28" s="7" t="n"/>
+      <c r="H28" s="18" t="n"/>
     </row>
     <row r="29">
       <c r="A29" s="5" t="n"/>
@@ -40889,32 +40895,32 @@
         <f>IF(OR(B29="",F29=""),"",IF(E29=F29,"Match","ERROR"))</f>
         <v/>
       </c>
-      <c r="H29" s="5" t="n"/>
+      <c r="H29" s="13" t="n"/>
     </row>
     <row r="30">
       <c r="A30" s="7" t="n"/>
-      <c r="B30" s="13">
+      <c r="B30" s="14">
         <f>IF(A30="","",IFERROR(INDEX(FILTER('Audit Sample List'!$A$5:$A$48,'Audit Sample List'!$B$5:$B$48=A30),COUNTIF($A$5:A30,A30)),""))</f>
         <v/>
       </c>
-      <c r="C30" s="13">
+      <c r="C30" s="14">
         <f>IF(B30="","",IFERROR(VLOOKUP(B30,'Raw Export (Scuba TSV)'!$A$5:$E$1478,3,FALSE),""))</f>
         <v/>
       </c>
-      <c r="D30" s="14">
+      <c r="D30" s="15">
         <f>IF(B30="","",IFERROR(VLOOKUP(B30,'Raw Export (Scuba TSV)'!$A$5:$E$1478,4,FALSE),""))</f>
         <v/>
       </c>
-      <c r="E30" s="13">
+      <c r="E30" s="14">
         <f>IF(B30="","",IFERROR(VLOOKUP(B30,'Raw Export (Scuba TSV)'!$A$5:$E$1478,5,FALSE),""))</f>
         <v/>
       </c>
-      <c r="F30" s="15" t="n"/>
-      <c r="G30" s="16">
+      <c r="F30" s="16" t="n"/>
+      <c r="G30" s="17">
         <f>IF(OR(B30="",F30=""),"",IF(E30=F30,"Match","ERROR"))</f>
         <v/>
       </c>
-      <c r="H30" s="7" t="n"/>
+      <c r="H30" s="18" t="n"/>
     </row>
     <row r="31">
       <c r="A31" s="5" t="n"/>
@@ -40939,32 +40945,32 @@
         <f>IF(OR(B31="",F31=""),"",IF(E31=F31,"Match","ERROR"))</f>
         <v/>
       </c>
-      <c r="H31" s="5" t="n"/>
+      <c r="H31" s="13" t="n"/>
     </row>
     <row r="32">
       <c r="A32" s="7" t="n"/>
-      <c r="B32" s="13">
+      <c r="B32" s="14">
         <f>IF(A32="","",IFERROR(INDEX(FILTER('Audit Sample List'!$A$5:$A$48,'Audit Sample List'!$B$5:$B$48=A32),COUNTIF($A$5:A32,A32)),""))</f>
         <v/>
       </c>
-      <c r="C32" s="13">
+      <c r="C32" s="14">
         <f>IF(B32="","",IFERROR(VLOOKUP(B32,'Raw Export (Scuba TSV)'!$A$5:$E$1478,3,FALSE),""))</f>
         <v/>
       </c>
-      <c r="D32" s="14">
+      <c r="D32" s="15">
         <f>IF(B32="","",IFERROR(VLOOKUP(B32,'Raw Export (Scuba TSV)'!$A$5:$E$1478,4,FALSE),""))</f>
         <v/>
       </c>
-      <c r="E32" s="13">
+      <c r="E32" s="14">
         <f>IF(B32="","",IFERROR(VLOOKUP(B32,'Raw Export (Scuba TSV)'!$A$5:$E$1478,5,FALSE),""))</f>
         <v/>
       </c>
-      <c r="F32" s="15" t="n"/>
-      <c r="G32" s="16">
+      <c r="F32" s="16" t="n"/>
+      <c r="G32" s="17">
         <f>IF(OR(B32="",F32=""),"",IF(E32=F32,"Match","ERROR"))</f>
         <v/>
       </c>
-      <c r="H32" s="7" t="n"/>
+      <c r="H32" s="18" t="n"/>
     </row>
     <row r="33">
       <c r="A33" s="5" t="n"/>
@@ -40989,32 +40995,32 @@
         <f>IF(OR(B33="",F33=""),"",IF(E33=F33,"Match","ERROR"))</f>
         <v/>
       </c>
-      <c r="H33" s="5" t="n"/>
+      <c r="H33" s="13" t="n"/>
     </row>
     <row r="34">
       <c r="A34" s="7" t="n"/>
-      <c r="B34" s="13">
+      <c r="B34" s="14">
         <f>IF(A34="","",IFERROR(INDEX(FILTER('Audit Sample List'!$A$5:$A$48,'Audit Sample List'!$B$5:$B$48=A34),COUNTIF($A$5:A34,A34)),""))</f>
         <v/>
       </c>
-      <c r="C34" s="13">
+      <c r="C34" s="14">
         <f>IF(B34="","",IFERROR(VLOOKUP(B34,'Raw Export (Scuba TSV)'!$A$5:$E$1478,3,FALSE),""))</f>
         <v/>
       </c>
-      <c r="D34" s="14">
+      <c r="D34" s="15">
         <f>IF(B34="","",IFERROR(VLOOKUP(B34,'Raw Export (Scuba TSV)'!$A$5:$E$1478,4,FALSE),""))</f>
         <v/>
       </c>
-      <c r="E34" s="13">
+      <c r="E34" s="14">
         <f>IF(B34="","",IFERROR(VLOOKUP(B34,'Raw Export (Scuba TSV)'!$A$5:$E$1478,5,FALSE),""))</f>
         <v/>
       </c>
-      <c r="F34" s="15" t="n"/>
-      <c r="G34" s="16">
+      <c r="F34" s="16" t="n"/>
+      <c r="G34" s="17">
         <f>IF(OR(B34="",F34=""),"",IF(E34=F34,"Match","ERROR"))</f>
         <v/>
       </c>
-      <c r="H34" s="7" t="n"/>
+      <c r="H34" s="18" t="n"/>
     </row>
     <row r="35">
       <c r="A35" s="5" t="n"/>
@@ -41039,32 +41045,32 @@
         <f>IF(OR(B35="",F35=""),"",IF(E35=F35,"Match","ERROR"))</f>
         <v/>
       </c>
-      <c r="H35" s="5" t="n"/>
+      <c r="H35" s="13" t="n"/>
     </row>
     <row r="36">
       <c r="A36" s="7" t="n"/>
-      <c r="B36" s="13">
+      <c r="B36" s="14">
         <f>IF(A36="","",IFERROR(INDEX(FILTER('Audit Sample List'!$A$5:$A$48,'Audit Sample List'!$B$5:$B$48=A36),COUNTIF($A$5:A36,A36)),""))</f>
         <v/>
       </c>
-      <c r="C36" s="13">
+      <c r="C36" s="14">
         <f>IF(B36="","",IFERROR(VLOOKUP(B36,'Raw Export (Scuba TSV)'!$A$5:$E$1478,3,FALSE),""))</f>
         <v/>
       </c>
-      <c r="D36" s="14">
+      <c r="D36" s="15">
         <f>IF(B36="","",IFERROR(VLOOKUP(B36,'Raw Export (Scuba TSV)'!$A$5:$E$1478,4,FALSE),""))</f>
         <v/>
       </c>
-      <c r="E36" s="13">
+      <c r="E36" s="14">
         <f>IF(B36="","",IFERROR(VLOOKUP(B36,'Raw Export (Scuba TSV)'!$A$5:$E$1478,5,FALSE),""))</f>
         <v/>
       </c>
-      <c r="F36" s="15" t="n"/>
-      <c r="G36" s="16">
+      <c r="F36" s="16" t="n"/>
+      <c r="G36" s="17">
         <f>IF(OR(B36="",F36=""),"",IF(E36=F36,"Match","ERROR"))</f>
         <v/>
       </c>
-      <c r="H36" s="7" t="n"/>
+      <c r="H36" s="18" t="n"/>
     </row>
     <row r="37">
       <c r="A37" s="5" t="n"/>
@@ -41089,32 +41095,32 @@
         <f>IF(OR(B37="",F37=""),"",IF(E37=F37,"Match","ERROR"))</f>
         <v/>
       </c>
-      <c r="H37" s="5" t="n"/>
+      <c r="H37" s="13" t="n"/>
     </row>
     <row r="38">
       <c r="A38" s="7" t="n"/>
-      <c r="B38" s="13">
+      <c r="B38" s="14">
         <f>IF(A38="","",IFERROR(INDEX(FILTER('Audit Sample List'!$A$5:$A$48,'Audit Sample List'!$B$5:$B$48=A38),COUNTIF($A$5:A38,A38)),""))</f>
         <v/>
       </c>
-      <c r="C38" s="13">
+      <c r="C38" s="14">
         <f>IF(B38="","",IFERROR(VLOOKUP(B38,'Raw Export (Scuba TSV)'!$A$5:$E$1478,3,FALSE),""))</f>
         <v/>
       </c>
-      <c r="D38" s="14">
+      <c r="D38" s="15">
         <f>IF(B38="","",IFERROR(VLOOKUP(B38,'Raw Export (Scuba TSV)'!$A$5:$E$1478,4,FALSE),""))</f>
         <v/>
       </c>
-      <c r="E38" s="13">
+      <c r="E38" s="14">
         <f>IF(B38="","",IFERROR(VLOOKUP(B38,'Raw Export (Scuba TSV)'!$A$5:$E$1478,5,FALSE),""))</f>
         <v/>
       </c>
-      <c r="F38" s="15" t="n"/>
-      <c r="G38" s="16">
+      <c r="F38" s="16" t="n"/>
+      <c r="G38" s="17">
         <f>IF(OR(B38="",F38=""),"",IF(E38=F38,"Match","ERROR"))</f>
         <v/>
       </c>
-      <c r="H38" s="7" t="n"/>
+      <c r="H38" s="18" t="n"/>
     </row>
     <row r="39">
       <c r="A39" s="5" t="n"/>
@@ -41139,32 +41145,32 @@
         <f>IF(OR(B39="",F39=""),"",IF(E39=F39,"Match","ERROR"))</f>
         <v/>
       </c>
-      <c r="H39" s="5" t="n"/>
+      <c r="H39" s="13" t="n"/>
     </row>
     <row r="40">
       <c r="A40" s="7" t="n"/>
-      <c r="B40" s="13">
+      <c r="B40" s="14">
         <f>IF(A40="","",IFERROR(INDEX(FILTER('Audit Sample List'!$A$5:$A$48,'Audit Sample List'!$B$5:$B$48=A40),COUNTIF($A$5:A40,A40)),""))</f>
         <v/>
       </c>
-      <c r="C40" s="13">
+      <c r="C40" s="14">
         <f>IF(B40="","",IFERROR(VLOOKUP(B40,'Raw Export (Scuba TSV)'!$A$5:$E$1478,3,FALSE),""))</f>
         <v/>
       </c>
-      <c r="D40" s="14">
+      <c r="D40" s="15">
         <f>IF(B40="","",IFERROR(VLOOKUP(B40,'Raw Export (Scuba TSV)'!$A$5:$E$1478,4,FALSE),""))</f>
         <v/>
       </c>
-      <c r="E40" s="13">
+      <c r="E40" s="14">
         <f>IF(B40="","",IFERROR(VLOOKUP(B40,'Raw Export (Scuba TSV)'!$A$5:$E$1478,5,FALSE),""))</f>
         <v/>
       </c>
-      <c r="F40" s="15" t="n"/>
-      <c r="G40" s="16">
+      <c r="F40" s="16" t="n"/>
+      <c r="G40" s="17">
         <f>IF(OR(B40="",F40=""),"",IF(E40=F40,"Match","ERROR"))</f>
         <v/>
       </c>
-      <c r="H40" s="7" t="n"/>
+      <c r="H40" s="18" t="n"/>
     </row>
     <row r="41">
       <c r="A41" s="5" t="n"/>
@@ -41189,32 +41195,32 @@
         <f>IF(OR(B41="",F41=""),"",IF(E41=F41,"Match","ERROR"))</f>
         <v/>
       </c>
-      <c r="H41" s="5" t="n"/>
+      <c r="H41" s="13" t="n"/>
     </row>
     <row r="42">
       <c r="A42" s="7" t="n"/>
-      <c r="B42" s="13">
+      <c r="B42" s="14">
         <f>IF(A42="","",IFERROR(INDEX(FILTER('Audit Sample List'!$A$5:$A$48,'Audit Sample List'!$B$5:$B$48=A42),COUNTIF($A$5:A42,A42)),""))</f>
         <v/>
       </c>
-      <c r="C42" s="13">
+      <c r="C42" s="14">
         <f>IF(B42="","",IFERROR(VLOOKUP(B42,'Raw Export (Scuba TSV)'!$A$5:$E$1478,3,FALSE),""))</f>
         <v/>
       </c>
-      <c r="D42" s="14">
+      <c r="D42" s="15">
         <f>IF(B42="","",IFERROR(VLOOKUP(B42,'Raw Export (Scuba TSV)'!$A$5:$E$1478,4,FALSE),""))</f>
         <v/>
       </c>
-      <c r="E42" s="13">
+      <c r="E42" s="14">
         <f>IF(B42="","",IFERROR(VLOOKUP(B42,'Raw Export (Scuba TSV)'!$A$5:$E$1478,5,FALSE),""))</f>
         <v/>
       </c>
-      <c r="F42" s="15" t="n"/>
-      <c r="G42" s="16">
+      <c r="F42" s="16" t="n"/>
+      <c r="G42" s="17">
         <f>IF(OR(B42="",F42=""),"",IF(E42=F42,"Match","ERROR"))</f>
         <v/>
       </c>
-      <c r="H42" s="7" t="n"/>
+      <c r="H42" s="18" t="n"/>
     </row>
     <row r="43">
       <c r="A43" s="5" t="n"/>
@@ -41239,32 +41245,32 @@
         <f>IF(OR(B43="",F43=""),"",IF(E43=F43,"Match","ERROR"))</f>
         <v/>
       </c>
-      <c r="H43" s="5" t="n"/>
+      <c r="H43" s="13" t="n"/>
     </row>
     <row r="44">
       <c r="A44" s="7" t="n"/>
-      <c r="B44" s="13">
+      <c r="B44" s="14">
         <f>IF(A44="","",IFERROR(INDEX(FILTER('Audit Sample List'!$A$5:$A$48,'Audit Sample List'!$B$5:$B$48=A44),COUNTIF($A$5:A44,A44)),""))</f>
         <v/>
       </c>
-      <c r="C44" s="13">
+      <c r="C44" s="14">
         <f>IF(B44="","",IFERROR(VLOOKUP(B44,'Raw Export (Scuba TSV)'!$A$5:$E$1478,3,FALSE),""))</f>
         <v/>
       </c>
-      <c r="D44" s="14">
+      <c r="D44" s="15">
         <f>IF(B44="","",IFERROR(VLOOKUP(B44,'Raw Export (Scuba TSV)'!$A$5:$E$1478,4,FALSE),""))</f>
         <v/>
       </c>
-      <c r="E44" s="13">
+      <c r="E44" s="14">
         <f>IF(B44="","",IFERROR(VLOOKUP(B44,'Raw Export (Scuba TSV)'!$A$5:$E$1478,5,FALSE),""))</f>
         <v/>
       </c>
-      <c r="F44" s="15" t="n"/>
-      <c r="G44" s="16">
+      <c r="F44" s="16" t="n"/>
+      <c r="G44" s="17">
         <f>IF(OR(B44="",F44=""),"",IF(E44=F44,"Match","ERROR"))</f>
         <v/>
       </c>
-      <c r="H44" s="7" t="n"/>
+      <c r="H44" s="18" t="n"/>
     </row>
     <row r="45">
       <c r="A45" s="5" t="n"/>
@@ -41289,32 +41295,32 @@
         <f>IF(OR(B45="",F45=""),"",IF(E45=F45,"Match","ERROR"))</f>
         <v/>
       </c>
-      <c r="H45" s="5" t="n"/>
+      <c r="H45" s="13" t="n"/>
     </row>
     <row r="46">
       <c r="A46" s="7" t="n"/>
-      <c r="B46" s="13">
+      <c r="B46" s="14">
         <f>IF(A46="","",IFERROR(INDEX(FILTER('Audit Sample List'!$A$5:$A$48,'Audit Sample List'!$B$5:$B$48=A46),COUNTIF($A$5:A46,A46)),""))</f>
         <v/>
       </c>
-      <c r="C46" s="13">
+      <c r="C46" s="14">
         <f>IF(B46="","",IFERROR(VLOOKUP(B46,'Raw Export (Scuba TSV)'!$A$5:$E$1478,3,FALSE),""))</f>
         <v/>
       </c>
-      <c r="D46" s="14">
+      <c r="D46" s="15">
         <f>IF(B46="","",IFERROR(VLOOKUP(B46,'Raw Export (Scuba TSV)'!$A$5:$E$1478,4,FALSE),""))</f>
         <v/>
       </c>
-      <c r="E46" s="13">
+      <c r="E46" s="14">
         <f>IF(B46="","",IFERROR(VLOOKUP(B46,'Raw Export (Scuba TSV)'!$A$5:$E$1478,5,FALSE),""))</f>
         <v/>
       </c>
-      <c r="F46" s="15" t="n"/>
-      <c r="G46" s="16">
+      <c r="F46" s="16" t="n"/>
+      <c r="G46" s="17">
         <f>IF(OR(B46="",F46=""),"",IF(E46=F46,"Match","ERROR"))</f>
         <v/>
       </c>
-      <c r="H46" s="7" t="n"/>
+      <c r="H46" s="18" t="n"/>
     </row>
     <row r="47">
       <c r="A47" s="5" t="n"/>
@@ -41339,32 +41345,32 @@
         <f>IF(OR(B47="",F47=""),"",IF(E47=F47,"Match","ERROR"))</f>
         <v/>
       </c>
-      <c r="H47" s="5" t="n"/>
+      <c r="H47" s="13" t="n"/>
     </row>
     <row r="48">
       <c r="A48" s="7" t="n"/>
-      <c r="B48" s="13">
+      <c r="B48" s="14">
         <f>IF(A48="","",IFERROR(INDEX(FILTER('Audit Sample List'!$A$5:$A$48,'Audit Sample List'!$B$5:$B$48=A48),COUNTIF($A$5:A48,A48)),""))</f>
         <v/>
       </c>
-      <c r="C48" s="13">
+      <c r="C48" s="14">
         <f>IF(B48="","",IFERROR(VLOOKUP(B48,'Raw Export (Scuba TSV)'!$A$5:$E$1478,3,FALSE),""))</f>
         <v/>
       </c>
-      <c r="D48" s="14">
+      <c r="D48" s="15">
         <f>IF(B48="","",IFERROR(VLOOKUP(B48,'Raw Export (Scuba TSV)'!$A$5:$E$1478,4,FALSE),""))</f>
         <v/>
       </c>
-      <c r="E48" s="13">
+      <c r="E48" s="14">
         <f>IF(B48="","",IFERROR(VLOOKUP(B48,'Raw Export (Scuba TSV)'!$A$5:$E$1478,5,FALSE),""))</f>
         <v/>
       </c>
-      <c r="F48" s="15" t="n"/>
-      <c r="G48" s="16">
+      <c r="F48" s="16" t="n"/>
+      <c r="G48" s="17">
         <f>IF(OR(B48="",F48=""),"",IF(E48=F48,"Match","ERROR"))</f>
         <v/>
       </c>
-      <c r="H48" s="7" t="n"/>
+      <c r="H48" s="18" t="n"/>
     </row>
     <row r="49">
       <c r="A49" s="5" t="n"/>
@@ -41389,32 +41395,32 @@
         <f>IF(OR(B49="",F49=""),"",IF(E49=F49,"Match","ERROR"))</f>
         <v/>
       </c>
-      <c r="H49" s="5" t="n"/>
+      <c r="H49" s="13" t="n"/>
     </row>
     <row r="50">
       <c r="A50" s="7" t="n"/>
-      <c r="B50" s="13">
+      <c r="B50" s="14">
         <f>IF(A50="","",IFERROR(INDEX(FILTER('Audit Sample List'!$A$5:$A$48,'Audit Sample List'!$B$5:$B$48=A50),COUNTIF($A$5:A50,A50)),""))</f>
         <v/>
       </c>
-      <c r="C50" s="13">
+      <c r="C50" s="14">
         <f>IF(B50="","",IFERROR(VLOOKUP(B50,'Raw Export (Scuba TSV)'!$A$5:$E$1478,3,FALSE),""))</f>
         <v/>
       </c>
-      <c r="D50" s="14">
+      <c r="D50" s="15">
         <f>IF(B50="","",IFERROR(VLOOKUP(B50,'Raw Export (Scuba TSV)'!$A$5:$E$1478,4,FALSE),""))</f>
         <v/>
       </c>
-      <c r="E50" s="13">
+      <c r="E50" s="14">
         <f>IF(B50="","",IFERROR(VLOOKUP(B50,'Raw Export (Scuba TSV)'!$A$5:$E$1478,5,FALSE),""))</f>
         <v/>
       </c>
-      <c r="F50" s="15" t="n"/>
-      <c r="G50" s="16">
+      <c r="F50" s="16" t="n"/>
+      <c r="G50" s="17">
         <f>IF(OR(B50="",F50=""),"",IF(E50=F50,"Match","ERROR"))</f>
         <v/>
       </c>
-      <c r="H50" s="7" t="n"/>
+      <c r="H50" s="18" t="n"/>
     </row>
     <row r="51">
       <c r="A51" s="5" t="n"/>
@@ -41439,32 +41445,32 @@
         <f>IF(OR(B51="",F51=""),"",IF(E51=F51,"Match","ERROR"))</f>
         <v/>
       </c>
-      <c r="H51" s="5" t="n"/>
+      <c r="H51" s="13" t="n"/>
     </row>
     <row r="52">
       <c r="A52" s="7" t="n"/>
-      <c r="B52" s="13">
+      <c r="B52" s="14">
         <f>IF(A52="","",IFERROR(INDEX(FILTER('Audit Sample List'!$A$5:$A$48,'Audit Sample List'!$B$5:$B$48=A52),COUNTIF($A$5:A52,A52)),""))</f>
         <v/>
       </c>
-      <c r="C52" s="13">
+      <c r="C52" s="14">
         <f>IF(B52="","",IFERROR(VLOOKUP(B52,'Raw Export (Scuba TSV)'!$A$5:$E$1478,3,FALSE),""))</f>
         <v/>
       </c>
-      <c r="D52" s="14">
+      <c r="D52" s="15">
         <f>IF(B52="","",IFERROR(VLOOKUP(B52,'Raw Export (Scuba TSV)'!$A$5:$E$1478,4,FALSE),""))</f>
         <v/>
       </c>
-      <c r="E52" s="13">
+      <c r="E52" s="14">
         <f>IF(B52="","",IFERROR(VLOOKUP(B52,'Raw Export (Scuba TSV)'!$A$5:$E$1478,5,FALSE),""))</f>
         <v/>
       </c>
-      <c r="F52" s="15" t="n"/>
-      <c r="G52" s="16">
+      <c r="F52" s="16" t="n"/>
+      <c r="G52" s="17">
         <f>IF(OR(B52="",F52=""),"",IF(E52=F52,"Match","ERROR"))</f>
         <v/>
       </c>
-      <c r="H52" s="7" t="n"/>
+      <c r="H52" s="18" t="n"/>
     </row>
     <row r="53">
       <c r="A53" s="5" t="n"/>
@@ -41489,32 +41495,32 @@
         <f>IF(OR(B53="",F53=""),"",IF(E53=F53,"Match","ERROR"))</f>
         <v/>
       </c>
-      <c r="H53" s="5" t="n"/>
+      <c r="H53" s="13" t="n"/>
     </row>
     <row r="54">
       <c r="A54" s="7" t="n"/>
-      <c r="B54" s="13">
+      <c r="B54" s="14">
         <f>IF(A54="","",IFERROR(INDEX(FILTER('Audit Sample List'!$A$5:$A$48,'Audit Sample List'!$B$5:$B$48=A54),COUNTIF($A$5:A54,A54)),""))</f>
         <v/>
       </c>
-      <c r="C54" s="13">
+      <c r="C54" s="14">
         <f>IF(B54="","",IFERROR(VLOOKUP(B54,'Raw Export (Scuba TSV)'!$A$5:$E$1478,3,FALSE),""))</f>
         <v/>
       </c>
-      <c r="D54" s="14">
+      <c r="D54" s="15">
         <f>IF(B54="","",IFERROR(VLOOKUP(B54,'Raw Export (Scuba TSV)'!$A$5:$E$1478,4,FALSE),""))</f>
         <v/>
       </c>
-      <c r="E54" s="13">
+      <c r="E54" s="14">
         <f>IF(B54="","",IFERROR(VLOOKUP(B54,'Raw Export (Scuba TSV)'!$A$5:$E$1478,5,FALSE),""))</f>
         <v/>
       </c>
-      <c r="F54" s="15" t="n"/>
-      <c r="G54" s="16">
+      <c r="F54" s="16" t="n"/>
+      <c r="G54" s="17">
         <f>IF(OR(B54="",F54=""),"",IF(E54=F54,"Match","ERROR"))</f>
         <v/>
       </c>
-      <c r="H54" s="7" t="n"/>
+      <c r="H54" s="18" t="n"/>
     </row>
     <row r="55">
       <c r="A55" s="5" t="n"/>
@@ -41539,32 +41545,32 @@
         <f>IF(OR(B55="",F55=""),"",IF(E55=F55,"Match","ERROR"))</f>
         <v/>
       </c>
-      <c r="H55" s="5" t="n"/>
+      <c r="H55" s="13" t="n"/>
     </row>
     <row r="56">
       <c r="A56" s="7" t="n"/>
-      <c r="B56" s="13">
+      <c r="B56" s="14">
         <f>IF(A56="","",IFERROR(INDEX(FILTER('Audit Sample List'!$A$5:$A$48,'Audit Sample List'!$B$5:$B$48=A56),COUNTIF($A$5:A56,A56)),""))</f>
         <v/>
       </c>
-      <c r="C56" s="13">
+      <c r="C56" s="14">
         <f>IF(B56="","",IFERROR(VLOOKUP(B56,'Raw Export (Scuba TSV)'!$A$5:$E$1478,3,FALSE),""))</f>
         <v/>
       </c>
-      <c r="D56" s="14">
+      <c r="D56" s="15">
         <f>IF(B56="","",IFERROR(VLOOKUP(B56,'Raw Export (Scuba TSV)'!$A$5:$E$1478,4,FALSE),""))</f>
         <v/>
       </c>
-      <c r="E56" s="13">
+      <c r="E56" s="14">
         <f>IF(B56="","",IFERROR(VLOOKUP(B56,'Raw Export (Scuba TSV)'!$A$5:$E$1478,5,FALSE),""))</f>
         <v/>
       </c>
-      <c r="F56" s="15" t="n"/>
-      <c r="G56" s="16">
+      <c r="F56" s="16" t="n"/>
+      <c r="G56" s="17">
         <f>IF(OR(B56="",F56=""),"",IF(E56=F56,"Match","ERROR"))</f>
         <v/>
       </c>
-      <c r="H56" s="7" t="n"/>
+      <c r="H56" s="18" t="n"/>
     </row>
     <row r="57">
       <c r="A57" s="5" t="n"/>
@@ -41589,32 +41595,32 @@
         <f>IF(OR(B57="",F57=""),"",IF(E57=F57,"Match","ERROR"))</f>
         <v/>
       </c>
-      <c r="H57" s="5" t="n"/>
+      <c r="H57" s="13" t="n"/>
     </row>
     <row r="58">
       <c r="A58" s="7" t="n"/>
-      <c r="B58" s="13">
+      <c r="B58" s="14">
         <f>IF(A58="","",IFERROR(INDEX(FILTER('Audit Sample List'!$A$5:$A$48,'Audit Sample List'!$B$5:$B$48=A58),COUNTIF($A$5:A58,A58)),""))</f>
         <v/>
       </c>
-      <c r="C58" s="13">
+      <c r="C58" s="14">
         <f>IF(B58="","",IFERROR(VLOOKUP(B58,'Raw Export (Scuba TSV)'!$A$5:$E$1478,3,FALSE),""))</f>
         <v/>
       </c>
-      <c r="D58" s="14">
+      <c r="D58" s="15">
         <f>IF(B58="","",IFERROR(VLOOKUP(B58,'Raw Export (Scuba TSV)'!$A$5:$E$1478,4,FALSE),""))</f>
         <v/>
       </c>
-      <c r="E58" s="13">
+      <c r="E58" s="14">
         <f>IF(B58="","",IFERROR(VLOOKUP(B58,'Raw Export (Scuba TSV)'!$A$5:$E$1478,5,FALSE),""))</f>
         <v/>
       </c>
-      <c r="F58" s="15" t="n"/>
-      <c r="G58" s="16">
+      <c r="F58" s="16" t="n"/>
+      <c r="G58" s="17">
         <f>IF(OR(B58="",F58=""),"",IF(E58=F58,"Match","ERROR"))</f>
         <v/>
       </c>
-      <c r="H58" s="7" t="n"/>
+      <c r="H58" s="18" t="n"/>
     </row>
     <row r="59">
       <c r="A59" s="5" t="n"/>
@@ -41639,32 +41645,32 @@
         <f>IF(OR(B59="",F59=""),"",IF(E59=F59,"Match","ERROR"))</f>
         <v/>
       </c>
-      <c r="H59" s="5" t="n"/>
+      <c r="H59" s="13" t="n"/>
     </row>
     <row r="60">
       <c r="A60" s="7" t="n"/>
-      <c r="B60" s="13">
+      <c r="B60" s="14">
         <f>IF(A60="","",IFERROR(INDEX(FILTER('Audit Sample List'!$A$5:$A$48,'Audit Sample List'!$B$5:$B$48=A60),COUNTIF($A$5:A60,A60)),""))</f>
         <v/>
       </c>
-      <c r="C60" s="13">
+      <c r="C60" s="14">
         <f>IF(B60="","",IFERROR(VLOOKUP(B60,'Raw Export (Scuba TSV)'!$A$5:$E$1478,3,FALSE),""))</f>
         <v/>
       </c>
-      <c r="D60" s="14">
+      <c r="D60" s="15">
         <f>IF(B60="","",IFERROR(VLOOKUP(B60,'Raw Export (Scuba TSV)'!$A$5:$E$1478,4,FALSE),""))</f>
         <v/>
       </c>
-      <c r="E60" s="13">
+      <c r="E60" s="14">
         <f>IF(B60="","",IFERROR(VLOOKUP(B60,'Raw Export (Scuba TSV)'!$A$5:$E$1478,5,FALSE),""))</f>
         <v/>
       </c>
-      <c r="F60" s="15" t="n"/>
-      <c r="G60" s="16">
+      <c r="F60" s="16" t="n"/>
+      <c r="G60" s="17">
         <f>IF(OR(B60="",F60=""),"",IF(E60=F60,"Match","ERROR"))</f>
         <v/>
       </c>
-      <c r="H60" s="7" t="n"/>
+      <c r="H60" s="18" t="n"/>
     </row>
     <row r="61">
       <c r="A61" s="5" t="n"/>
@@ -41689,32 +41695,32 @@
         <f>IF(OR(B61="",F61=""),"",IF(E61=F61,"Match","ERROR"))</f>
         <v/>
       </c>
-      <c r="H61" s="5" t="n"/>
+      <c r="H61" s="13" t="n"/>
     </row>
     <row r="62">
       <c r="A62" s="7" t="n"/>
-      <c r="B62" s="13">
+      <c r="B62" s="14">
         <f>IF(A62="","",IFERROR(INDEX(FILTER('Audit Sample List'!$A$5:$A$48,'Audit Sample List'!$B$5:$B$48=A62),COUNTIF($A$5:A62,A62)),""))</f>
         <v/>
       </c>
-      <c r="C62" s="13">
+      <c r="C62" s="14">
         <f>IF(B62="","",IFERROR(VLOOKUP(B62,'Raw Export (Scuba TSV)'!$A$5:$E$1478,3,FALSE),""))</f>
         <v/>
       </c>
-      <c r="D62" s="14">
+      <c r="D62" s="15">
         <f>IF(B62="","",IFERROR(VLOOKUP(B62,'Raw Export (Scuba TSV)'!$A$5:$E$1478,4,FALSE),""))</f>
         <v/>
       </c>
-      <c r="E62" s="13">
+      <c r="E62" s="14">
         <f>IF(B62="","",IFERROR(VLOOKUP(B62,'Raw Export (Scuba TSV)'!$A$5:$E$1478,5,FALSE),""))</f>
         <v/>
       </c>
-      <c r="F62" s="15" t="n"/>
-      <c r="G62" s="16">
+      <c r="F62" s="16" t="n"/>
+      <c r="G62" s="17">
         <f>IF(OR(B62="",F62=""),"",IF(E62=F62,"Match","ERROR"))</f>
         <v/>
       </c>
-      <c r="H62" s="7" t="n"/>
+      <c r="H62" s="18" t="n"/>
     </row>
     <row r="63">
       <c r="A63" s="5" t="n"/>
@@ -41739,32 +41745,32 @@
         <f>IF(OR(B63="",F63=""),"",IF(E63=F63,"Match","ERROR"))</f>
         <v/>
       </c>
-      <c r="H63" s="5" t="n"/>
+      <c r="H63" s="13" t="n"/>
     </row>
     <row r="64">
       <c r="A64" s="7" t="n"/>
-      <c r="B64" s="13">
+      <c r="B64" s="14">
         <f>IF(A64="","",IFERROR(INDEX(FILTER('Audit Sample List'!$A$5:$A$48,'Audit Sample List'!$B$5:$B$48=A64),COUNTIF($A$5:A64,A64)),""))</f>
         <v/>
       </c>
-      <c r="C64" s="13">
+      <c r="C64" s="14">
         <f>IF(B64="","",IFERROR(VLOOKUP(B64,'Raw Export (Scuba TSV)'!$A$5:$E$1478,3,FALSE),""))</f>
         <v/>
       </c>
-      <c r="D64" s="14">
+      <c r="D64" s="15">
         <f>IF(B64="","",IFERROR(VLOOKUP(B64,'Raw Export (Scuba TSV)'!$A$5:$E$1478,4,FALSE),""))</f>
         <v/>
       </c>
-      <c r="E64" s="13">
+      <c r="E64" s="14">
         <f>IF(B64="","",IFERROR(VLOOKUP(B64,'Raw Export (Scuba TSV)'!$A$5:$E$1478,5,FALSE),""))</f>
         <v/>
       </c>
-      <c r="F64" s="15" t="n"/>
-      <c r="G64" s="16">
+      <c r="F64" s="16" t="n"/>
+      <c r="G64" s="17">
         <f>IF(OR(B64="",F64=""),"",IF(E64=F64,"Match","ERROR"))</f>
         <v/>
       </c>
-      <c r="H64" s="7" t="n"/>
+      <c r="H64" s="18" t="n"/>
     </row>
   </sheetData>
   <conditionalFormatting sqref="G5:G64">
@@ -41780,7 +41786,7 @@
       <formula1>"ACT-1001,ACT-1002,ACT-1003,ACT-1004"</formula1>
     </dataValidation>
     <dataValidation sqref="F5:F64" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"No Violation,Hate Speech,Graphic Violence,Adult Nudity &amp; Sexual Activity,Bullying &amp; Harassment,Spam,Misinformation,Fraud &amp; Deceptive Practices,Child Safety,Dangerous Organizations"</formula1>
+      <formula1>"No Violation,Hate Speech,Graphic Violence,Adult Nudity &amp; Sexual Activity,Adult Sexual Solicitation &amp; Prostitution,Bullying &amp; Harassment,Spam,Fraud &amp; Deceptive Practices,Child Safety,Dangerous Organizations"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -41892,11 +41898,11 @@
         <f>COUNTIFS('QA Audit (Demo Sample)'!$B$5:$B$48,A5,'QA Audit (Demo Sample)'!$C$5:$C$48,B5,'QA Audit (Demo Sample)'!$G$5:$G$48,"ERROR")</f>
         <v/>
       </c>
-      <c r="F5" s="17">
+      <c r="F5" s="19">
         <f>IF(D5=0,"-",(D5-E5)/D5)</f>
         <v/>
       </c>
-      <c r="G5" s="17">
+      <c r="G5" s="19">
         <f>IF(C5=0,"-",D5/C5)</f>
         <v/>
       </c>
@@ -41912,23 +41918,23 @@
           <t>PRM</t>
         </is>
       </c>
-      <c r="C6" s="13">
+      <c r="C6" s="14">
         <f>COUNTIFS('Raw Export (Scuba TSV)'!$B$5:$B$1478,A6,'Raw Export (Scuba TSV)'!$C$5:$C$1478,B6)</f>
         <v/>
       </c>
-      <c r="D6" s="13">
+      <c r="D6" s="14">
         <f>COUNTIFS('QA Audit (Demo Sample)'!$B$5:$B$48,A6,'QA Audit (Demo Sample)'!$C$5:$C$48,B6)</f>
         <v/>
       </c>
-      <c r="E6" s="13">
+      <c r="E6" s="14">
         <f>COUNTIFS('QA Audit (Demo Sample)'!$B$5:$B$48,A6,'QA Audit (Demo Sample)'!$C$5:$C$48,B6,'QA Audit (Demo Sample)'!$G$5:$G$48,"ERROR")</f>
         <v/>
       </c>
-      <c r="F6" s="18">
+      <c r="F6" s="20">
         <f>IF(D6=0,"-",(D6-E6)/D6)</f>
         <v/>
       </c>
-      <c r="G6" s="18">
+      <c r="G6" s="20">
         <f>IF(C6=0,"-",D6/C6)</f>
         <v/>
       </c>
@@ -41956,11 +41962,11 @@
         <f>COUNTIFS('QA Audit (Demo Sample)'!$B$5:$B$48,A7,'QA Audit (Demo Sample)'!$C$5:$C$48,B7,'QA Audit (Demo Sample)'!$G$5:$G$48,"ERROR")</f>
         <v/>
       </c>
-      <c r="F7" s="17">
+      <c r="F7" s="19">
         <f>IF(D7=0,"-",(D7-E7)/D7)</f>
         <v/>
       </c>
-      <c r="G7" s="17">
+      <c r="G7" s="19">
         <f>IF(C7=0,"-",D7/C7)</f>
         <v/>
       </c>
@@ -41976,23 +41982,23 @@
           <t>TARGETED ENFORCEMENT</t>
         </is>
       </c>
-      <c r="C8" s="13">
+      <c r="C8" s="14">
         <f>COUNTIFS('Raw Export (Scuba TSV)'!$B$5:$B$1478,A8,'Raw Export (Scuba TSV)'!$C$5:$C$1478,B8)</f>
         <v/>
       </c>
-      <c r="D8" s="13">
+      <c r="D8" s="14">
         <f>COUNTIFS('QA Audit (Demo Sample)'!$B$5:$B$48,A8,'QA Audit (Demo Sample)'!$C$5:$C$48,B8)</f>
         <v/>
       </c>
-      <c r="E8" s="13">
+      <c r="E8" s="14">
         <f>COUNTIFS('QA Audit (Demo Sample)'!$B$5:$B$48,A8,'QA Audit (Demo Sample)'!$C$5:$C$48,B8,'QA Audit (Demo Sample)'!$G$5:$G$48,"ERROR")</f>
         <v/>
       </c>
-      <c r="F8" s="18">
+      <c r="F8" s="20">
         <f>IF(D8=0,"-",(D8-E8)/D8)</f>
         <v/>
       </c>
-      <c r="G8" s="18">
+      <c r="G8" s="20">
         <f>IF(C8=0,"-",D8/C8)</f>
         <v/>
       </c>
@@ -42020,11 +42026,11 @@
         <f>COUNTIFS('QA Audit (Demo Sample)'!$B$5:$B$48,A9,'QA Audit (Demo Sample)'!$C$5:$C$48,B9,'QA Audit (Demo Sample)'!$G$5:$G$48,"ERROR")</f>
         <v/>
       </c>
-      <c r="F9" s="17">
+      <c r="F9" s="19">
         <f>IF(D9=0,"-",(D9-E9)/D9)</f>
         <v/>
       </c>
-      <c r="G9" s="17">
+      <c r="G9" s="19">
         <f>IF(C9=0,"-",D9/C9)</f>
         <v/>
       </c>
@@ -42040,23 +42046,23 @@
           <t>MEMORIALIZATION</t>
         </is>
       </c>
-      <c r="C10" s="13">
+      <c r="C10" s="14">
         <f>COUNTIFS('Raw Export (Scuba TSV)'!$B$5:$B$1478,A10,'Raw Export (Scuba TSV)'!$C$5:$C$1478,B10)</f>
         <v/>
       </c>
-      <c r="D10" s="13">
+      <c r="D10" s="14">
         <f>COUNTIFS('QA Audit (Demo Sample)'!$B$5:$B$48,A10,'QA Audit (Demo Sample)'!$C$5:$C$48,B10)</f>
         <v/>
       </c>
-      <c r="E10" s="13">
+      <c r="E10" s="14">
         <f>COUNTIFS('QA Audit (Demo Sample)'!$B$5:$B$48,A10,'QA Audit (Demo Sample)'!$C$5:$C$48,B10,'QA Audit (Demo Sample)'!$G$5:$G$48,"ERROR")</f>
         <v/>
       </c>
-      <c r="F10" s="18">
+      <c r="F10" s="20">
         <f>IF(D10=0,"-",(D10-E10)/D10)</f>
         <v/>
       </c>
-      <c r="G10" s="18">
+      <c r="G10" s="20">
         <f>IF(C10=0,"-",D10/C10)</f>
         <v/>
       </c>
@@ -42084,11 +42090,11 @@
         <f>COUNTIFS('QA Audit (Demo Sample)'!$B$5:$B$48,A11,'QA Audit (Demo Sample)'!$C$5:$C$48,B11,'QA Audit (Demo Sample)'!$G$5:$G$48,"ERROR")</f>
         <v/>
       </c>
-      <c r="F11" s="17">
+      <c r="F11" s="19">
         <f>IF(D11=0,"-",(D11-E11)/D11)</f>
         <v/>
       </c>
-      <c r="G11" s="17">
+      <c r="G11" s="19">
         <f>IF(C11=0,"-",D11/C11)</f>
         <v/>
       </c>
@@ -42104,23 +42110,23 @@
           <t>ANZ XCHECK</t>
         </is>
       </c>
-      <c r="C12" s="13">
+      <c r="C12" s="14">
         <f>COUNTIFS('Raw Export (Scuba TSV)'!$B$5:$B$1478,A12,'Raw Export (Scuba TSV)'!$C$5:$C$1478,B12)</f>
         <v/>
       </c>
-      <c r="D12" s="13">
+      <c r="D12" s="14">
         <f>COUNTIFS('QA Audit (Demo Sample)'!$B$5:$B$48,A12,'QA Audit (Demo Sample)'!$C$5:$C$48,B12)</f>
         <v/>
       </c>
-      <c r="E12" s="13">
+      <c r="E12" s="14">
         <f>COUNTIFS('QA Audit (Demo Sample)'!$B$5:$B$48,A12,'QA Audit (Demo Sample)'!$C$5:$C$48,B12,'QA Audit (Demo Sample)'!$G$5:$G$48,"ERROR")</f>
         <v/>
       </c>
-      <c r="F12" s="18">
+      <c r="F12" s="20">
         <f>IF(D12=0,"-",(D12-E12)/D12)</f>
         <v/>
       </c>
-      <c r="G12" s="18">
+      <c r="G12" s="20">
         <f>IF(C12=0,"-",D12/C12)</f>
         <v/>
       </c>
@@ -42148,11 +42154,11 @@
         <f>COUNTIFS('QA Audit (Demo Sample)'!$B$5:$B$48,A13,'QA Audit (Demo Sample)'!$C$5:$C$48,B13,'QA Audit (Demo Sample)'!$G$5:$G$48,"ERROR")</f>
         <v/>
       </c>
-      <c r="F13" s="17">
+      <c r="F13" s="19">
         <f>IF(D13=0,"-",(D13-E13)/D13)</f>
         <v/>
       </c>
-      <c r="G13" s="17">
+      <c r="G13" s="19">
         <f>IF(C13=0,"-",D13/C13)</f>
         <v/>
       </c>
@@ -42168,23 +42174,23 @@
           <t>SUPPORT INVESTIGATION</t>
         </is>
       </c>
-      <c r="C14" s="13">
+      <c r="C14" s="14">
         <f>COUNTIFS('Raw Export (Scuba TSV)'!$B$5:$B$1478,A14,'Raw Export (Scuba TSV)'!$C$5:$C$1478,B14)</f>
         <v/>
       </c>
-      <c r="D14" s="13">
+      <c r="D14" s="14">
         <f>COUNTIFS('QA Audit (Demo Sample)'!$B$5:$B$48,A14,'QA Audit (Demo Sample)'!$C$5:$C$48,B14)</f>
         <v/>
       </c>
-      <c r="E14" s="13">
+      <c r="E14" s="14">
         <f>COUNTIFS('QA Audit (Demo Sample)'!$B$5:$B$48,A14,'QA Audit (Demo Sample)'!$C$5:$C$48,B14,'QA Audit (Demo Sample)'!$G$5:$G$48,"ERROR")</f>
         <v/>
       </c>
-      <c r="F14" s="18">
+      <c r="F14" s="20">
         <f>IF(D14=0,"-",(D14-E14)/D14)</f>
         <v/>
       </c>
-      <c r="G14" s="18">
+      <c r="G14" s="20">
         <f>IF(C14=0,"-",D14/C14)</f>
         <v/>
       </c>
@@ -42212,11 +42218,11 @@
         <f>COUNTIFS('QA Audit (Demo Sample)'!$B$5:$B$48,A15,'QA Audit (Demo Sample)'!$C$5:$C$48,B15,'QA Audit (Demo Sample)'!$G$5:$G$48,"ERROR")</f>
         <v/>
       </c>
-      <c r="F15" s="17">
+      <c r="F15" s="19">
         <f>IF(D15=0,"-",(D15-E15)/D15)</f>
         <v/>
       </c>
-      <c r="G15" s="17">
+      <c r="G15" s="19">
         <f>IF(C15=0,"-",D15/C15)</f>
         <v/>
       </c>
@@ -42232,23 +42238,23 @@
           <t>X-CHECK</t>
         </is>
       </c>
-      <c r="C16" s="13">
+      <c r="C16" s="14">
         <f>COUNTIFS('Raw Export (Scuba TSV)'!$B$5:$B$1478,A16,'Raw Export (Scuba TSV)'!$C$5:$C$1478,B16)</f>
         <v/>
       </c>
-      <c r="D16" s="13">
+      <c r="D16" s="14">
         <f>COUNTIFS('QA Audit (Demo Sample)'!$B$5:$B$48,A16,'QA Audit (Demo Sample)'!$C$5:$C$48,B16)</f>
         <v/>
       </c>
-      <c r="E16" s="13">
+      <c r="E16" s="14">
         <f>COUNTIFS('QA Audit (Demo Sample)'!$B$5:$B$48,A16,'QA Audit (Demo Sample)'!$C$5:$C$48,B16,'QA Audit (Demo Sample)'!$G$5:$G$48,"ERROR")</f>
         <v/>
       </c>
-      <c r="F16" s="18">
+      <c r="F16" s="20">
         <f>IF(D16=0,"-",(D16-E16)/D16)</f>
         <v/>
       </c>
-      <c r="G16" s="18">
+      <c r="G16" s="20">
         <f>IF(C16=0,"-",D16/C16)</f>
         <v/>
       </c>
@@ -42276,11 +42282,11 @@
         <f>COUNTIFS('QA Audit (Demo Sample)'!$B$5:$B$48,A17,'QA Audit (Demo Sample)'!$C$5:$C$48,B17,'QA Audit (Demo Sample)'!$G$5:$G$48,"ERROR")</f>
         <v/>
       </c>
-      <c r="F17" s="17">
+      <c r="F17" s="19">
         <f>IF(D17=0,"-",(D17-E17)/D17)</f>
         <v/>
       </c>
-      <c r="G17" s="17">
+      <c r="G17" s="19">
         <f>IF(C17=0,"-",D17/C17)</f>
         <v/>
       </c>
@@ -42296,23 +42302,23 @@
           <t>PROACTIVE</t>
         </is>
       </c>
-      <c r="C18" s="13">
+      <c r="C18" s="14">
         <f>COUNTIFS('Raw Export (Scuba TSV)'!$B$5:$B$1478,A18,'Raw Export (Scuba TSV)'!$C$5:$C$1478,B18)</f>
         <v/>
       </c>
-      <c r="D18" s="13">
+      <c r="D18" s="14">
         <f>COUNTIFS('QA Audit (Demo Sample)'!$B$5:$B$48,A18,'QA Audit (Demo Sample)'!$C$5:$C$48,B18)</f>
         <v/>
       </c>
-      <c r="E18" s="13">
+      <c r="E18" s="14">
         <f>COUNTIFS('QA Audit (Demo Sample)'!$B$5:$B$48,A18,'QA Audit (Demo Sample)'!$C$5:$C$48,B18,'QA Audit (Demo Sample)'!$G$5:$G$48,"ERROR")</f>
         <v/>
       </c>
-      <c r="F18" s="18">
+      <c r="F18" s="20">
         <f>IF(D18=0,"-",(D18-E18)/D18)</f>
         <v/>
       </c>
-      <c r="G18" s="18">
+      <c r="G18" s="20">
         <f>IF(C18=0,"-",D18/C18)</f>
         <v/>
       </c>
@@ -42340,11 +42346,11 @@
         <f>COUNTIFS('QA Audit (Demo Sample)'!$B$5:$B$48,A19,'QA Audit (Demo Sample)'!$C$5:$C$48,B19,'QA Audit (Demo Sample)'!$G$5:$G$48,"ERROR")</f>
         <v/>
       </c>
-      <c r="F19" s="17">
+      <c r="F19" s="19">
         <f>IF(D19=0,"-",(D19-E19)/D19)</f>
         <v/>
       </c>
-      <c r="G19" s="17">
+      <c r="G19" s="19">
         <f>IF(C19=0,"-",D19/C19)</f>
         <v/>
       </c>
@@ -42360,23 +42366,23 @@
           <t>COMMUNITY NOTES</t>
         </is>
       </c>
-      <c r="C20" s="13">
+      <c r="C20" s="14">
         <f>COUNTIFS('Raw Export (Scuba TSV)'!$B$5:$B$1478,A20,'Raw Export (Scuba TSV)'!$C$5:$C$1478,B20)</f>
         <v/>
       </c>
-      <c r="D20" s="13">
+      <c r="D20" s="14">
         <f>COUNTIFS('QA Audit (Demo Sample)'!$B$5:$B$48,A20,'QA Audit (Demo Sample)'!$C$5:$C$48,B20)</f>
         <v/>
       </c>
-      <c r="E20" s="13">
+      <c r="E20" s="14">
         <f>COUNTIFS('QA Audit (Demo Sample)'!$B$5:$B$48,A20,'QA Audit (Demo Sample)'!$C$5:$C$48,B20,'QA Audit (Demo Sample)'!$G$5:$G$48,"ERROR")</f>
         <v/>
       </c>
-      <c r="F20" s="18">
+      <c r="F20" s="20">
         <f>IF(D20=0,"-",(D20-E20)/D20)</f>
         <v/>
       </c>
-      <c r="G20" s="18">
+      <c r="G20" s="20">
         <f>IF(C20=0,"-",D20/C20)</f>
         <v/>
       </c>
@@ -42404,11 +42410,11 @@
         <f>COUNTIFS('QA Audit (Demo Sample)'!$B$5:$B$48,A21,'QA Audit (Demo Sample)'!$C$5:$C$48,B21,'QA Audit (Demo Sample)'!$G$5:$G$48,"ERROR")</f>
         <v/>
       </c>
-      <c r="F21" s="17">
+      <c r="F21" s="19">
         <f>IF(D21=0,"-",(D21-E21)/D21)</f>
         <v/>
       </c>
-      <c r="G21" s="17">
+      <c r="G21" s="19">
         <f>IF(C21=0,"-",D21/C21)</f>
         <v/>
       </c>
@@ -42424,23 +42430,23 @@
           <t>SEXTORTION APPEALS</t>
         </is>
       </c>
-      <c r="C22" s="13">
+      <c r="C22" s="14">
         <f>COUNTIFS('Raw Export (Scuba TSV)'!$B$5:$B$1478,A22,'Raw Export (Scuba TSV)'!$C$5:$C$1478,B22)</f>
         <v/>
       </c>
-      <c r="D22" s="13">
+      <c r="D22" s="14">
         <f>COUNTIFS('QA Audit (Demo Sample)'!$B$5:$B$48,A22,'QA Audit (Demo Sample)'!$C$5:$C$48,B22)</f>
         <v/>
       </c>
-      <c r="E22" s="13">
+      <c r="E22" s="14">
         <f>COUNTIFS('QA Audit (Demo Sample)'!$B$5:$B$48,A22,'QA Audit (Demo Sample)'!$C$5:$C$48,B22,'QA Audit (Demo Sample)'!$G$5:$G$48,"ERROR")</f>
         <v/>
       </c>
-      <c r="F22" s="18">
+      <c r="F22" s="20">
         <f>IF(D22=0,"-",(D22-E22)/D22)</f>
         <v/>
       </c>
-      <c r="G22" s="18">
+      <c r="G22" s="20">
         <f>IF(C22=0,"-",D22/C22)</f>
         <v/>
       </c>
@@ -42468,11 +42474,11 @@
         <f>COUNTIFS('QA Audit (Demo Sample)'!$B$5:$B$48,A23,'QA Audit (Demo Sample)'!$C$5:$C$48,B23,'QA Audit (Demo Sample)'!$G$5:$G$48,"ERROR")</f>
         <v/>
       </c>
-      <c r="F23" s="17">
+      <c r="F23" s="19">
         <f>IF(D23=0,"-",(D23-E23)/D23)</f>
         <v/>
       </c>
-      <c r="G23" s="17">
+      <c r="G23" s="19">
         <f>IF(C23=0,"-",D23/C23)</f>
         <v/>
       </c>
@@ -42488,23 +42494,23 @@
           <t>NAME AUTHENTICITY/IDENTITY</t>
         </is>
       </c>
-      <c r="C24" s="13">
+      <c r="C24" s="14">
         <f>COUNTIFS('Raw Export (Scuba TSV)'!$B$5:$B$1478,A24,'Raw Export (Scuba TSV)'!$C$5:$C$1478,B24)</f>
         <v/>
       </c>
-      <c r="D24" s="13">
+      <c r="D24" s="14">
         <f>COUNTIFS('QA Audit (Demo Sample)'!$B$5:$B$48,A24,'QA Audit (Demo Sample)'!$C$5:$C$48,B24)</f>
         <v/>
       </c>
-      <c r="E24" s="13">
+      <c r="E24" s="14">
         <f>COUNTIFS('QA Audit (Demo Sample)'!$B$5:$B$48,A24,'QA Audit (Demo Sample)'!$C$5:$C$48,B24,'QA Audit (Demo Sample)'!$G$5:$G$48,"ERROR")</f>
         <v/>
       </c>
-      <c r="F24" s="18">
+      <c r="F24" s="20">
         <f>IF(D24=0,"-",(D24-E24)/D24)</f>
         <v/>
       </c>
-      <c r="G24" s="18">
+      <c r="G24" s="20">
         <f>IF(C24=0,"-",D24/C24)</f>
         <v/>
       </c>
@@ -42532,11 +42538,11 @@
         <f>COUNTIFS('QA Audit (Demo Sample)'!$B$5:$B$48,A25,'QA Audit (Demo Sample)'!$C$5:$C$48,B25,'QA Audit (Demo Sample)'!$G$5:$G$48,"ERROR")</f>
         <v/>
       </c>
-      <c r="F25" s="17">
+      <c r="F25" s="19">
         <f>IF(D25=0,"-",(D25-E25)/D25)</f>
         <v/>
       </c>
-      <c r="G25" s="17">
+      <c r="G25" s="19">
         <f>IF(C25=0,"-",D25/C25)</f>
         <v/>
       </c>
@@ -42552,23 +42558,23 @@
           <t>ESCALATION TAGGING</t>
         </is>
       </c>
-      <c r="C26" s="13">
+      <c r="C26" s="14">
         <f>COUNTIFS('Raw Export (Scuba TSV)'!$B$5:$B$1478,A26,'Raw Export (Scuba TSV)'!$C$5:$C$1478,B26)</f>
         <v/>
       </c>
-      <c r="D26" s="13">
+      <c r="D26" s="14">
         <f>COUNTIFS('QA Audit (Demo Sample)'!$B$5:$B$48,A26,'QA Audit (Demo Sample)'!$C$5:$C$48,B26)</f>
         <v/>
       </c>
-      <c r="E26" s="13">
+      <c r="E26" s="14">
         <f>COUNTIFS('QA Audit (Demo Sample)'!$B$5:$B$48,A26,'QA Audit (Demo Sample)'!$C$5:$C$48,B26,'QA Audit (Demo Sample)'!$G$5:$G$48,"ERROR")</f>
         <v/>
       </c>
-      <c r="F26" s="18">
+      <c r="F26" s="20">
         <f>IF(D26=0,"-",(D26-E26)/D26)</f>
         <v/>
       </c>
-      <c r="G26" s="18">
+      <c r="G26" s="20">
         <f>IF(C26=0,"-",D26/C26)</f>
         <v/>
       </c>
@@ -42596,11 +42602,11 @@
         <f>COUNTIFS('QA Audit (Demo Sample)'!$B$5:$B$48,A27,'QA Audit (Demo Sample)'!$C$5:$C$48,B27,'QA Audit (Demo Sample)'!$G$5:$G$48,"ERROR")</f>
         <v/>
       </c>
-      <c r="F27" s="17">
+      <c r="F27" s="19">
         <f>IF(D27=0,"-",(D27-E27)/D27)</f>
         <v/>
       </c>
-      <c r="G27" s="17">
+      <c r="G27" s="19">
         <f>IF(C27=0,"-",D27/C27)</f>
         <v/>
       </c>
@@ -42616,23 +42622,23 @@
           <t>PRM</t>
         </is>
       </c>
-      <c r="C28" s="13">
+      <c r="C28" s="14">
         <f>COUNTIFS('Raw Export (Scuba TSV)'!$B$5:$B$1478,A28,'Raw Export (Scuba TSV)'!$C$5:$C$1478,B28)</f>
         <v/>
       </c>
-      <c r="D28" s="13">
+      <c r="D28" s="14">
         <f>COUNTIFS('QA Audit (Demo Sample)'!$B$5:$B$48,A28,'QA Audit (Demo Sample)'!$C$5:$C$48,B28)</f>
         <v/>
       </c>
-      <c r="E28" s="13">
+      <c r="E28" s="14">
         <f>COUNTIFS('QA Audit (Demo Sample)'!$B$5:$B$48,A28,'QA Audit (Demo Sample)'!$C$5:$C$48,B28,'QA Audit (Demo Sample)'!$G$5:$G$48,"ERROR")</f>
         <v/>
       </c>
-      <c r="F28" s="18">
+      <c r="F28" s="20">
         <f>IF(D28=0,"-",(D28-E28)/D28)</f>
         <v/>
       </c>
-      <c r="G28" s="18">
+      <c r="G28" s="20">
         <f>IF(C28=0,"-",D28/C28)</f>
         <v/>
       </c>
@@ -42660,11 +42666,11 @@
         <f>COUNTIFS('QA Audit (Demo Sample)'!$B$5:$B$48,A29,'QA Audit (Demo Sample)'!$C$5:$C$48,B29,'QA Audit (Demo Sample)'!$G$5:$G$48,"ERROR")</f>
         <v/>
       </c>
-      <c r="F29" s="17">
+      <c r="F29" s="19">
         <f>IF(D29=0,"-",(D29-E29)/D29)</f>
         <v/>
       </c>
-      <c r="G29" s="17">
+      <c r="G29" s="19">
         <f>IF(C29=0,"-",D29/C29)</f>
         <v/>
       </c>
@@ -42680,23 +42686,23 @@
           <t>TARGETED ENFORCEMENT</t>
         </is>
       </c>
-      <c r="C30" s="13">
+      <c r="C30" s="14">
         <f>COUNTIFS('Raw Export (Scuba TSV)'!$B$5:$B$1478,A30,'Raw Export (Scuba TSV)'!$C$5:$C$1478,B30)</f>
         <v/>
       </c>
-      <c r="D30" s="13">
+      <c r="D30" s="14">
         <f>COUNTIFS('QA Audit (Demo Sample)'!$B$5:$B$48,A30,'QA Audit (Demo Sample)'!$C$5:$C$48,B30)</f>
         <v/>
       </c>
-      <c r="E30" s="13">
+      <c r="E30" s="14">
         <f>COUNTIFS('QA Audit (Demo Sample)'!$B$5:$B$48,A30,'QA Audit (Demo Sample)'!$C$5:$C$48,B30,'QA Audit (Demo Sample)'!$G$5:$G$48,"ERROR")</f>
         <v/>
       </c>
-      <c r="F30" s="18">
+      <c r="F30" s="20">
         <f>IF(D30=0,"-",(D30-E30)/D30)</f>
         <v/>
       </c>
-      <c r="G30" s="18">
+      <c r="G30" s="20">
         <f>IF(C30=0,"-",D30/C30)</f>
         <v/>
       </c>
@@ -42724,11 +42730,11 @@
         <f>COUNTIFS('QA Audit (Demo Sample)'!$B$5:$B$48,A31,'QA Audit (Demo Sample)'!$C$5:$C$48,B31,'QA Audit (Demo Sample)'!$G$5:$G$48,"ERROR")</f>
         <v/>
       </c>
-      <c r="F31" s="17">
+      <c r="F31" s="19">
         <f>IF(D31=0,"-",(D31-E31)/D31)</f>
         <v/>
       </c>
-      <c r="G31" s="17">
+      <c r="G31" s="19">
         <f>IF(C31=0,"-",D31/C31)</f>
         <v/>
       </c>
@@ -42744,23 +42750,23 @@
           <t>MEMORIALIZATION</t>
         </is>
       </c>
-      <c r="C32" s="13">
+      <c r="C32" s="14">
         <f>COUNTIFS('Raw Export (Scuba TSV)'!$B$5:$B$1478,A32,'Raw Export (Scuba TSV)'!$C$5:$C$1478,B32)</f>
         <v/>
       </c>
-      <c r="D32" s="13">
+      <c r="D32" s="14">
         <f>COUNTIFS('QA Audit (Demo Sample)'!$B$5:$B$48,A32,'QA Audit (Demo Sample)'!$C$5:$C$48,B32)</f>
         <v/>
       </c>
-      <c r="E32" s="13">
+      <c r="E32" s="14">
         <f>COUNTIFS('QA Audit (Demo Sample)'!$B$5:$B$48,A32,'QA Audit (Demo Sample)'!$C$5:$C$48,B32,'QA Audit (Demo Sample)'!$G$5:$G$48,"ERROR")</f>
         <v/>
       </c>
-      <c r="F32" s="18">
+      <c r="F32" s="20">
         <f>IF(D32=0,"-",(D32-E32)/D32)</f>
         <v/>
       </c>
-      <c r="G32" s="18">
+      <c r="G32" s="20">
         <f>IF(C32=0,"-",D32/C32)</f>
         <v/>
       </c>
@@ -42788,11 +42794,11 @@
         <f>COUNTIFS('QA Audit (Demo Sample)'!$B$5:$B$48,A33,'QA Audit (Demo Sample)'!$C$5:$C$48,B33,'QA Audit (Demo Sample)'!$G$5:$G$48,"ERROR")</f>
         <v/>
       </c>
-      <c r="F33" s="17">
+      <c r="F33" s="19">
         <f>IF(D33=0,"-",(D33-E33)/D33)</f>
         <v/>
       </c>
-      <c r="G33" s="17">
+      <c r="G33" s="19">
         <f>IF(C33=0,"-",D33/C33)</f>
         <v/>
       </c>
@@ -42808,23 +42814,23 @@
           <t>ANZ XCHECK</t>
         </is>
       </c>
-      <c r="C34" s="13">
+      <c r="C34" s="14">
         <f>COUNTIFS('Raw Export (Scuba TSV)'!$B$5:$B$1478,A34,'Raw Export (Scuba TSV)'!$C$5:$C$1478,B34)</f>
         <v/>
       </c>
-      <c r="D34" s="13">
+      <c r="D34" s="14">
         <f>COUNTIFS('QA Audit (Demo Sample)'!$B$5:$B$48,A34,'QA Audit (Demo Sample)'!$C$5:$C$48,B34)</f>
         <v/>
       </c>
-      <c r="E34" s="13">
+      <c r="E34" s="14">
         <f>COUNTIFS('QA Audit (Demo Sample)'!$B$5:$B$48,A34,'QA Audit (Demo Sample)'!$C$5:$C$48,B34,'QA Audit (Demo Sample)'!$G$5:$G$48,"ERROR")</f>
         <v/>
       </c>
-      <c r="F34" s="18">
+      <c r="F34" s="20">
         <f>IF(D34=0,"-",(D34-E34)/D34)</f>
         <v/>
       </c>
-      <c r="G34" s="18">
+      <c r="G34" s="20">
         <f>IF(C34=0,"-",D34/C34)</f>
         <v/>
       </c>
@@ -42852,11 +42858,11 @@
         <f>COUNTIFS('QA Audit (Demo Sample)'!$B$5:$B$48,A35,'QA Audit (Demo Sample)'!$C$5:$C$48,B35,'QA Audit (Demo Sample)'!$G$5:$G$48,"ERROR")</f>
         <v/>
       </c>
-      <c r="F35" s="17">
+      <c r="F35" s="19">
         <f>IF(D35=0,"-",(D35-E35)/D35)</f>
         <v/>
       </c>
-      <c r="G35" s="17">
+      <c r="G35" s="19">
         <f>IF(C35=0,"-",D35/C35)</f>
         <v/>
       </c>
@@ -42872,23 +42878,23 @@
           <t>SUPPORT INVESTIGATION</t>
         </is>
       </c>
-      <c r="C36" s="13">
+      <c r="C36" s="14">
         <f>COUNTIFS('Raw Export (Scuba TSV)'!$B$5:$B$1478,A36,'Raw Export (Scuba TSV)'!$C$5:$C$1478,B36)</f>
         <v/>
       </c>
-      <c r="D36" s="13">
+      <c r="D36" s="14">
         <f>COUNTIFS('QA Audit (Demo Sample)'!$B$5:$B$48,A36,'QA Audit (Demo Sample)'!$C$5:$C$48,B36)</f>
         <v/>
       </c>
-      <c r="E36" s="13">
+      <c r="E36" s="14">
         <f>COUNTIFS('QA Audit (Demo Sample)'!$B$5:$B$48,A36,'QA Audit (Demo Sample)'!$C$5:$C$48,B36,'QA Audit (Demo Sample)'!$G$5:$G$48,"ERROR")</f>
         <v/>
       </c>
-      <c r="F36" s="18">
+      <c r="F36" s="20">
         <f>IF(D36=0,"-",(D36-E36)/D36)</f>
         <v/>
       </c>
-      <c r="G36" s="18">
+      <c r="G36" s="20">
         <f>IF(C36=0,"-",D36/C36)</f>
         <v/>
       </c>
@@ -42916,11 +42922,11 @@
         <f>COUNTIFS('QA Audit (Demo Sample)'!$B$5:$B$48,A37,'QA Audit (Demo Sample)'!$C$5:$C$48,B37,'QA Audit (Demo Sample)'!$G$5:$G$48,"ERROR")</f>
         <v/>
       </c>
-      <c r="F37" s="17">
+      <c r="F37" s="19">
         <f>IF(D37=0,"-",(D37-E37)/D37)</f>
         <v/>
       </c>
-      <c r="G37" s="17">
+      <c r="G37" s="19">
         <f>IF(C37=0,"-",D37/C37)</f>
         <v/>
       </c>
@@ -42936,23 +42942,23 @@
           <t>X-CHECK</t>
         </is>
       </c>
-      <c r="C38" s="13">
+      <c r="C38" s="14">
         <f>COUNTIFS('Raw Export (Scuba TSV)'!$B$5:$B$1478,A38,'Raw Export (Scuba TSV)'!$C$5:$C$1478,B38)</f>
         <v/>
       </c>
-      <c r="D38" s="13">
+      <c r="D38" s="14">
         <f>COUNTIFS('QA Audit (Demo Sample)'!$B$5:$B$48,A38,'QA Audit (Demo Sample)'!$C$5:$C$48,B38)</f>
         <v/>
       </c>
-      <c r="E38" s="13">
+      <c r="E38" s="14">
         <f>COUNTIFS('QA Audit (Demo Sample)'!$B$5:$B$48,A38,'QA Audit (Demo Sample)'!$C$5:$C$48,B38,'QA Audit (Demo Sample)'!$G$5:$G$48,"ERROR")</f>
         <v/>
       </c>
-      <c r="F38" s="18">
+      <c r="F38" s="20">
         <f>IF(D38=0,"-",(D38-E38)/D38)</f>
         <v/>
       </c>
-      <c r="G38" s="18">
+      <c r="G38" s="20">
         <f>IF(C38=0,"-",D38/C38)</f>
         <v/>
       </c>
@@ -42980,11 +42986,11 @@
         <f>COUNTIFS('QA Audit (Demo Sample)'!$B$5:$B$48,A39,'QA Audit (Demo Sample)'!$C$5:$C$48,B39,'QA Audit (Demo Sample)'!$G$5:$G$48,"ERROR")</f>
         <v/>
       </c>
-      <c r="F39" s="17">
+      <c r="F39" s="19">
         <f>IF(D39=0,"-",(D39-E39)/D39)</f>
         <v/>
       </c>
-      <c r="G39" s="17">
+      <c r="G39" s="19">
         <f>IF(C39=0,"-",D39/C39)</f>
         <v/>
       </c>
@@ -43000,23 +43006,23 @@
           <t>PROACTIVE</t>
         </is>
       </c>
-      <c r="C40" s="13">
+      <c r="C40" s="14">
         <f>COUNTIFS('Raw Export (Scuba TSV)'!$B$5:$B$1478,A40,'Raw Export (Scuba TSV)'!$C$5:$C$1478,B40)</f>
         <v/>
       </c>
-      <c r="D40" s="13">
+      <c r="D40" s="14">
         <f>COUNTIFS('QA Audit (Demo Sample)'!$B$5:$B$48,A40,'QA Audit (Demo Sample)'!$C$5:$C$48,B40)</f>
         <v/>
       </c>
-      <c r="E40" s="13">
+      <c r="E40" s="14">
         <f>COUNTIFS('QA Audit (Demo Sample)'!$B$5:$B$48,A40,'QA Audit (Demo Sample)'!$C$5:$C$48,B40,'QA Audit (Demo Sample)'!$G$5:$G$48,"ERROR")</f>
         <v/>
       </c>
-      <c r="F40" s="18">
+      <c r="F40" s="20">
         <f>IF(D40=0,"-",(D40-E40)/D40)</f>
         <v/>
       </c>
-      <c r="G40" s="18">
+      <c r="G40" s="20">
         <f>IF(C40=0,"-",D40/C40)</f>
         <v/>
       </c>
@@ -43044,11 +43050,11 @@
         <f>COUNTIFS('QA Audit (Demo Sample)'!$B$5:$B$48,A41,'QA Audit (Demo Sample)'!$C$5:$C$48,B41,'QA Audit (Demo Sample)'!$G$5:$G$48,"ERROR")</f>
         <v/>
       </c>
-      <c r="F41" s="17">
+      <c r="F41" s="19">
         <f>IF(D41=0,"-",(D41-E41)/D41)</f>
         <v/>
       </c>
-      <c r="G41" s="17">
+      <c r="G41" s="19">
         <f>IF(C41=0,"-",D41/C41)</f>
         <v/>
       </c>
@@ -43064,23 +43070,23 @@
           <t>COMMUNITY NOTES</t>
         </is>
       </c>
-      <c r="C42" s="13">
+      <c r="C42" s="14">
         <f>COUNTIFS('Raw Export (Scuba TSV)'!$B$5:$B$1478,A42,'Raw Export (Scuba TSV)'!$C$5:$C$1478,B42)</f>
         <v/>
       </c>
-      <c r="D42" s="13">
+      <c r="D42" s="14">
         <f>COUNTIFS('QA Audit (Demo Sample)'!$B$5:$B$48,A42,'QA Audit (Demo Sample)'!$C$5:$C$48,B42)</f>
         <v/>
       </c>
-      <c r="E42" s="13">
+      <c r="E42" s="14">
         <f>COUNTIFS('QA Audit (Demo Sample)'!$B$5:$B$48,A42,'QA Audit (Demo Sample)'!$C$5:$C$48,B42,'QA Audit (Demo Sample)'!$G$5:$G$48,"ERROR")</f>
         <v/>
       </c>
-      <c r="F42" s="18">
+      <c r="F42" s="20">
         <f>IF(D42=0,"-",(D42-E42)/D42)</f>
         <v/>
       </c>
-      <c r="G42" s="18">
+      <c r="G42" s="20">
         <f>IF(C42=0,"-",D42/C42)</f>
         <v/>
       </c>
@@ -43108,11 +43114,11 @@
         <f>COUNTIFS('QA Audit (Demo Sample)'!$B$5:$B$48,A43,'QA Audit (Demo Sample)'!$C$5:$C$48,B43,'QA Audit (Demo Sample)'!$G$5:$G$48,"ERROR")</f>
         <v/>
       </c>
-      <c r="F43" s="17">
+      <c r="F43" s="19">
         <f>IF(D43=0,"-",(D43-E43)/D43)</f>
         <v/>
       </c>
-      <c r="G43" s="17">
+      <c r="G43" s="19">
         <f>IF(C43=0,"-",D43/C43)</f>
         <v/>
       </c>
@@ -43128,23 +43134,23 @@
           <t>SEXTORTION APPEALS</t>
         </is>
       </c>
-      <c r="C44" s="13">
+      <c r="C44" s="14">
         <f>COUNTIFS('Raw Export (Scuba TSV)'!$B$5:$B$1478,A44,'Raw Export (Scuba TSV)'!$C$5:$C$1478,B44)</f>
         <v/>
       </c>
-      <c r="D44" s="13">
+      <c r="D44" s="14">
         <f>COUNTIFS('QA Audit (Demo Sample)'!$B$5:$B$48,A44,'QA Audit (Demo Sample)'!$C$5:$C$48,B44)</f>
         <v/>
       </c>
-      <c r="E44" s="13">
+      <c r="E44" s="14">
         <f>COUNTIFS('QA Audit (Demo Sample)'!$B$5:$B$48,A44,'QA Audit (Demo Sample)'!$C$5:$C$48,B44,'QA Audit (Demo Sample)'!$G$5:$G$48,"ERROR")</f>
         <v/>
       </c>
-      <c r="F44" s="18">
+      <c r="F44" s="20">
         <f>IF(D44=0,"-",(D44-E44)/D44)</f>
         <v/>
       </c>
-      <c r="G44" s="18">
+      <c r="G44" s="20">
         <f>IF(C44=0,"-",D44/C44)</f>
         <v/>
       </c>
@@ -43172,11 +43178,11 @@
         <f>COUNTIFS('QA Audit (Demo Sample)'!$B$5:$B$48,A45,'QA Audit (Demo Sample)'!$C$5:$C$48,B45,'QA Audit (Demo Sample)'!$G$5:$G$48,"ERROR")</f>
         <v/>
       </c>
-      <c r="F45" s="17">
+      <c r="F45" s="19">
         <f>IF(D45=0,"-",(D45-E45)/D45)</f>
         <v/>
       </c>
-      <c r="G45" s="17">
+      <c r="G45" s="19">
         <f>IF(C45=0,"-",D45/C45)</f>
         <v/>
       </c>
@@ -43192,23 +43198,23 @@
           <t>NAME AUTHENTICITY/IDENTITY</t>
         </is>
       </c>
-      <c r="C46" s="13">
+      <c r="C46" s="14">
         <f>COUNTIFS('Raw Export (Scuba TSV)'!$B$5:$B$1478,A46,'Raw Export (Scuba TSV)'!$C$5:$C$1478,B46)</f>
         <v/>
       </c>
-      <c r="D46" s="13">
+      <c r="D46" s="14">
         <f>COUNTIFS('QA Audit (Demo Sample)'!$B$5:$B$48,A46,'QA Audit (Demo Sample)'!$C$5:$C$48,B46)</f>
         <v/>
       </c>
-      <c r="E46" s="13">
+      <c r="E46" s="14">
         <f>COUNTIFS('QA Audit (Demo Sample)'!$B$5:$B$48,A46,'QA Audit (Demo Sample)'!$C$5:$C$48,B46,'QA Audit (Demo Sample)'!$G$5:$G$48,"ERROR")</f>
         <v/>
       </c>
-      <c r="F46" s="18">
+      <c r="F46" s="20">
         <f>IF(D46=0,"-",(D46-E46)/D46)</f>
         <v/>
       </c>
-      <c r="G46" s="18">
+      <c r="G46" s="20">
         <f>IF(C46=0,"-",D46/C46)</f>
         <v/>
       </c>
@@ -43236,11 +43242,11 @@
         <f>COUNTIFS('QA Audit (Demo Sample)'!$B$5:$B$48,A47,'QA Audit (Demo Sample)'!$C$5:$C$48,B47,'QA Audit (Demo Sample)'!$G$5:$G$48,"ERROR")</f>
         <v/>
       </c>
-      <c r="F47" s="17">
+      <c r="F47" s="19">
         <f>IF(D47=0,"-",(D47-E47)/D47)</f>
         <v/>
       </c>
-      <c r="G47" s="17">
+      <c r="G47" s="19">
         <f>IF(C47=0,"-",D47/C47)</f>
         <v/>
       </c>
@@ -43256,51 +43262,51 @@
           <t>ESCALATION TAGGING</t>
         </is>
       </c>
-      <c r="C48" s="13">
+      <c r="C48" s="14">
         <f>COUNTIFS('Raw Export (Scuba TSV)'!$B$5:$B$1478,A48,'Raw Export (Scuba TSV)'!$C$5:$C$1478,B48)</f>
         <v/>
       </c>
-      <c r="D48" s="13">
+      <c r="D48" s="14">
         <f>COUNTIFS('QA Audit (Demo Sample)'!$B$5:$B$48,A48,'QA Audit (Demo Sample)'!$C$5:$C$48,B48)</f>
         <v/>
       </c>
-      <c r="E48" s="13">
+      <c r="E48" s="14">
         <f>COUNTIFS('QA Audit (Demo Sample)'!$B$5:$B$48,A48,'QA Audit (Demo Sample)'!$C$5:$C$48,B48,'QA Audit (Demo Sample)'!$G$5:$G$48,"ERROR")</f>
         <v/>
       </c>
-      <c r="F48" s="18">
+      <c r="F48" s="20">
         <f>IF(D48=0,"-",(D48-E48)/D48)</f>
         <v/>
       </c>
-      <c r="G48" s="18">
+      <c r="G48" s="20">
         <f>IF(C48=0,"-",D48/C48)</f>
         <v/>
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="19" t="inlineStr">
+      <c r="A50" s="21" t="inlineStr">
         <is>
           <t>OVERALL</t>
         </is>
       </c>
       <c r="B50" s="2" t="n"/>
-      <c r="C50" s="19">
+      <c r="C50" s="21">
         <f>SUM(C5:C48)</f>
         <v/>
       </c>
-      <c r="D50" s="19">
+      <c r="D50" s="21">
         <f>SUM(D5:D48)</f>
         <v/>
       </c>
-      <c r="E50" s="19">
+      <c r="E50" s="21">
         <f>SUM(E5:E48)</f>
         <v/>
       </c>
-      <c r="F50" s="20">
+      <c r="F50" s="22">
         <f>IF(D50=0,"-",(D50-E50)/D50)</f>
         <v/>
       </c>
-      <c r="G50" s="20">
+      <c r="G50" s="22">
         <f>IF(C50=0,"-",D50/C50)</f>
         <v/>
       </c>
@@ -43361,7 +43367,7 @@
         <f>COUNTIFS('QA Audit (Demo Sample)'!$C$5:$C$48,A55,'QA Audit (Demo Sample)'!$G$5:$G$48,"ERROR")</f>
         <v/>
       </c>
-      <c r="E55" s="17">
+      <c r="E55" s="19">
         <f>IF(C55=0,"-",(C55-D55)/C55)</f>
         <v/>
       </c>
@@ -43372,19 +43378,19 @@
           <t>PRM</t>
         </is>
       </c>
-      <c r="B56" s="13">
+      <c r="B56" s="14">
         <f>COUNTIF('Raw Export (Scuba TSV)'!$C$5:$C$1478,A56)</f>
         <v/>
       </c>
-      <c r="C56" s="13">
+      <c r="C56" s="14">
         <f>COUNTIF('QA Audit (Demo Sample)'!$C$5:$C$48,A56)</f>
         <v/>
       </c>
-      <c r="D56" s="13">
+      <c r="D56" s="14">
         <f>COUNTIFS('QA Audit (Demo Sample)'!$C$5:$C$48,A56,'QA Audit (Demo Sample)'!$G$5:$G$48,"ERROR")</f>
         <v/>
       </c>
-      <c r="E56" s="18">
+      <c r="E56" s="20">
         <f>IF(C56=0,"-",(C56-D56)/C56)</f>
         <v/>
       </c>
@@ -43407,7 +43413,7 @@
         <f>COUNTIFS('QA Audit (Demo Sample)'!$C$5:$C$48,A57,'QA Audit (Demo Sample)'!$G$5:$G$48,"ERROR")</f>
         <v/>
       </c>
-      <c r="E57" s="17">
+      <c r="E57" s="19">
         <f>IF(C57=0,"-",(C57-D57)/C57)</f>
         <v/>
       </c>
@@ -43418,19 +43424,19 @@
           <t>TARGETED ENFORCEMENT</t>
         </is>
       </c>
-      <c r="B58" s="13">
+      <c r="B58" s="14">
         <f>COUNTIF('Raw Export (Scuba TSV)'!$C$5:$C$1478,A58)</f>
         <v/>
       </c>
-      <c r="C58" s="13">
+      <c r="C58" s="14">
         <f>COUNTIF('QA Audit (Demo Sample)'!$C$5:$C$48,A58)</f>
         <v/>
       </c>
-      <c r="D58" s="13">
+      <c r="D58" s="14">
         <f>COUNTIFS('QA Audit (Demo Sample)'!$C$5:$C$48,A58,'QA Audit (Demo Sample)'!$G$5:$G$48,"ERROR")</f>
         <v/>
       </c>
-      <c r="E58" s="18">
+      <c r="E58" s="20">
         <f>IF(C58=0,"-",(C58-D58)/C58)</f>
         <v/>
       </c>
@@ -43453,7 +43459,7 @@
         <f>COUNTIFS('QA Audit (Demo Sample)'!$C$5:$C$48,A59,'QA Audit (Demo Sample)'!$G$5:$G$48,"ERROR")</f>
         <v/>
       </c>
-      <c r="E59" s="17">
+      <c r="E59" s="19">
         <f>IF(C59=0,"-",(C59-D59)/C59)</f>
         <v/>
       </c>
@@ -43464,19 +43470,19 @@
           <t>MEMORIALIZATION</t>
         </is>
       </c>
-      <c r="B60" s="13">
+      <c r="B60" s="14">
         <f>COUNTIF('Raw Export (Scuba TSV)'!$C$5:$C$1478,A60)</f>
         <v/>
       </c>
-      <c r="C60" s="13">
+      <c r="C60" s="14">
         <f>COUNTIF('QA Audit (Demo Sample)'!$C$5:$C$48,A60)</f>
         <v/>
       </c>
-      <c r="D60" s="13">
+      <c r="D60" s="14">
         <f>COUNTIFS('QA Audit (Demo Sample)'!$C$5:$C$48,A60,'QA Audit (Demo Sample)'!$G$5:$G$48,"ERROR")</f>
         <v/>
       </c>
-      <c r="E60" s="18">
+      <c r="E60" s="20">
         <f>IF(C60=0,"-",(C60-D60)/C60)</f>
         <v/>
       </c>
@@ -43499,7 +43505,7 @@
         <f>COUNTIFS('QA Audit (Demo Sample)'!$C$5:$C$48,A61,'QA Audit (Demo Sample)'!$G$5:$G$48,"ERROR")</f>
         <v/>
       </c>
-      <c r="E61" s="17">
+      <c r="E61" s="19">
         <f>IF(C61=0,"-",(C61-D61)/C61)</f>
         <v/>
       </c>
@@ -43510,19 +43516,19 @@
           <t>ANZ XCHECK</t>
         </is>
       </c>
-      <c r="B62" s="13">
+      <c r="B62" s="14">
         <f>COUNTIF('Raw Export (Scuba TSV)'!$C$5:$C$1478,A62)</f>
         <v/>
       </c>
-      <c r="C62" s="13">
+      <c r="C62" s="14">
         <f>COUNTIF('QA Audit (Demo Sample)'!$C$5:$C$48,A62)</f>
         <v/>
       </c>
-      <c r="D62" s="13">
+      <c r="D62" s="14">
         <f>COUNTIFS('QA Audit (Demo Sample)'!$C$5:$C$48,A62,'QA Audit (Demo Sample)'!$G$5:$G$48,"ERROR")</f>
         <v/>
       </c>
-      <c r="E62" s="18">
+      <c r="E62" s="20">
         <f>IF(C62=0,"-",(C62-D62)/C62)</f>
         <v/>
       </c>
@@ -43545,7 +43551,7 @@
         <f>COUNTIFS('QA Audit (Demo Sample)'!$C$5:$C$48,A63,'QA Audit (Demo Sample)'!$G$5:$G$48,"ERROR")</f>
         <v/>
       </c>
-      <c r="E63" s="17">
+      <c r="E63" s="19">
         <f>IF(C63=0,"-",(C63-D63)/C63)</f>
         <v/>
       </c>
@@ -43556,19 +43562,19 @@
           <t>SUPPORT INVESTIGATION</t>
         </is>
       </c>
-      <c r="B64" s="13">
+      <c r="B64" s="14">
         <f>COUNTIF('Raw Export (Scuba TSV)'!$C$5:$C$1478,A64)</f>
         <v/>
       </c>
-      <c r="C64" s="13">
+      <c r="C64" s="14">
         <f>COUNTIF('QA Audit (Demo Sample)'!$C$5:$C$48,A64)</f>
         <v/>
       </c>
-      <c r="D64" s="13">
+      <c r="D64" s="14">
         <f>COUNTIFS('QA Audit (Demo Sample)'!$C$5:$C$48,A64,'QA Audit (Demo Sample)'!$G$5:$G$48,"ERROR")</f>
         <v/>
       </c>
-      <c r="E64" s="18">
+      <c r="E64" s="20">
         <f>IF(C64=0,"-",(C64-D64)/C64)</f>
         <v/>
       </c>
@@ -43591,30 +43597,30 @@
         <f>COUNTIFS('QA Audit (Demo Sample)'!$C$5:$C$48,A65,'QA Audit (Demo Sample)'!$G$5:$G$48,"ERROR")</f>
         <v/>
       </c>
-      <c r="E65" s="17">
+      <c r="E65" s="19">
         <f>IF(C65=0,"-",(C65-D65)/C65)</f>
         <v/>
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="19" t="inlineStr">
+      <c r="A67" s="21" t="inlineStr">
         <is>
           <t>OVERALL</t>
         </is>
       </c>
-      <c r="B67" s="19">
+      <c r="B67" s="21">
         <f>SUM(B55:B65)</f>
         <v/>
       </c>
-      <c r="C67" s="19">
+      <c r="C67" s="21">
         <f>SUM(C55:C65)</f>
         <v/>
       </c>
-      <c r="D67" s="19">
+      <c r="D67" s="21">
         <f>SUM(D55:D65)</f>
         <v/>
       </c>
-      <c r="E67" s="20">
+      <c r="E67" s="22">
         <f>IF(C67=0,"-",(C67-D67)/C67)</f>
         <v/>
       </c>
